--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -601,7 +601,7 @@
         <v>45741</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46014</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>45966</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44588</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45019</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>46135</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45726</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45623</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>46052</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>45593</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45842</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45302</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>45825</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>45982</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45926</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>45926</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45848</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>45107</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>45741</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>45315</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>45638</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45274</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>46089</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45324</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45898</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>45614</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45693</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45715</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>46041</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>46174</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>46052</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>46185</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45302</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45281</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>46136</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>46282</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>46107</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>45898</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45398</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>46176</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>45420</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>46076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>46254</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>46279</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45825</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>44876</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>45107</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>45737</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>45512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>46139</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>44887</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>45903</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>45420</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>45281</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>46101</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>45943</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>46119</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>46153</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>45338</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>46162</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>45994</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>46169</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>46174</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>46100</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>46185</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>46185</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>46094</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>46199</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>46093</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>46134</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>46254</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>45533</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>46280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>45699</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>44658</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44959</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44959</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>45120</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>45645</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>45015</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>44790</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44840</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>46101</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45884</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>46101</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>46101</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>45719</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>46141</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45820</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>45938</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>46101</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45272</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>46093</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>46153</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45604</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>45967</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45379</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45720</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>45984</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>46157</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44999</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45440</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45631</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45943</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>46185</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>46185</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>46185</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>46185</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45726</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>46097</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>46197</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>46119</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>46133</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45420</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>46094</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>46251</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44811</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>46252</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>46255</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>46217</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45728</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>45386</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>46267</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>46160</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>46259</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>46274</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>46283</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>46265</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>46282</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>45588</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45730</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>45827</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45726</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>44585</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45680</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45562</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>46113</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44519</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>44749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44775</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44886</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>44629</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>44805</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>44494</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44735</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>44775</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44462</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>44573</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44663</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44882</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44813</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>44756</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44671</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44671</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>44459</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>44599</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44658</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>44776</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>44571</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44788</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>44589</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44498</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44796</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>44785</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>44599</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44845</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>44840</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>44461</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>44785</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44734</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44684</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44795</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>44491</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45706</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>44889</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45014</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45454</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>44959</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45611</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45040</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45699</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45660</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>44585</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44637</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44656</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>45666</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45726</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45646</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45547</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>45089</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45706</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>45158</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>45158</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>45265</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>44708</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>45715</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>45104</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44840</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>44862</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>44942</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>44691</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45184</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45324</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>45117</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44756</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>44756</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45084</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44539</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45125</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45632</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44693</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44867</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45162</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45719</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>44733</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45540</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45645</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45652</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44988</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45475</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>44823</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45030</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45726</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>44589</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45468</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45146</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>45530</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>45324</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>45672</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45261</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45034</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>44951</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45463</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45420</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>44935</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23892,7 +23892,7 @@
         <v>45720</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44960</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>45084</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>45356</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44517</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>44533</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>45526</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>45681</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24496,7 +24496,7 @@
         <v>45593</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>45468</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45805</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45884</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>46094</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45245</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>45862</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>44684</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>46031</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>45744</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45905</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45715</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>46106</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>46077</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>46107</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>46105</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45161</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>45884</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>45744</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45113</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>44735</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45223</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45715</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>46070</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>44693</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45891</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>46065</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>45401</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>46107</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>46105</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45454</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45595</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45742</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45895</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45895</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>44585</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45665</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>46069</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45896</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45882</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45897</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>44735</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45898</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>45898</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>44701</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>45749</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45898</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>45898</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>45869</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45898</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>45898</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>45898</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45511</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45485</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>45630</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>46100</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45902</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>45905</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45909</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>45909</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45909</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>45909</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>44600</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>46106</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45911</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45908</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>46140</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>46030</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>44684</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>46077</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>46111</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>46111</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>46108</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45915</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>46141</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>46033</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>46141</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>44694</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45138</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45888</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45705</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45168</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>44951</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>44951</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>45923</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45896</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45784</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>45924</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45924</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31258,7 +31258,7 @@
         <v>44904</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>44962</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45660</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45926</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>46141</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>46141</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>45926</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>45926</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45931</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45931</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44942</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>46142</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>46142</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32247,7 +32247,7 @@
         <v>45586</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45930</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32393,7 +32393,7 @@
         <v>45930</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>45440</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>45203</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>45932</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45632</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45933</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>44466</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>45933</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>45933</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45932</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33143,7 +33143,7 @@
         <v>45932</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>45526</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>45666</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33367,7 +33367,7 @@
         <v>45933</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>46045</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45436</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>46147</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>45120</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45937</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>46146</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>45938</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45939</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45916</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>45939</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>46101</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45940</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45940</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>46108</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>45943</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45645</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>45944</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34741,7 +34741,7 @@
         <v>45282</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45944</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>45817</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>45672</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45645</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>45422</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>46153</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>45162</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45058</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45933</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>45952</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>44586</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45953</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45957</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>45658</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>44518</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>45084</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>46153</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>45957</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>45957</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>44756</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45547</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>46153</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>45960</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44936</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
         <v>45964</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>45719</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45965</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>44911</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45600</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>46155</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>46119</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45719</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45649</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37298,7 +37298,7 @@
         <v>46105</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>46155</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45967</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45967</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45967</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37688,7 +37688,7 @@
         <v>45966</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>45967</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>45965</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45971</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45320</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45968</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>45973</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>46155</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>45973</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45973</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>45973</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45974</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45974</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>45974</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45974</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45974</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45974</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45120</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45974</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>45974</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>45974</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45978</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>45978</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>46105</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45978</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45574</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>45312</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>46101</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39837,7 +39837,7 @@
         <v>46154</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45257</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>46107</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45912</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40149,7 +40149,7 @@
         <v>45912</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45922</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>45922</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>45922</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>45922</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45922</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>45912</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>45985</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>45912</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>45922</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>44651</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45922</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45922</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45922</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>45922</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>45987</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41397,7 +41397,7 @@
         <v>46107</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45312</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45182</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45912</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41704,7 +41704,7 @@
         <v>45757</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41777,7 +41777,7 @@
         <v>46106</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>45992</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>46105</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>46107</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>45993</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45992</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45539</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>46155</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>45660</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>46161</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>46163</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>45673</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42683,7 +42683,7 @@
         <v>45673</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>45994</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>45995</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45995</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45968</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45995</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43126,7 +43126,7 @@
         <v>45646</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>44853</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>46167</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>46031</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>46000</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>44841</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>46003</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43642,7 +43642,7 @@
         <v>46002</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43715,7 +43715,7 @@
         <v>45330</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>46002</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>46002</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>46003</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>46006</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>45217</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>46008</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>46169</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44616</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>46169</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>46169</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>44876</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>44546</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>46169</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>46169</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>46168</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>46169</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>44468</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>46168</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>45855</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>46169</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45313,7 +45313,7 @@
         <v>46168</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>44488</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>46019</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45537,7 +45537,7 @@
         <v>45967</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>44519</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>45932</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45932</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45829,7 +45829,7 @@
         <v>46019</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>45908</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45975,7 +45975,7 @@
         <v>45937</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46048,7 +46048,7 @@
         <v>45937</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45908</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45931</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46267,7 +46267,7 @@
         <v>45932</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>46022</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45090</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>46030</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>46170</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>44936</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>46003</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         <v>46030</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46856,7 +46856,7 @@
         <v>46173</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46929,7 +46929,7 @@
         <v>45312</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>46034</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47075,7 +47075,7 @@
         <v>45218</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>45412</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45595</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>46041</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45282</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47440,7 +47440,7 @@
         <v>45282</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47513,7 +47513,7 @@
         <v>45282</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>46171</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47664,7 +47664,7 @@
         <v>46045</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>46147</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>46045</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>46045</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>46176</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>45182</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44804</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>44845</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>46176</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>46052</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>45644</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48497,7 +48497,7 @@
         <v>45644</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>46052</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48653,7 +48653,7 @@
         <v>46052</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48731,7 +48731,7 @@
         <v>46178</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>46147</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48887,7 +48887,7 @@
         <v>44713</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48965,7 +48965,7 @@
         <v>46177</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>46056</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>46056</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49189,7 +49189,7 @@
         <v>45245</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>46141</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>46056</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49418,7 +49418,7 @@
         <v>45400</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>46058</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49564,7 +49564,7 @@
         <v>46058</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49637,7 +49637,7 @@
         <v>46100</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49715,7 +49715,7 @@
         <v>46177</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>45104</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>46063</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49949,7 +49949,7 @@
         <v>46063</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>46063</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50105,7 +50105,7 @@
         <v>46062</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>46062</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>46063</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>46177</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>46178</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>44910</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>46177</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45462</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>46065</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>45660</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50845,7 +50845,7 @@
         <v>45660</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50918,7 +50918,7 @@
         <v>46069</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>44741</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         <v>46181</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>46069</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51220,7 +51220,7 @@
         <v>45586</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51298,7 +51298,7 @@
         <v>46071</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51376,7 +51376,7 @@
         <v>46073</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51454,7 +51454,7 @@
         <v>46072</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51532,7 +51532,7 @@
         <v>46072</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45350</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>44498</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51756,7 +51756,7 @@
         <v>46076</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>46076</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51912,7 +51912,7 @@
         <v>46077</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45614</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52063,7 +52063,7 @@
         <v>46183</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52141,7 +52141,7 @@
         <v>46079</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         <v>45261</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>46183</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52370,7 +52370,7 @@
         <v>46184</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52448,7 +52448,7 @@
         <v>45019</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52521,7 +52521,7 @@
         <v>46185</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52594,7 +52594,7 @@
         <v>46083</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52672,7 +52672,7 @@
         <v>46185</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52750,7 +52750,7 @@
         <v>46185</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>46185</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52906,7 +52906,7 @@
         <v>46185</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52984,7 +52984,7 @@
         <v>46085</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>46185</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53140,7 +53140,7 @@
         <v>46185</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53218,7 +53218,7 @@
         <v>46085</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>44874</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53369,7 +53369,7 @@
         <v>45113</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         <v>46185</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>46185</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53598,7 +53598,7 @@
         <v>46188</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53676,7 +53676,7 @@
         <v>46185</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53754,7 +53754,7 @@
         <v>46185</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45070</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>46185</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>46185</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>46185</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>46185</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54217,7 +54217,7 @@
         <v>45026</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54290,7 +54290,7 @@
         <v>46188</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>46188</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54446,7 +54446,7 @@
         <v>46185</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54524,7 +54524,7 @@
         <v>46185</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45467</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         <v>46185</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54758,7 +54758,7 @@
         <v>46185</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54836,7 +54836,7 @@
         <v>46185</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54914,7 +54914,7 @@
         <v>46185</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>46185</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55070,7 +55070,7 @@
         <v>45702</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55143,7 +55143,7 @@
         <v>46092</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>44539</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55294,7 +55294,7 @@
         <v>46092</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>46092</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55450,7 +55450,7 @@
         <v>46094</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55528,7 +55528,7 @@
         <v>46094</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>46094</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55684,7 +55684,7 @@
         <v>46094</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>46094</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55840,7 +55840,7 @@
         <v>46094</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55918,7 +55918,7 @@
         <v>46094</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55996,7 +55996,7 @@
         <v>46094</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56074,7 +56074,7 @@
         <v>46094</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56152,7 +56152,7 @@
         <v>46094</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56230,7 +56230,7 @@
         <v>45652</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56303,7 +56303,7 @@
         <v>46093</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>46094</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>44694</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>46095</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56610,7 +56610,7 @@
         <v>44818</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56683,7 +56683,7 @@
         <v>46098</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>46132</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>46099</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>46100</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56990,7 +56990,7 @@
         <v>46196</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57068,7 +57068,7 @@
         <v>46196</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>44763</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57219,7 +57219,7 @@
         <v>46196</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57297,7 +57297,7 @@
         <v>46196</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57375,7 +57375,7 @@
         <v>45645</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57453,7 +57453,7 @@
         <v>46104</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57531,7 +57531,7 @@
         <v>46101</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>46195</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57682,7 +57682,7 @@
         <v>46104</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45540</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57828,7 +57828,7 @@
         <v>45757</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57901,7 +57901,7 @@
         <v>45757</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57974,7 +57974,7 @@
         <v>46160</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>46106</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>46198</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58208,7 +58208,7 @@
         <v>46198</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>46106</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58364,7 +58364,7 @@
         <v>46105</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58442,7 +58442,7 @@
         <v>46198</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58520,7 +58520,7 @@
         <v>46197</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>46198</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58676,7 +58676,7 @@
         <v>46198</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45243</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58827,7 +58827,7 @@
         <v>44616</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58900,7 +58900,7 @@
         <v>46198</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         <v>46198</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59056,7 +59056,7 @@
         <v>46198</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>46108</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59212,7 +59212,7 @@
         <v>45735</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59285,7 +59285,7 @@
         <v>45106</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59358,7 +59358,7 @@
         <v>45014</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>46244</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59509,7 +59509,7 @@
         <v>46202</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>46111</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59665,7 +59665,7 @@
         <v>46202</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59743,7 +59743,7 @@
         <v>44790</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59816,7 +59816,7 @@
         <v>46244</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59894,7 +59894,7 @@
         <v>45699</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59967,7 +59967,7 @@
         <v>46120</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60040,7 +60040,7 @@
         <v>45373</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60113,7 +60113,7 @@
         <v>46122</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60191,7 +60191,7 @@
         <v>44885</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60264,7 +60264,7 @@
         <v>46077</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60342,7 +60342,7 @@
         <v>46244</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60420,7 +60420,7 @@
         <v>45282</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60493,7 +60493,7 @@
         <v>46125</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>46084</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60644,7 +60644,7 @@
         <v>46125</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>46124</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60790,7 +60790,7 @@
         <v>46124</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60863,7 +60863,7 @@
         <v>46124</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60936,7 +60936,7 @@
         <v>46093</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61014,7 +61014,7 @@
         <v>46128</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61092,7 +61092,7 @@
         <v>46106</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61170,7 +61170,7 @@
         <v>46104</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61248,7 +61248,7 @@
         <v>45107</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61321,7 +61321,7 @@
         <v>46128</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61399,7 +61399,7 @@
         <v>46094</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61477,7 +61477,7 @@
         <v>46106</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>46106</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61633,7 +61633,7 @@
         <v>46106</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>46132</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61789,7 +61789,7 @@
         <v>45082</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61862,7 +61862,7 @@
         <v>46132</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61940,7 +61940,7 @@
         <v>46132</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62018,7 +62018,7 @@
         <v>46246</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62091,7 +62091,7 @@
         <v>45034</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62169,7 +62169,7 @@
         <v>46133</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62247,7 +62247,7 @@
         <v>46133</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62325,7 +62325,7 @@
         <v>44973</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62398,7 +62398,7 @@
         <v>46132</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62471,7 +62471,7 @@
         <v>45397</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62549,7 +62549,7 @@
         <v>46134</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62627,7 +62627,7 @@
         <v>46134</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62705,7 +62705,7 @@
         <v>46090</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>46203</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62861,7 +62861,7 @@
         <v>46246</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62939,7 +62939,7 @@
         <v>46134</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63017,7 +63017,7 @@
         <v>46134</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63095,7 +63095,7 @@
         <v>46105</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63173,7 +63173,7 @@
         <v>44800</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63246,7 +63246,7 @@
         <v>46134</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63324,7 +63324,7 @@
         <v>46100</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63402,7 +63402,7 @@
         <v>46133</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63480,7 +63480,7 @@
         <v>46134</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63558,7 +63558,7 @@
         <v>45915</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63636,7 +63636,7 @@
         <v>46105</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63714,7 +63714,7 @@
         <v>46029</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>46107</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63865,7 +63865,7 @@
         <v>45686</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63943,7 +63943,7 @@
         <v>45945</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64016,7 +64016,7 @@
         <v>45266</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64089,7 +64089,7 @@
         <v>46107</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64167,7 +64167,7 @@
         <v>46246</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64245,7 +64245,7 @@
         <v>45414</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64318,7 +64318,7 @@
         <v>46246</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64396,7 +64396,7 @@
         <v>44922</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64469,7 +64469,7 @@
         <v>46246</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64542,7 +64542,7 @@
         <v>45631</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64620,7 +64620,7 @@
         <v>46246</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64698,7 +64698,7 @@
         <v>46246</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64776,7 +64776,7 @@
         <v>45715</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64849,7 +64849,7 @@
         <v>46251</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64927,7 +64927,7 @@
         <v>45266</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65000,7 +65000,7 @@
         <v>45660</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65073,7 +65073,7 @@
         <v>46106</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65151,7 +65151,7 @@
         <v>45950</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65224,7 +65224,7 @@
         <v>45519</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65297,7 +65297,7 @@
         <v>46248</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65375,7 +65375,7 @@
         <v>45146</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>46206</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65526,7 +65526,7 @@
         <v>44586</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65604,7 +65604,7 @@
         <v>45705</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65677,7 +65677,7 @@
         <v>45530</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65750,7 +65750,7 @@
         <v>44927</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65823,7 +65823,7 @@
         <v>46207</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65901,7 +65901,7 @@
         <v>45574</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65979,7 +65979,7 @@
         <v>46154</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66057,7 +66057,7 @@
         <v>46248</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66130,7 +66130,7 @@
         <v>45608</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66203,7 +66203,7 @@
         <v>46248</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66276,7 +66276,7 @@
         <v>44767</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66349,7 +66349,7 @@
         <v>46248</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66427,7 +66427,7 @@
         <v>44910</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66500,7 +66500,7 @@
         <v>45559</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66573,7 +66573,7 @@
         <v>46169</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66646,7 +66646,7 @@
         <v>46252</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66719,7 +66719,7 @@
         <v>46210</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66797,7 +66797,7 @@
         <v>46210</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66875,7 +66875,7 @@
         <v>45530</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66953,7 +66953,7 @@
         <v>45751</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67031,7 +67031,7 @@
         <v>46254</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67109,7 +67109,7 @@
         <v>46255</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -67187,7 +67187,7 @@
         <v>45334</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -67260,7 +67260,7 @@
         <v>46255</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -67338,7 +67338,7 @@
         <v>45392</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67411,7 +67411,7 @@
         <v>46255</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67484,7 +67484,7 @@
         <v>45089</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67557,7 +67557,7 @@
         <v>46254</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67635,7 +67635,7 @@
         <v>46213</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67713,7 +67713,7 @@
         <v>44603</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67786,7 +67786,7 @@
         <v>46258</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67864,7 +67864,7 @@
         <v>45176</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -67937,7 +67937,7 @@
         <v>45176</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68010,7 +68010,7 @@
         <v>44959</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -68083,7 +68083,7 @@
         <v>46258</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -68161,7 +68161,7 @@
         <v>46217</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -68239,7 +68239,7 @@
         <v>46213</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -68317,7 +68317,7 @@
         <v>45685</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68390,7 +68390,7 @@
         <v>46258</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68463,7 +68463,7 @@
         <v>46213</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68541,7 +68541,7 @@
         <v>45660</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68614,7 +68614,7 @@
         <v>46213</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68692,7 +68692,7 @@
         <v>45240</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68765,7 +68765,7 @@
         <v>46217</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68838,7 +68838,7 @@
         <v>46261</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -68916,7 +68916,7 @@
         <v>46260</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68989,7 +68989,7 @@
         <v>45520</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -69062,7 +69062,7 @@
         <v>45520</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -69135,7 +69135,7 @@
         <v>46261</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -69213,7 +69213,7 @@
         <v>46261</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -69291,7 +69291,7 @@
         <v>45089</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -69369,7 +69369,7 @@
         <v>44973</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69442,7 +69442,7 @@
         <v>46261</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69520,7 +69520,7 @@
         <v>45232</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69598,7 +69598,7 @@
         <v>45749</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69671,7 +69671,7 @@
         <v>46265</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69744,7 +69744,7 @@
         <v>46262</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69822,7 +69822,7 @@
         <v>46220</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -69900,7 +69900,7 @@
         <v>45090</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -69973,7 +69973,7 @@
         <v>45014</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70046,7 +70046,7 @@
         <v>45728</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -70119,7 +70119,7 @@
         <v>45306</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -70192,7 +70192,7 @@
         <v>46262</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -70265,7 +70265,7 @@
         <v>46265</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -70343,7 +70343,7 @@
         <v>46223</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70421,7 +70421,7 @@
         <v>46262</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70499,7 +70499,7 @@
         <v>46262</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70577,7 +70577,7 @@
         <v>46267</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70655,7 +70655,7 @@
         <v>46267</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70733,7 +70733,7 @@
         <v>46267</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70811,7 +70811,7 @@
         <v>45272</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -70884,7 +70884,7 @@
         <v>45523</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -70957,7 +70957,7 @@
         <v>46267</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71035,7 +71035,7 @@
         <v>46267</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -71113,7 +71113,7 @@
         <v>46269</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -71191,7 +71191,7 @@
         <v>46269</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -71269,7 +71269,7 @@
         <v>46269</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -71347,7 +71347,7 @@
         <v>45776</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71420,7 +71420,7 @@
         <v>46269</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71498,7 +71498,7 @@
         <v>46104</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71571,7 +71571,7 @@
         <v>46273</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71649,7 +71649,7 @@
         <v>46273</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71727,7 +71727,7 @@
         <v>46273</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71805,7 +71805,7 @@
         <v>45580</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -71883,7 +71883,7 @@
         <v>45782</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -71956,7 +71956,7 @@
         <v>46273</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72034,7 +72034,7 @@
         <v>46273</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72112,7 +72112,7 @@
         <v>46272</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -72185,7 +72185,7 @@
         <v>46272</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -72258,7 +72258,7 @@
         <v>46273</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -72336,7 +72336,7 @@
         <v>46272</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -72414,7 +72414,7 @@
         <v>46274</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72492,7 +72492,7 @@
         <v>45702</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72570,7 +72570,7 @@
         <v>46275</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72648,7 +72648,7 @@
         <v>46275</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72726,7 +72726,7 @@
         <v>46274</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72804,7 +72804,7 @@
         <v>46274</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -72882,7 +72882,7 @@
         <v>46276</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -72960,7 +72960,7 @@
         <v>45252</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73033,7 +73033,7 @@
         <v>46276</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73111,7 +73111,7 @@
         <v>45322</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -73184,7 +73184,7 @@
         <v>46276</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -73262,7 +73262,7 @@
         <v>46279</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -73335,7 +73335,7 @@
         <v>46276</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -73413,7 +73413,7 @@
         <v>45705</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73491,7 +73491,7 @@
         <v>46279</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73569,7 +73569,7 @@
         <v>46280</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73647,7 +73647,7 @@
         <v>46280</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73725,7 +73725,7 @@
         <v>46280</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73803,7 +73803,7 @@
         <v>46280</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -73881,7 +73881,7 @@
         <v>46280</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -73959,7 +73959,7 @@
         <v>46280</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -74037,7 +74037,7 @@
         <v>46281</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -74110,7 +74110,7 @@
         <v>46281</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -74188,7 +74188,7 @@
         <v>46280</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -74266,7 +74266,7 @@
         <v>46280</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -74344,7 +74344,7 @@
         <v>46281</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -74422,7 +74422,7 @@
         <v>45791</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -74500,7 +74500,7 @@
         <v>45791</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74573,7 +74573,7 @@
         <v>45790</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74646,7 +74646,7 @@
         <v>45791</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74719,7 +74719,7 @@
         <v>46280</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74797,7 +74797,7 @@
         <v>45790</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74870,7 +74870,7 @@
         <v>45660</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -74948,7 +74948,7 @@
         <v>46282</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -75026,7 +75026,7 @@
         <v>46239</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -75104,7 +75104,7 @@
         <v>46283</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -75182,7 +75182,7 @@
         <v>45797</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -75255,7 +75255,7 @@
         <v>46282</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -75333,7 +75333,7 @@
         <v>45623</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -75406,7 +75406,7 @@
         <v>46239</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -75484,7 +75484,7 @@
         <v>45594</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75562,7 +75562,7 @@
         <v>45797</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75635,7 +75635,7 @@
         <v>46283</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75713,7 +75713,7 @@
         <v>45632</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75786,7 +75786,7 @@
         <v>45505</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -75859,7 +75859,7 @@
         <v>46283</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -75937,7 +75937,7 @@
         <v>45798</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -76010,7 +76010,7 @@
         <v>46283</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -76088,7 +76088,7 @@
         <v>46283</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -76166,7 +76166,7 @@
         <v>46283</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -76244,7 +76244,7 @@
         <v>46283</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -76322,7 +76322,7 @@
         <v>46282</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -76400,7 +76400,7 @@
         <v>46282</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -76478,7 +76478,7 @@
         <v>46282</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -76556,7 +76556,7 @@
         <v>46282</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76634,7 +76634,7 @@
         <v>46283</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76712,7 +76712,7 @@
         <v>46282</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76790,7 +76790,7 @@
         <v>46283</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76868,7 +76868,7 @@
         <v>46283</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -76946,7 +76946,7 @@
         <v>46283</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -77024,7 +77024,7 @@
         <v>46283</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -77102,7 +77102,7 @@
         <v>46283</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -77180,7 +77180,7 @@
         <v>46283</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -77258,7 +77258,7 @@
         <v>46283</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -77336,7 +77336,7 @@
         <v>44739</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -77409,7 +77409,7 @@
         <v>45804</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -77487,7 +77487,7 @@
         <v>45813</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -77560,7 +77560,7 @@
         <v>45813</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77633,7 +77633,7 @@
         <v>45817</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77706,7 +77706,7 @@
         <v>45819</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77779,7 +77779,7 @@
         <v>45819</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77857,7 +77857,7 @@
         <v>45827</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -77930,7 +77930,7 @@
         <v>45827</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -78003,7 +78003,7 @@
         <v>45741</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -78076,7 +78076,7 @@
         <v>45827</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -78149,7 +78149,7 @@
         <v>45827</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -78222,7 +78222,7 @@
         <v>45832</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -78295,7 +78295,7 @@
         <v>45834</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -78368,7 +78368,7 @@
         <v>45835</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -78441,7 +78441,7 @@
         <v>45784</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -78514,7 +78514,7 @@
         <v>45845</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -78587,7 +78587,7 @@
         <v>45845</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78660,7 +78660,7 @@
         <v>45848</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78733,7 +78733,7 @@
         <v>45848</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78806,7 +78806,7 @@
         <v>45540</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -78879,7 +78879,7 @@
         <v>45854</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -78952,7 +78952,7 @@
         <v>45859</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -79030,7 +79030,7 @@
         <v>45862</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -79103,7 +79103,7 @@
         <v>45862</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -79181,7 +79181,7 @@
         <v>45862</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -79254,7 +79254,7 @@
         <v>45866</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -79332,7 +79332,7 @@
         <v>45867</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -79405,7 +79405,7 @@
         <v>45869</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -79478,7 +79478,7 @@
         <v>45869</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -79551,7 +79551,7 @@
         <v>45873</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -79629,7 +79629,7 @@
         <v>45545</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -79707,7 +79707,7 @@
         <v>45740</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -79785,7 +79785,7 @@
         <v>45205</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -79878,7 +79878,7 @@
         <v>44995</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -79956,7 +79956,7 @@
         <v>45376</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -80034,7 +80034,7 @@
         <v>45470</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -80112,7 +80112,7 @@
         <v>46089</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -601,7 +601,7 @@
         <v>46014</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>45966</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44588</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45019</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>46135</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45623</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45842</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45825</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45302</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45982</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45926</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45926</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>45848</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45107</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45315</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>45638</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46089</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46041</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>46052</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45614</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45693</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45715</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>46174</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>46185</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>46136</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>46282</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>45302</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>45281</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>45398</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45420</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>46076</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>45825</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>46176</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>46254</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>46279</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44587</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44876</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>45338</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>45898</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>45903</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>46100</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>46094</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>45943</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45420</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>46093</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>46134</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>45994</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>46139</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>46101</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>46153</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>44887</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>46119</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>46162</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>46169</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>46174</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>46185</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>46185</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>46199</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>46254</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45737</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>45533</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>46280</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45281</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>45792</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44658</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45884</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45120</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45588</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44735</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45943</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45730</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45604</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45938</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>46097</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45272</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45015</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>46119</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>45967</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>46133</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>45984</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>46094</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45645</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45728</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45726</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44840</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>45720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>46101</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>46101</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>46101</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45719</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>46141</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45827</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>46093</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>46101</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>46153</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>46157</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>44959</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44959</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>46185</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45726</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>46185</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>46185</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45440</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>46197</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>45631</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>46251</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>46252</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>46255</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>46217</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45420</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44790</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>46267</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>46160</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>46259</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>46274</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
         <v>46282</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>46283</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>46265</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44811</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>46287</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>46185</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>46290</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>46290</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45379</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45530</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44999</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44585</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45680</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45562</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>46113</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44749</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44519</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44775</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44886</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44629</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>44494</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>44735</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44775</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44663</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44573</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44882</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44756</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44813</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44671</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>44599</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>44658</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>44776</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44571</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>44788</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>44589</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44498</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44796</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>44785</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44599</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>44845</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>44840</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>44785</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44734</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44684</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44795</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>44491</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45715</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45715</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>44862</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45232</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>45467</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45261</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45138</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45400</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>44804</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>44876</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45373</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>44841</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45454</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45574</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45454</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45436</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>45257</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>44498</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44823</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45468</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>45594</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>46019</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45967</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>45931</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>45937</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>45855</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>46019</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45908</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45932</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45932</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45937</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>45908</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>46022</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>45932</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45623</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>46030</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45884</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>44533</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45632</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45797</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45798</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>44942</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45530</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45797</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45505</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>46030</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>46034</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>46003</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45586</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44936</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44845</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45511</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45658</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45644</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>45665</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45891</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>46041</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45895</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45895</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45896</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45898</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>45898</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>45898</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>45898</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45540</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45897</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45898</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45882</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45898</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45475</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>46045</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45898</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45902</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>46045</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45540</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45485</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45749</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45905</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>46052</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>46052</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>44889</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>44517</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>46052</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45909</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45909</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>44988</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45908</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44585</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>45909</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45909</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>45911</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>44739</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>46056</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>46056</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>46056</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>46058</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>46100</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>46058</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45915</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>45726</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45804</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>46062</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>46062</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45742</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>46063</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>46063</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45547</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>46063</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>46063</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>45888</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>46065</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>44693</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45223</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>46069</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45924</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>46069</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45923</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45586</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>46071</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45896</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>45924</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>46072</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>46072</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45926</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45030</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45019</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>46076</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>46077</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45926</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45926</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>46079</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45652</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>44691</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>45930</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>45930</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45040</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>46083</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45932</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45932</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45931</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45595</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45931</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45932</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45933</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>46085</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45933</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44951</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>44951</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>46085</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45933</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45324</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45282</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45282</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45933</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45938</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45937</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>46093</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>46092</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>46092</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44713</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45330</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>46092</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45916</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>46094</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>46094</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45939</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>46094</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>46094</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45940</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>46094</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>46095</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>46094</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>46094</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>46094</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>45939</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>46094</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>46094</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46094</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45943</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45944</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>46098</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>46099</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45944</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44708</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45699</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>46101</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45817</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>46100</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>45082</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>46104</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45462</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>46105</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>46104</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>45463</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45952</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>46106</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>46106</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>45614</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45953</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>46111</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>45933</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>46108</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45957</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>45034</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>45957</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>45960</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>46077</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>45964</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35062,7 +35062,7 @@
         <v>46120</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>46124</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>46124</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45965</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>46122</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>46124</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>46125</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>46125</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>45965</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>46093</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>46106</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>46106</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>46084</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>45967</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45967</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45967</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45968</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>45967</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45813</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>45089</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>45813</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45971</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>45672</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45974</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45974</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45974</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45974</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>45974</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45973</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44936</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45974</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>46106</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>46094</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>46104</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>44518</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>46132</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45973</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>45974</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45974</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45974</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45973</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45973</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>46106</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>46128</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45084</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>46132</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45631</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45978</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>45978</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38804,7 +38804,7 @@
         <v>46132</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
         <v>45978</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38960,7 +38960,7 @@
         <v>46128</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>44922</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>46132</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45089</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>46133</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>46105</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>46133</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>46133</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45014</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>46100</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>46134</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>46134</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>46094</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45985</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>46134</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>46134</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>45113</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>46100</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40349,7 +40349,7 @@
         <v>45922</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>45912</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45915</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>45912</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>45922</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45922</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>45922</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45922</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>46134</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>46134</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45912</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>45912</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>45922</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>45922</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>46090</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>45630</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45987</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>45184</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41743,7 +41743,7 @@
         <v>45922</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45912</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45922</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>45922</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>44694</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45992</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>46107</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45992</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>45869</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>45632</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>45993</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>45862</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>45715</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>44600</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>45994</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45660</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45995</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>46031</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>46077</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>45995</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>45968</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>44756</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>44756</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>45995</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43540,7 +43540,7 @@
         <v>46106</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43618,7 +43618,7 @@
         <v>46106</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>46000</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>46108</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45014</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45744</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>46107</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>46140</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>46002</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>46002</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>46002</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45652</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45805</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>46105</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>46105</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>46107</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44748,7 +44748,7 @@
         <v>46107</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>46069</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45817</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>46003</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>46006</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>45530</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>46003</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>45686</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>46008</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45819</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45705</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45581,7 +45581,7 @@
         <v>45784</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>46070</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>46077</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45805,7 +45805,7 @@
         <v>45089</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45685</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45956,7 +45956,7 @@
         <v>46029</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45660</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45660</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45945</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45176</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46321,7 +46321,7 @@
         <v>45176</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>46105</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>45681</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45350</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>44973</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>44589</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>45905</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>45243</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45744</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>44539</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>46031</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>46033</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>46065</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47295,7 +47295,7 @@
         <v>45741</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47368,7 +47368,7 @@
         <v>46141</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>45026</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>46141</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>46030</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47670,7 +47670,7 @@
         <v>46111</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47748,7 +47748,7 @@
         <v>46111</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>46141</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45827</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>45827</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48050,7 +48050,7 @@
         <v>45245</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>46142</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>45320</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45827</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>45014</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
         <v>46141</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45827</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>46142</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>46045</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45706</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45203</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>46146</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>46108</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>46147</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45070</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>46101</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>45757</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45757</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>45090</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49472,7 +49472,7 @@
         <v>45832</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49545,7 +49545,7 @@
         <v>45757</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>46101</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>46154</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45272</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>44874</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
         <v>44867</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>46153</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>46153</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>46153</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>45834</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>46155</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>46155</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>46119</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50519,7 +50519,7 @@
         <v>46105</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>46155</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>46105</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45835</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>46155</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>45334</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>46105</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>46107</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>46106</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>46107</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>45107</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>46161</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>45526</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51513,7 +51513,7 @@
         <v>45312</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>46107</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45845</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51737,7 +51737,7 @@
         <v>45784</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45845</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>46163</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45848</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>46168</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45645</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>46167</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52263,7 +52263,7 @@
         <v>45672</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52341,7 +52341,7 @@
         <v>46168</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52419,7 +52419,7 @@
         <v>45848</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52492,7 +52492,7 @@
         <v>45540</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45660</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52638,7 +52638,7 @@
         <v>45660</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52711,7 +52711,7 @@
         <v>45117</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>44935</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45854</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>46168</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53013,7 +53013,7 @@
         <v>45113</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>46169</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>46169</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>46169</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53320,7 +53320,7 @@
         <v>46169</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53398,7 +53398,7 @@
         <v>46169</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53476,7 +53476,7 @@
         <v>46169</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53554,7 +53554,7 @@
         <v>46169</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53632,7 +53632,7 @@
         <v>45859</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45862</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53788,7 +53788,7 @@
         <v>45162</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45862</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45600</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54007,7 +54007,7 @@
         <v>45862</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54080,7 +54080,7 @@
         <v>46173</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54153,7 +54153,7 @@
         <v>46170</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45519</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45539</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54372,7 +54372,7 @@
         <v>44910</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54445,7 +54445,7 @@
         <v>44910</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54518,7 +54518,7 @@
         <v>45866</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>44885</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54669,7 +54669,7 @@
         <v>45867</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54742,7 +54742,7 @@
         <v>46147</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54820,7 +54820,7 @@
         <v>46177</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>46177</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54971,7 +54971,7 @@
         <v>45306</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55044,7 +55044,7 @@
         <v>46177</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55117,7 +55117,7 @@
         <v>46141</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>46147</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>46176</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55346,7 +55346,7 @@
         <v>46176</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55419,7 +55419,7 @@
         <v>45869</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45161</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>46178</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>44546</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45869</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>46178</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45104</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45414</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>46181</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>45412</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>46183</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>45120</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56325,7 +56325,7 @@
         <v>44637</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56398,7 +56398,7 @@
         <v>45719</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>46183</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56549,7 +56549,7 @@
         <v>46185</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>46185</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56705,7 +56705,7 @@
         <v>46185</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>46185</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>46185</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56939,7 +56939,7 @@
         <v>46185</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>46185</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>46185</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>46185</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>46185</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57329,7 +57329,7 @@
         <v>46185</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>46184</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57485,7 +57485,7 @@
         <v>46185</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57563,7 +57563,7 @@
         <v>46185</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>46185</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57719,7 +57719,7 @@
         <v>46185</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>46185</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>46185</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>46185</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58026,7 +58026,7 @@
         <v>46185</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45324</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>46185</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>46185</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58333,7 +58333,7 @@
         <v>45182</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>46188</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58489,7 +58489,7 @@
         <v>46188</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>46188</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>44585</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>46132</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>45146</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58864,7 +58864,7 @@
         <v>45106</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>45873</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>45523</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59088,7 +59088,7 @@
         <v>45660</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>46195</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59234,7 +59234,7 @@
         <v>45644</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>46198</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59390,7 +59390,7 @@
         <v>46198</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>46196</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59546,7 +59546,7 @@
         <v>46197</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59624,7 +59624,7 @@
         <v>46196</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59702,7 +59702,7 @@
         <v>46196</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59780,7 +59780,7 @@
         <v>46160</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59858,7 +59858,7 @@
         <v>46196</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59936,7 +59936,7 @@
         <v>45104</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60014,7 +60014,7 @@
         <v>45545</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60092,7 +60092,7 @@
         <v>46198</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60170,7 +60170,7 @@
         <v>45702</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60243,7 +60243,7 @@
         <v>46198</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>46198</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60399,7 +60399,7 @@
         <v>46198</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60477,7 +60477,7 @@
         <v>46198</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60555,7 +60555,7 @@
         <v>46198</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>46202</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60711,7 +60711,7 @@
         <v>45740</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60789,7 +60789,7 @@
         <v>46202</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60867,7 +60867,7 @@
         <v>45645</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>44763</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>46203</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>45420</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61174,7 +61174,7 @@
         <v>45884</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61252,7 +61252,7 @@
         <v>46206</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>45058</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61403,7 +61403,7 @@
         <v>45356</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61476,7 +61476,7 @@
         <v>44586</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>45950</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61627,7 +61627,7 @@
         <v>46106</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61705,7 +61705,7 @@
         <v>45646</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61778,7 +61778,7 @@
         <v>46169</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61851,7 +61851,7 @@
         <v>46154</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61929,7 +61929,7 @@
         <v>45735</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>46251</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62080,7 +62080,7 @@
         <v>46207</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>46252</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62231,7 +62231,7 @@
         <v>45547</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62304,7 +62304,7 @@
         <v>46210</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62382,7 +62382,7 @@
         <v>46254</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62460,7 +62460,7 @@
         <v>45673</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62533,7 +62533,7 @@
         <v>45673</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62606,7 +62606,7 @@
         <v>46210</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62684,7 +62684,7 @@
         <v>46254</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62762,7 +62762,7 @@
         <v>46213</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>44684</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62918,7 +62918,7 @@
         <v>45728</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62991,7 +62991,7 @@
         <v>45084</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63064,7 +63064,7 @@
         <v>45705</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63137,7 +63137,7 @@
         <v>46213</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63215,7 +63215,7 @@
         <v>45090</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63288,7 +63288,7 @@
         <v>46213</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63366,7 +63366,7 @@
         <v>45666</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63439,7 +63439,7 @@
         <v>46255</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>46255</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63590,7 +63590,7 @@
         <v>46255</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>44684</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63746,7 +63746,7 @@
         <v>45218</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63819,7 +63819,7 @@
         <v>44586</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63897,7 +63897,7 @@
         <v>46213</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63975,7 +63975,7 @@
         <v>46258</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>46258</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64126,7 +64126,7 @@
         <v>45666</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>46258</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64277,7 +64277,7 @@
         <v>46217</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64355,7 +64355,7 @@
         <v>45245</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64433,7 +64433,7 @@
         <v>46217</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64506,7 +64506,7 @@
         <v>46260</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64579,7 +64579,7 @@
         <v>44790</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64652,7 +64652,7 @@
         <v>46262</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64730,7 +64730,7 @@
         <v>46261</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64808,7 +64808,7 @@
         <v>46220</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64886,7 +64886,7 @@
         <v>46261</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64964,7 +64964,7 @@
         <v>44735</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65037,7 +65037,7 @@
         <v>46262</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65115,7 +65115,7 @@
         <v>46261</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65193,7 +65193,7 @@
         <v>44701</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65271,7 +65271,7 @@
         <v>46261</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65349,7 +65349,7 @@
         <v>46262</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65427,7 +65427,7 @@
         <v>46262</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65500,7 +65500,7 @@
         <v>44741</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65573,7 +65573,7 @@
         <v>44800</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65646,7 +65646,7 @@
         <v>46223</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65724,7 +65724,7 @@
         <v>46265</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65797,7 +65797,7 @@
         <v>44904</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65875,7 +65875,7 @@
         <v>46265</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65953,7 +65953,7 @@
         <v>46267</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>45265</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66104,7 +66104,7 @@
         <v>46267</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>46267</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66260,7 +66260,7 @@
         <v>46267</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66338,7 +66338,7 @@
         <v>44767</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66411,7 +66411,7 @@
         <v>46267</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66489,7 +66489,7 @@
         <v>45715</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66562,7 +66562,7 @@
         <v>46269</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66640,7 +66640,7 @@
         <v>45261</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66713,7 +66713,7 @@
         <v>46269</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66791,7 +66791,7 @@
         <v>46269</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66869,7 +66869,7 @@
         <v>46269</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66947,7 +66947,7 @@
         <v>46272</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67025,7 +67025,7 @@
         <v>45312</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67098,7 +67098,7 @@
         <v>46272</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67171,7 +67171,7 @@
         <v>46272</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -67244,7 +67244,7 @@
         <v>46274</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -67322,7 +67322,7 @@
         <v>46273</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -67400,7 +67400,7 @@
         <v>46274</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67478,7 +67478,7 @@
         <v>46274</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67556,7 +67556,7 @@
         <v>46104</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67629,7 +67629,7 @@
         <v>46273</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67707,7 +67707,7 @@
         <v>46273</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67785,7 +67785,7 @@
         <v>46273</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67863,7 +67863,7 @@
         <v>46273</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67941,7 +67941,7 @@
         <v>46273</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68019,7 +68019,7 @@
         <v>45751</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68097,7 +68097,7 @@
         <v>46276</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -68175,7 +68175,7 @@
         <v>45282</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -68248,7 +68248,7 @@
         <v>45282</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -68321,7 +68321,7 @@
         <v>46276</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -68399,7 +68399,7 @@
         <v>46275</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68477,7 +68477,7 @@
         <v>46275</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68555,7 +68555,7 @@
         <v>46276</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68633,7 +68633,7 @@
         <v>46276</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68711,7 +68711,7 @@
         <v>46280</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68789,7 +68789,7 @@
         <v>46280</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68867,7 +68867,7 @@
         <v>46280</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68945,7 +68945,7 @@
         <v>46280</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69023,7 +69023,7 @@
         <v>46280</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69101,7 +69101,7 @@
         <v>45392</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -69174,7 +69174,7 @@
         <v>45401</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -69247,7 +69247,7 @@
         <v>45526</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -69325,7 +69325,7 @@
         <v>46279</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -69398,7 +69398,7 @@
         <v>46279</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -69476,7 +69476,7 @@
         <v>46280</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69554,7 +69554,7 @@
         <v>46280</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69632,7 +69632,7 @@
         <v>46280</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69710,7 +69710,7 @@
         <v>46280</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69788,7 +69788,7 @@
         <v>45645</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69861,7 +69861,7 @@
         <v>45574</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69939,7 +69939,7 @@
         <v>46281</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70017,7 +70017,7 @@
         <v>44853</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70090,7 +70090,7 @@
         <v>46239</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70168,7 +70168,7 @@
         <v>46282</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -70246,7 +70246,7 @@
         <v>46282</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -70324,7 +70324,7 @@
         <v>46282</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -70402,7 +70402,7 @@
         <v>46281</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -70475,7 +70475,7 @@
         <v>46282</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70553,7 +70553,7 @@
         <v>46282</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70631,7 +70631,7 @@
         <v>46239</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70709,7 +70709,7 @@
         <v>45520</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70782,7 +70782,7 @@
         <v>45520</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70855,7 +70855,7 @@
         <v>46282</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70933,7 +70933,7 @@
         <v>46281</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71011,7 +71011,7 @@
         <v>45726</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71084,7 +71084,7 @@
         <v>46282</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71162,7 +71162,7 @@
         <v>45646</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -71235,7 +71235,7 @@
         <v>46283</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -71313,7 +71313,7 @@
         <v>45611</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -71386,7 +71386,7 @@
         <v>46283</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -71464,7 +71464,7 @@
         <v>46283</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71542,7 +71542,7 @@
         <v>46283</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71620,7 +71620,7 @@
         <v>46283</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71698,7 +71698,7 @@
         <v>46286</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71776,7 +71776,7 @@
         <v>46283</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71854,7 +71854,7 @@
         <v>46283</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71932,7 +71932,7 @@
         <v>46283</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72010,7 +72010,7 @@
         <v>46283</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72088,7 +72088,7 @@
         <v>44519</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72161,7 +72161,7 @@
         <v>44603</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72234,7 +72234,7 @@
         <v>44973</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -72307,7 +72307,7 @@
         <v>46283</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -72385,7 +72385,7 @@
         <v>46286</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -72458,7 +72458,7 @@
         <v>46283</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -72536,7 +72536,7 @@
         <v>46283</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72614,7 +72614,7 @@
         <v>46283</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72692,7 +72692,7 @@
         <v>46283</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72770,7 +72770,7 @@
         <v>46283</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72848,7 +72848,7 @@
         <v>46287</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72926,7 +72926,7 @@
         <v>46287</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73004,7 +73004,7 @@
         <v>44959</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73077,7 +73077,7 @@
         <v>44911</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73150,7 +73150,7 @@
         <v>44735</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73223,7 +73223,7 @@
         <v>44960</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -73301,7 +73301,7 @@
         <v>46288</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -73379,7 +73379,7 @@
         <v>46244</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -73457,7 +73457,7 @@
         <v>46287</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -73535,7 +73535,7 @@
         <v>46287</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73613,7 +73613,7 @@
         <v>46244</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73691,7 +73691,7 @@
         <v>46244</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73769,7 +73769,7 @@
         <v>46287</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73847,7 +73847,7 @@
         <v>44693</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73925,7 +73925,7 @@
         <v>46287</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -74003,7 +74003,7 @@
         <v>46185</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -74081,7 +74081,7 @@
         <v>46246</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -74159,7 +74159,7 @@
         <v>46246</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -74237,7 +74237,7 @@
         <v>46246</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -74310,7 +74310,7 @@
         <v>45158</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -74383,7 +74383,7 @@
         <v>45158</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -74456,7 +74456,7 @@
         <v>44656</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -74529,7 +74529,7 @@
         <v>46246</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -74602,7 +74602,7 @@
         <v>46290</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74680,7 +74680,7 @@
         <v>46290</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74758,7 +74758,7 @@
         <v>46289</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74831,7 +74831,7 @@
         <v>44468</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74909,7 +74909,7 @@
         <v>45397</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74987,7 +74987,7 @@
         <v>46246</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -75065,7 +75065,7 @@
         <v>46246</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -75143,7 +75143,7 @@
         <v>46246</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -75221,7 +75221,7 @@
         <v>46289</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -75299,7 +75299,7 @@
         <v>44694</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -75377,7 +75377,7 @@
         <v>46290</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -75455,7 +75455,7 @@
         <v>45819</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -75533,7 +75533,7 @@
         <v>46289</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -75611,7 +75611,7 @@
         <v>46290</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75689,7 +75689,7 @@
         <v>46248</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75767,7 +75767,7 @@
         <v>46290</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75845,7 +75845,7 @@
         <v>44651</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75923,7 +75923,7 @@
         <v>46248</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -76001,7 +76001,7 @@
         <v>46248</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -76074,7 +76074,7 @@
         <v>46248</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -76147,7 +76147,7 @@
         <v>44616</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -76220,7 +76220,7 @@
         <v>44962</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -76293,7 +76293,7 @@
         <v>45422</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -76371,7 +76371,7 @@
         <v>44927</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -76444,7 +76444,7 @@
         <v>45125</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -76517,7 +76517,7 @@
         <v>45282</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -76590,7 +76590,7 @@
         <v>44616</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -76663,7 +76663,7 @@
         <v>45146</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76736,7 +76736,7 @@
         <v>44466</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76814,7 +76814,7 @@
         <v>45034</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76892,7 +76892,7 @@
         <v>45120</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76965,7 +76965,7 @@
         <v>44942</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -77038,7 +77038,7 @@
         <v>45162</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -77111,7 +77111,7 @@
         <v>45608</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -77184,7 +77184,7 @@
         <v>45706</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -77257,7 +77257,7 @@
         <v>44951</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -77335,7 +77335,7 @@
         <v>45468</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -77413,7 +77413,7 @@
         <v>45559</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -77486,7 +77486,7 @@
         <v>44840</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -77564,7 +77564,7 @@
         <v>45084</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -77637,7 +77637,7 @@
         <v>44539</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77710,7 +77710,7 @@
         <v>45240</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77783,7 +77783,7 @@
         <v>44733</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77861,7 +77861,7 @@
         <v>45217</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77934,7 +77934,7 @@
         <v>45593</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -78007,7 +78007,7 @@
         <v>45632</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -78080,7 +78080,7 @@
         <v>45182</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -78158,7 +78158,7 @@
         <v>45649</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -78231,7 +78231,7 @@
         <v>45645</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -78304,7 +78304,7 @@
         <v>44818</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -78377,7 +78377,7 @@
         <v>45168</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -78455,7 +78455,7 @@
         <v>45699</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -78528,7 +78528,7 @@
         <v>45749</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -78601,7 +78601,7 @@
         <v>44756</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -78674,7 +78674,7 @@
         <v>45720</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78747,7 +78747,7 @@
         <v>44488</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78820,7 +78820,7 @@
         <v>45530</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78898,7 +78898,7 @@
         <v>45266</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -78971,7 +78971,7 @@
         <v>45312</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -79044,7 +79044,7 @@
         <v>45440</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -79117,7 +79117,7 @@
         <v>45266</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -79190,7 +79190,7 @@
         <v>45660</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -79263,7 +79263,7 @@
         <v>45595</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -79336,7 +79336,7 @@
         <v>45580</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -79414,7 +79414,7 @@
         <v>45776</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -79487,7 +79487,7 @@
         <v>45782</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -79560,7 +79560,7 @@
         <v>45252</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -79633,7 +79633,7 @@
         <v>45705</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -79711,7 +79711,7 @@
         <v>45702</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -79789,7 +79789,7 @@
         <v>45790</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -79862,7 +79862,7 @@
         <v>45790</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -79935,7 +79935,7 @@
         <v>45660</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -80013,7 +80013,7 @@
         <v>45791</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -80086,7 +80086,7 @@
         <v>45791</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -80164,7 +80164,7 @@
         <v>45791</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -80237,7 +80237,7 @@
         <v>45205</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -80330,7 +80330,7 @@
         <v>44995</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -80408,7 +80408,7 @@
         <v>45376</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -80486,7 +80486,7 @@
         <v>45470</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -80564,7 +80564,7 @@
         <v>46089</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -601,7 +601,7 @@
         <v>46014</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>45966</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44588</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45019</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>46135</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45623</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45842</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45825</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45302</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45982</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45926</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45926</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>45848</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45107</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45315</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>45638</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46089</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46041</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>46052</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45614</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45693</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45715</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>46174</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>46185</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>46136</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>46282</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>45302</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>45281</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>45398</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45420</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>46076</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>45825</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>46176</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>46254</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>46279</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44587</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44876</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>45338</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>45898</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>45903</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>46100</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>46094</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>45943</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45420</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>46093</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>46134</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>45994</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>46139</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>46101</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>46153</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>44887</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>46119</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>46162</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>46169</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>46174</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>46185</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>46185</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>46199</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>46254</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45737</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>45533</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>46280</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45281</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>45792</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44658</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45884</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45120</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45588</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44735</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45943</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45730</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45604</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45820</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45938</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>46097</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45272</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45015</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>46119</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>45967</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>46133</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>45984</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>46094</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45645</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45728</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45726</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44840</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>45720</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>46101</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>46101</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>46101</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45719</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>46141</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45827</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>46093</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>46101</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>46153</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>46157</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>44959</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44959</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>46185</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45726</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>46185</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>46185</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45440</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>46197</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>45631</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>46251</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>46252</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>46255</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>46217</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45420</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44790</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>46267</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>46160</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>46259</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>46274</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
         <v>46282</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>46283</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>46265</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>44811</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>46287</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>46185</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>46290</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>46290</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45379</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>45530</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44999</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44585</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45680</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45562</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>46113</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44749</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44519</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44775</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44886</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44629</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>44494</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>44735</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44775</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44663</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44573</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44882</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44756</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44813</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44671</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>44599</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44735</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>44658</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>44776</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44571</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>44788</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>44589</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>44498</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44796</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>44785</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>44599</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>44845</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>44840</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>44785</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44734</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44684</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44795</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>44491</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45715</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45715</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>44862</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45232</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>45467</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45261</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45138</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45400</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>44804</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>44876</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45373</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>44841</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45454</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45574</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45454</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45436</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>45257</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>44498</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44823</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45468</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>45594</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>46019</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45967</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>45931</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>45937</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>45855</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>46019</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45908</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45932</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45932</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45937</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>45908</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>46022</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>45932</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45623</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>46030</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45884</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>44533</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45632</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45797</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45798</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>44942</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45530</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45797</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45505</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>46030</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>46034</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>46003</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45586</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44936</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44845</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45511</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45658</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45644</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>45665</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45891</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>46041</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45895</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45895</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45896</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45898</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>45898</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>45898</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>45898</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45540</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>45897</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45898</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45882</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45898</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45475</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>46045</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45898</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45902</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>46045</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45540</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45485</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45749</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45905</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>46052</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>46052</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>44889</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>44517</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>46052</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45909</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45909</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>44988</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45908</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>44585</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>45909</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45909</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>45911</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>44739</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>46056</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>46056</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>46056</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>46058</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>46100</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>46058</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>45915</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>45726</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45804</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>46062</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>46062</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45742</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>46063</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>46063</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45547</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>46063</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>46063</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>45888</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>46065</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27671,7 +27671,7 @@
         <v>44693</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45223</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>46069</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45924</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>46069</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45923</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45586</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>46071</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45896</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>45924</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>46072</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>46072</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45926</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45030</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45019</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>46076</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>46077</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45926</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45926</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>46079</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45652</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>44691</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>45930</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>45930</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>45040</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>46083</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45932</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45932</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45931</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45595</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45931</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45932</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45933</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>46085</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45933</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44951</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>44951</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>46085</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30555,7 +30555,7 @@
         <v>45933</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45324</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45282</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>45282</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45933</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45938</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45937</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>46093</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>46092</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>46092</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44713</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45330</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>46092</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45916</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>46094</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>46094</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45939</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>46094</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>46094</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45940</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>46094</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>46095</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>46094</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>46094</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>46094</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>45939</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>46094</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>46094</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>46094</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45943</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45944</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>46098</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>46099</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45944</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>44708</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45699</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>46101</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45817</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>46100</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>45082</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>46104</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45462</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>46105</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>46104</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>45463</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45952</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>46106</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>46106</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>45614</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45953</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>46111</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>45933</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>46108</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45957</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>45034</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>45957</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>45960</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>46077</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>45964</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35062,7 +35062,7 @@
         <v>46120</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>46124</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>46124</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45965</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>46122</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>46124</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>46125</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>46125</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>45965</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>46093</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>46106</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>46106</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>46084</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>45967</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         <v>45967</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45967</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45968</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>45967</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45813</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>45089</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>45813</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45971</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>45672</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45974</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45974</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45974</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45974</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>45974</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45973</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>44936</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>45974</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>46106</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>46094</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>46104</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>44518</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>46132</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45973</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>45974</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45974</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45974</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45973</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45973</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38268,7 +38268,7 @@
         <v>46106</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>46128</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45084</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>46132</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45631</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45978</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>45978</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38804,7 +38804,7 @@
         <v>46132</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
         <v>45978</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38960,7 +38960,7 @@
         <v>46128</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>44922</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>46132</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45089</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>46133</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>46105</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>46133</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>46133</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45014</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>46100</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>46134</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>46134</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>46094</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45985</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>46134</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>46134</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>45113</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>46100</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40349,7 +40349,7 @@
         <v>45922</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>45912</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45915</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>45912</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>45922</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45922</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>45922</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45922</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>46134</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>46134</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45912</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>45912</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>45922</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>45922</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>46090</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>45630</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45987</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>45184</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41743,7 +41743,7 @@
         <v>45922</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45912</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45922</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>45922</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>44694</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45992</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>46107</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45992</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>45869</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>45632</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>45993</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>45862</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>45715</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>44600</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>45994</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45660</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45995</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>46031</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>46077</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>45995</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>45968</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>44756</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>44756</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>45995</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43540,7 +43540,7 @@
         <v>46106</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43618,7 +43618,7 @@
         <v>46106</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>46000</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>46108</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>45014</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45744</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43998,7 +43998,7 @@
         <v>46107</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>46140</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>46002</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>46002</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>46002</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45652</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45805</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>46105</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>46105</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>46107</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44748,7 +44748,7 @@
         <v>46107</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>46069</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45817</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>46003</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>46006</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>45530</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>46003</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>45686</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>46008</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45819</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45705</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45581,7 +45581,7 @@
         <v>45784</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>46070</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>46077</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45805,7 +45805,7 @@
         <v>45089</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45685</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45956,7 +45956,7 @@
         <v>46029</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45660</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>45660</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45945</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45176</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46321,7 +46321,7 @@
         <v>45176</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>46105</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>45681</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45350</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>44973</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>44589</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>45905</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>45243</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45744</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>44539</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>46031</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>46033</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>46065</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47295,7 +47295,7 @@
         <v>45741</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47368,7 +47368,7 @@
         <v>46141</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>45026</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>46141</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>46030</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47670,7 +47670,7 @@
         <v>46111</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47748,7 +47748,7 @@
         <v>46111</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>46141</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45827</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>45827</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48050,7 +48050,7 @@
         <v>45245</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>46142</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>45320</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45827</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>45014</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
         <v>46141</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45827</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>46142</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>46045</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45706</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45203</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>46146</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>46108</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>46147</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45070</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>46101</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>45757</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45757</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>45090</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49472,7 +49472,7 @@
         <v>45832</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49545,7 +49545,7 @@
         <v>45757</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>46101</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>46154</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45272</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>44874</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
         <v>44867</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>46153</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>46153</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>46153</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>45834</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>46155</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>46155</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>46119</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50519,7 +50519,7 @@
         <v>46105</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>46155</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>46105</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45835</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>46155</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>45334</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>46105</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>46107</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>46106</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>46107</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>45107</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>46161</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>45526</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51513,7 +51513,7 @@
         <v>45312</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>46107</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45845</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51737,7 +51737,7 @@
         <v>45784</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45845</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>46163</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45848</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>46168</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45645</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>46167</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52263,7 +52263,7 @@
         <v>45672</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52341,7 +52341,7 @@
         <v>46168</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52419,7 +52419,7 @@
         <v>45848</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52492,7 +52492,7 @@
         <v>45540</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>45660</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52638,7 +52638,7 @@
         <v>45660</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52711,7 +52711,7 @@
         <v>45117</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>44935</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45854</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>46168</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53013,7 +53013,7 @@
         <v>45113</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>46169</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>46169</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>46169</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53320,7 +53320,7 @@
         <v>46169</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53398,7 +53398,7 @@
         <v>46169</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53476,7 +53476,7 @@
         <v>46169</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53554,7 +53554,7 @@
         <v>46169</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53632,7 +53632,7 @@
         <v>45859</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45862</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53788,7 +53788,7 @@
         <v>45162</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45862</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45600</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54007,7 +54007,7 @@
         <v>45862</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54080,7 +54080,7 @@
         <v>46173</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54153,7 +54153,7 @@
         <v>46170</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45519</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45539</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54372,7 +54372,7 @@
         <v>44910</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54445,7 +54445,7 @@
         <v>44910</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54518,7 +54518,7 @@
         <v>45866</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>44885</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54669,7 +54669,7 @@
         <v>45867</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54742,7 +54742,7 @@
         <v>46147</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54820,7 +54820,7 @@
         <v>46177</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>46177</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54971,7 +54971,7 @@
         <v>45306</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55044,7 +55044,7 @@
         <v>46177</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55117,7 +55117,7 @@
         <v>46141</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>46147</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55273,7 +55273,7 @@
         <v>46176</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55346,7 +55346,7 @@
         <v>46176</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55419,7 +55419,7 @@
         <v>45869</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55492,7 +55492,7 @@
         <v>45161</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>46178</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>44546</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45869</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>46178</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>45104</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>45414</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>46181</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>45412</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>46183</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>45120</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56325,7 +56325,7 @@
         <v>44637</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56398,7 +56398,7 @@
         <v>45719</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56471,7 +56471,7 @@
         <v>46183</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56549,7 +56549,7 @@
         <v>46185</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>46185</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56705,7 +56705,7 @@
         <v>46185</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>46185</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>46185</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56939,7 +56939,7 @@
         <v>46185</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>46185</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>46185</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>46185</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>46185</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57329,7 +57329,7 @@
         <v>46185</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>46184</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57485,7 +57485,7 @@
         <v>46185</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57563,7 +57563,7 @@
         <v>46185</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>46185</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57719,7 +57719,7 @@
         <v>46185</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57797,7 +57797,7 @@
         <v>46185</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>46185</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>46185</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58026,7 +58026,7 @@
         <v>46185</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45324</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>46185</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>46185</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58333,7 +58333,7 @@
         <v>45182</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>46188</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58489,7 +58489,7 @@
         <v>46188</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>46188</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>44585</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>46132</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>45146</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58864,7 +58864,7 @@
         <v>45106</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>45873</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>45523</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59088,7 +59088,7 @@
         <v>45660</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>46195</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59234,7 +59234,7 @@
         <v>45644</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>46198</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59390,7 +59390,7 @@
         <v>46198</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>46196</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59546,7 +59546,7 @@
         <v>46197</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59624,7 +59624,7 @@
         <v>46196</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59702,7 +59702,7 @@
         <v>46196</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59780,7 +59780,7 @@
         <v>46160</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59858,7 +59858,7 @@
         <v>46196</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59936,7 +59936,7 @@
         <v>45104</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60014,7 +60014,7 @@
         <v>45545</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60092,7 +60092,7 @@
         <v>46198</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60170,7 +60170,7 @@
         <v>45702</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60243,7 +60243,7 @@
         <v>46198</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>46198</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60399,7 +60399,7 @@
         <v>46198</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60477,7 +60477,7 @@
         <v>46198</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60555,7 +60555,7 @@
         <v>46198</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>46202</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60711,7 +60711,7 @@
         <v>45740</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60789,7 +60789,7 @@
         <v>46202</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60867,7 +60867,7 @@
         <v>45645</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>44763</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>46203</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>45420</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61174,7 +61174,7 @@
         <v>45884</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61252,7 +61252,7 @@
         <v>46206</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>45058</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61403,7 +61403,7 @@
         <v>45356</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61476,7 +61476,7 @@
         <v>44586</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>45950</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61627,7 +61627,7 @@
         <v>46106</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61705,7 +61705,7 @@
         <v>45646</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61778,7 +61778,7 @@
         <v>46169</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61851,7 +61851,7 @@
         <v>46154</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61929,7 +61929,7 @@
         <v>45735</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>46251</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62080,7 +62080,7 @@
         <v>46207</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>46252</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62231,7 +62231,7 @@
         <v>45547</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62304,7 +62304,7 @@
         <v>46210</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62382,7 +62382,7 @@
         <v>46254</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62460,7 +62460,7 @@
         <v>45673</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62533,7 +62533,7 @@
         <v>45673</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62606,7 +62606,7 @@
         <v>46210</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62684,7 +62684,7 @@
         <v>46254</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62762,7 +62762,7 @@
         <v>46213</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>44684</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62918,7 +62918,7 @@
         <v>45728</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62991,7 +62991,7 @@
         <v>45084</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63064,7 +63064,7 @@
         <v>45705</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63137,7 +63137,7 @@
         <v>46213</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63215,7 +63215,7 @@
         <v>45090</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63288,7 +63288,7 @@
         <v>46213</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63366,7 +63366,7 @@
         <v>45666</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63439,7 +63439,7 @@
         <v>46255</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>46255</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63590,7 +63590,7 @@
         <v>46255</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>44684</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63746,7 +63746,7 @@
         <v>45218</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63819,7 +63819,7 @@
         <v>44586</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63897,7 +63897,7 @@
         <v>46213</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63975,7 +63975,7 @@
         <v>46258</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>46258</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64126,7 +64126,7 @@
         <v>45666</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>46258</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64277,7 +64277,7 @@
         <v>46217</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64355,7 +64355,7 @@
         <v>45245</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64433,7 +64433,7 @@
         <v>46217</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64506,7 +64506,7 @@
         <v>46260</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64579,7 +64579,7 @@
         <v>44790</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64652,7 +64652,7 @@
         <v>46262</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64730,7 +64730,7 @@
         <v>46261</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64808,7 +64808,7 @@
         <v>46220</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64886,7 +64886,7 @@
         <v>46261</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64964,7 +64964,7 @@
         <v>44735</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65037,7 +65037,7 @@
         <v>46262</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65115,7 +65115,7 @@
         <v>46261</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65193,7 +65193,7 @@
         <v>44701</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65271,7 +65271,7 @@
         <v>46261</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65349,7 +65349,7 @@
         <v>46262</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65427,7 +65427,7 @@
         <v>46262</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65500,7 +65500,7 @@
         <v>44741</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65573,7 +65573,7 @@
         <v>44800</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65646,7 +65646,7 @@
         <v>46223</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65724,7 +65724,7 @@
         <v>46265</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65797,7 +65797,7 @@
         <v>44904</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65875,7 +65875,7 @@
         <v>46265</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65953,7 +65953,7 @@
         <v>46267</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>45265</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66104,7 +66104,7 @@
         <v>46267</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>46267</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66260,7 +66260,7 @@
         <v>46267</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66338,7 +66338,7 @@
         <v>44767</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66411,7 +66411,7 @@
         <v>46267</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66489,7 +66489,7 @@
         <v>45715</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66562,7 +66562,7 @@
         <v>46269</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66640,7 +66640,7 @@
         <v>45261</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66713,7 +66713,7 @@
         <v>46269</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66791,7 +66791,7 @@
         <v>46269</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66869,7 +66869,7 @@
         <v>46269</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66947,7 +66947,7 @@
         <v>46272</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67025,7 +67025,7 @@
         <v>45312</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67098,7 +67098,7 @@
         <v>46272</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67171,7 +67171,7 @@
         <v>46272</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -67244,7 +67244,7 @@
         <v>46274</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -67322,7 +67322,7 @@
         <v>46273</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -67400,7 +67400,7 @@
         <v>46274</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67478,7 +67478,7 @@
         <v>46274</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67556,7 +67556,7 @@
         <v>46104</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67629,7 +67629,7 @@
         <v>46273</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67707,7 +67707,7 @@
         <v>46273</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67785,7 +67785,7 @@
         <v>46273</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67863,7 +67863,7 @@
         <v>46273</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67941,7 +67941,7 @@
         <v>46273</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68019,7 +68019,7 @@
         <v>45751</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68097,7 +68097,7 @@
         <v>46276</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -68175,7 +68175,7 @@
         <v>45282</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -68248,7 +68248,7 @@
         <v>45282</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -68321,7 +68321,7 @@
         <v>46276</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -68399,7 +68399,7 @@
         <v>46275</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68477,7 +68477,7 @@
         <v>46275</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68555,7 +68555,7 @@
         <v>46276</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68633,7 +68633,7 @@
         <v>46276</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68711,7 +68711,7 @@
         <v>46280</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68789,7 +68789,7 @@
         <v>46280</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68867,7 +68867,7 @@
         <v>46280</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68945,7 +68945,7 @@
         <v>46280</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69023,7 +69023,7 @@
         <v>46280</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69101,7 +69101,7 @@
         <v>45392</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -69174,7 +69174,7 @@
         <v>45401</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -69247,7 +69247,7 @@
         <v>45526</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -69325,7 +69325,7 @@
         <v>46279</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -69398,7 +69398,7 @@
         <v>46279</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -69476,7 +69476,7 @@
         <v>46280</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69554,7 +69554,7 @@
         <v>46280</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69632,7 +69632,7 @@
         <v>46280</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69710,7 +69710,7 @@
         <v>46280</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69788,7 +69788,7 @@
         <v>45645</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69861,7 +69861,7 @@
         <v>45574</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69939,7 +69939,7 @@
         <v>46281</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70017,7 +70017,7 @@
         <v>44853</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70090,7 +70090,7 @@
         <v>46239</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70168,7 +70168,7 @@
         <v>46282</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -70246,7 +70246,7 @@
         <v>46282</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -70324,7 +70324,7 @@
         <v>46282</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -70402,7 +70402,7 @@
         <v>46281</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -70475,7 +70475,7 @@
         <v>46282</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70553,7 +70553,7 @@
         <v>46282</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70631,7 +70631,7 @@
         <v>46239</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70709,7 +70709,7 @@
         <v>45520</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70782,7 +70782,7 @@
         <v>45520</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70855,7 +70855,7 @@
         <v>46282</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70933,7 +70933,7 @@
         <v>46281</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71011,7 +71011,7 @@
         <v>45726</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71084,7 +71084,7 @@
         <v>46282</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71162,7 +71162,7 @@
         <v>45646</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -71235,7 +71235,7 @@
         <v>46283</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -71313,7 +71313,7 @@
         <v>45611</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -71386,7 +71386,7 @@
         <v>46283</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -71464,7 +71464,7 @@
         <v>46283</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71542,7 +71542,7 @@
         <v>46283</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71620,7 +71620,7 @@
         <v>46283</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71698,7 +71698,7 @@
         <v>46286</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71776,7 +71776,7 @@
         <v>46283</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71854,7 +71854,7 @@
         <v>46283</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71932,7 +71932,7 @@
         <v>46283</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72010,7 +72010,7 @@
         <v>46283</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72088,7 +72088,7 @@
         <v>44519</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72161,7 +72161,7 @@
         <v>44603</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72234,7 +72234,7 @@
         <v>44973</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -72307,7 +72307,7 @@
         <v>46283</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -72385,7 +72385,7 @@
         <v>46286</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -72458,7 +72458,7 @@
         <v>46283</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -72536,7 +72536,7 @@
         <v>46283</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72614,7 +72614,7 @@
         <v>46283</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72692,7 +72692,7 @@
         <v>46283</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72770,7 +72770,7 @@
         <v>46283</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72848,7 +72848,7 @@
         <v>46287</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72926,7 +72926,7 @@
         <v>46287</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73004,7 +73004,7 @@
         <v>44959</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73077,7 +73077,7 @@
         <v>44911</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73150,7 +73150,7 @@
         <v>44735</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73223,7 +73223,7 @@
         <v>44960</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -73301,7 +73301,7 @@
         <v>46288</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -73379,7 +73379,7 @@
         <v>46244</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -73457,7 +73457,7 @@
         <v>46287</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -73535,7 +73535,7 @@
         <v>46287</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73613,7 +73613,7 @@
         <v>46244</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73691,7 +73691,7 @@
         <v>46244</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73769,7 +73769,7 @@
         <v>46287</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73847,7 +73847,7 @@
         <v>44693</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73925,7 +73925,7 @@
         <v>46287</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -74003,7 +74003,7 @@
         <v>46185</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -74081,7 +74081,7 @@
         <v>46246</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -74159,7 +74159,7 @@
         <v>46246</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -74237,7 +74237,7 @@
         <v>46246</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -74310,7 +74310,7 @@
         <v>45158</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -74383,7 +74383,7 @@
         <v>45158</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -74456,7 +74456,7 @@
         <v>44656</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -74529,7 +74529,7 @@
         <v>46246</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -74602,7 +74602,7 @@
         <v>46290</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74680,7 +74680,7 @@
         <v>46290</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74758,7 +74758,7 @@
         <v>46289</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74831,7 +74831,7 @@
         <v>44468</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74909,7 +74909,7 @@
         <v>45397</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74987,7 +74987,7 @@
         <v>46246</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -75065,7 +75065,7 @@
         <v>46246</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -75143,7 +75143,7 @@
         <v>46246</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -75221,7 +75221,7 @@
         <v>46289</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -75299,7 +75299,7 @@
         <v>44694</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -75377,7 +75377,7 @@
         <v>46290</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -75455,7 +75455,7 @@
         <v>45819</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -75533,7 +75533,7 @@
         <v>46289</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -75611,7 +75611,7 @@
         <v>46290</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75689,7 +75689,7 @@
         <v>46248</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75767,7 +75767,7 @@
         <v>46290</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75845,7 +75845,7 @@
         <v>44651</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75923,7 +75923,7 @@
         <v>46248</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -76001,7 +76001,7 @@
         <v>46248</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -76074,7 +76074,7 @@
         <v>46248</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -76147,7 +76147,7 @@
         <v>44616</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -76220,7 +76220,7 @@
         <v>44962</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -76293,7 +76293,7 @@
         <v>45422</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -76371,7 +76371,7 @@
         <v>44927</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -76444,7 +76444,7 @@
         <v>45125</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -76517,7 +76517,7 @@
         <v>45282</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -76590,7 +76590,7 @@
         <v>44616</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -76663,7 +76663,7 @@
         <v>45146</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76736,7 +76736,7 @@
         <v>44466</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76814,7 +76814,7 @@
         <v>45034</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76892,7 +76892,7 @@
         <v>45120</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76965,7 +76965,7 @@
         <v>44942</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -77038,7 +77038,7 @@
         <v>45162</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -77111,7 +77111,7 @@
         <v>45608</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -77184,7 +77184,7 @@
         <v>45706</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -77257,7 +77257,7 @@
         <v>44951</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -77335,7 +77335,7 @@
         <v>45468</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -77413,7 +77413,7 @@
         <v>45559</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -77486,7 +77486,7 @@
         <v>44840</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -77564,7 +77564,7 @@
         <v>45084</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -77637,7 +77637,7 @@
         <v>44539</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77710,7 +77710,7 @@
         <v>45240</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77783,7 +77783,7 @@
         <v>44733</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77861,7 +77861,7 @@
         <v>45217</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77934,7 +77934,7 @@
         <v>45593</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -78007,7 +78007,7 @@
         <v>45632</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -78080,7 +78080,7 @@
         <v>45182</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -78158,7 +78158,7 @@
         <v>45649</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -78231,7 +78231,7 @@
         <v>45645</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -78304,7 +78304,7 @@
         <v>44818</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -78377,7 +78377,7 @@
         <v>45168</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -78455,7 +78455,7 @@
         <v>45699</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -78528,7 +78528,7 @@
         <v>45749</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -78601,7 +78601,7 @@
         <v>44756</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -78674,7 +78674,7 @@
         <v>45720</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78747,7 +78747,7 @@
         <v>44488</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78820,7 +78820,7 @@
         <v>45530</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78898,7 +78898,7 @@
         <v>45266</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -78971,7 +78971,7 @@
         <v>45312</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -79044,7 +79044,7 @@
         <v>45440</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -79117,7 +79117,7 @@
         <v>45266</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -79190,7 +79190,7 @@
         <v>45660</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -79263,7 +79263,7 @@
         <v>45595</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -79336,7 +79336,7 @@
         <v>45580</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -79414,7 +79414,7 @@
         <v>45776</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -79487,7 +79487,7 @@
         <v>45782</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -79560,7 +79560,7 @@
         <v>45252</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -79633,7 +79633,7 @@
         <v>45705</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -79711,7 +79711,7 @@
         <v>45702</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -79789,7 +79789,7 @@
         <v>45790</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -79862,7 +79862,7 @@
         <v>45790</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -79935,7 +79935,7 @@
         <v>45660</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -80013,7 +80013,7 @@
         <v>45791</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -80086,7 +80086,7 @@
         <v>45791</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -80164,7 +80164,7 @@
         <v>45791</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -80237,7 +80237,7 @@
         <v>45205</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -80330,7 +80330,7 @@
         <v>44995</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -80408,7 +80408,7 @@
         <v>45376</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -80486,7 +80486,7 @@
         <v>45470</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -80564,7 +80564,7 @@
         <v>46089</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -601,7 +601,7 @@
         <v>46014</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45741</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>45966</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44588</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45019</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>46135</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45623</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45842</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45825</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45302</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45982</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45926</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45926</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>45848</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45107</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45315</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>45638</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46089</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45324</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>46041</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45614</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>46052</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>45693</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>46174</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>46185</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>46136</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>46282</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>45715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>45302</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>45281</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>45898</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>46076</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45825</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>46107</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>46176</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>45398</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>45420</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>46279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>46293</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>46254</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44876</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45107</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45737</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45898</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45792</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>46100</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>45943</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>46094</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>45512</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45994</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>46093</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>46134</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>44887</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>45420</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>45281</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>46139</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>46101</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>46119</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>46153</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>46169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>45338</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>46174</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>46185</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>46185</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>46199</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>46280</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>46254</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>45533</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44658</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>44959</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>44959</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45530</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45015</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>44790</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>45120</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45645</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44735</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>45884</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>45588</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45820</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45938</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45272</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45730</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>45943</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45967</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44840</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>46097</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>45984</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>45827</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>46133</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>46094</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>46101</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>46101</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>46101</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>45719</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>46141</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>46101</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>45726</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>46093</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>46153</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45604</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46157</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45379</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>45720</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>46185</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>46185</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>46185</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>44999</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45440</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45631</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>46197</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>46217</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>46267</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>46160</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>46274</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>46283</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>46265</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>46282</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>46185</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>46287</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>46290</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>46259</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>46290</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>46252</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>46294</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>45420</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>46251</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>46255</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15891,7 +15891,7 @@
         <v>46119</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>44811</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45728</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45386</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44585</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45680</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45562</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>46113</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>44519</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>44775</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>44886</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44749</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44629</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>44805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>44494</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44735</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>44775</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>44573</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44663</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44882</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44756</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>44813</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>44671</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>44671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>44599</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>44658</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44735</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44776</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44571</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>44788</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>44589</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44498</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44796</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>44785</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>44599</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>44845</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44840</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>44785</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44734</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>44684</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>44795</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>44491</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45706</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>44889</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44585</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>45454</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>44959</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>45699</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45611</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>44637</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>45014</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>45040</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>45660</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44656</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45666</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45726</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45646</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45089</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>45706</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45547</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45158</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45158</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>45265</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44708</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>45705</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>46003</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21044,7 +21044,7 @@
         <v>46002</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>46002</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>46002</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>45715</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44840</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>45104</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>44862</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>46006</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>45791</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>46008</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44942</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>45791</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45790</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45791</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45884</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44691</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45855</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>46019</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45967</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45932</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45932</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>46019</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>45908</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>45937</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>45891</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45937</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45908</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>45931</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45932</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>46022</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45895</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45895</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45665</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45324</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45896</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>45184</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>46030</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45882</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45790</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45897</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>46030</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45898</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>45898</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45749</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45117</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>45898</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45898</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>44756</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>44756</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45084</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45898</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45898</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45898</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>46034</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45485</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45902</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45905</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45125</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45660</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>46041</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>44539</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>45909</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>45909</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45909</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45909</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45911</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45908</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>46045</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>45797</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>45623</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>45594</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45797</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>46045</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>45915</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45632</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>45505</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>45798</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44867</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>44693</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45888</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>44739</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>45804</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>45632</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>46052</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>45162</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>45719</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>45923</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45896</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>46052</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>46052</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>45924</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>46056</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>46056</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>46056</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45924</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>45926</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>45540</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45926</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>46058</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>44733</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>46058</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45926</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>46100</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45931</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>45931</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>45645</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>46063</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>46063</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45652</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>46062</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>46062</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>45930</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29430,7 +29430,7 @@
         <v>45930</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29503,7 +29503,7 @@
         <v>45475</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>44823</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45932</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45933</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44988</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45933</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45933</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>46065</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>45932</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>45932</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45030</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>46069</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>45933</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>46069</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>45937</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>45726</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>44589</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45938</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>45939</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45916</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45939</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>46071</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>46072</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45940</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45146</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>46072</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45943</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>45468</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>45530</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>45944</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45817</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>46076</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>46077</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45324</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45672</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>46079</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>45261</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45933</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45952</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>45953</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>46083</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>45813</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45957</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>46085</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45813</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>46085</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45957</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>45034</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>45960</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>46092</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45463</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>45964</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>46092</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>45965</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>46092</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>44951</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>46094</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45817</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>46094</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33990,7 +33990,7 @@
         <v>45420</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>46094</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>45967</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>46094</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>46094</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>46094</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>46094</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34536,7 +34536,7 @@
         <v>46094</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>46094</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>46094</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45965</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>46093</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>46094</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45971</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44935</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>46095</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>46098</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>45968</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>45973</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>46099</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>46100</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>45973</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>45973</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45973</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>46104</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45720</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45974</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45974</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>46101</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>46104</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45974</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36451,7 +36451,7 @@
         <v>45974</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36529,7 +36529,7 @@
         <v>45974</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44960</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>45974</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>45974</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>46106</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>45974</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45084</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>45978</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45978</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>45819</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>46106</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>46105</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>45978</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45356</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>44517</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>46108</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>44533</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>46111</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45912</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45912</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>45681</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>45922</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45922</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>45922</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45922</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45922</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45912</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38620,7 +38620,7 @@
         <v>45985</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>45912</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45922</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>45922</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45922</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>45922</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45922</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>45987</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>45526</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>45912</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39395,7 +39395,7 @@
         <v>45593</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>46120</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45468</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>46122</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>46077</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>45245</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45992</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>45827</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39994,7 +39994,7 @@
         <v>45993</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>45992</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>45827</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>46125</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>44684</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40364,7 +40364,7 @@
         <v>45994</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>46084</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40515,7 +40515,7 @@
         <v>45995</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>46125</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45741</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45995</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>46124</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         <v>46124</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>45968</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>46124</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>46093</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45995</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>46128</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>45827</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>45827</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>46106</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>46104</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>46031</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>46128</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>46000</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>46094</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>46106</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>46106</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42093,7 +42093,7 @@
         <v>46106</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45161</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>46132</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>46132</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>46132</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42483,7 +42483,7 @@
         <v>45113</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>46133</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>46133</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>46132</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45832</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>44735</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>46134</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>46134</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45223</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>46090</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>46134</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>46134</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>46105</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43477,7 +43477,7 @@
         <v>45715</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>46134</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>46100</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>46133</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44693</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>45401</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>45834</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44008,7 +44008,7 @@
         <v>46134</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>45454</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45595</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45742</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>45915</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>46105</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45835</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>46029</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>44585</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>46107</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45686</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>45945</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>46107</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>44735</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>44701</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45805</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45511</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>46094</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45367,7 +45367,7 @@
         <v>45630</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45784</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45862</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45586,7 +45586,7 @@
         <v>46031</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45659,7 +45659,7 @@
         <v>45744</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45845</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>45845</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45905</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>45848</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>46106</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45848</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46185,7 +46185,7 @@
         <v>46077</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>46107</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46341,7 +46341,7 @@
         <v>46105</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45540</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46492,7 +46492,7 @@
         <v>44684</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45744</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>44694</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>46070</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46799,7 +46799,7 @@
         <v>46065</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46872,7 +46872,7 @@
         <v>45138</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>46107</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>46105</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45168</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>44951</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>44951</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>45854</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>46069</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>44904</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47559,7 +47559,7 @@
         <v>44962</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45660</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>45869</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>46100</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45859</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>44942</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48007,7 +48007,7 @@
         <v>45586</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>45440</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48153,7 +48153,7 @@
         <v>45203</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48226,7 +48226,7 @@
         <v>45632</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45862</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>44600</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45526</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>46106</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48606,7 +48606,7 @@
         <v>45862</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48684,7 +48684,7 @@
         <v>45666</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>45862</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48830,7 +48830,7 @@
         <v>45436</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48903,7 +48903,7 @@
         <v>46140</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>46030</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49049,7 +49049,7 @@
         <v>45866</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>45867</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49200,7 +49200,7 @@
         <v>45120</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>46077</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>46111</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49424,7 +49424,7 @@
         <v>46111</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>46108</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49580,7 +49580,7 @@
         <v>45869</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>46141</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49731,7 +49731,7 @@
         <v>45869</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>45645</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>46033</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>46141</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45705</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>45282</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>45784</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>45672</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>46141</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>46141</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50481,7 +50481,7 @@
         <v>45645</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>45422</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>46142</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>45873</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>46142</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50871,7 +50871,7 @@
         <v>45162</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50944,7 +50944,7 @@
         <v>46045</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>45058</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>46147</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51168,7 +51168,7 @@
         <v>44586</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>46146</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>46101</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51402,7 +51402,7 @@
         <v>46108</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51480,7 +51480,7 @@
         <v>45658</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>44518</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45084</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51699,7 +51699,7 @@
         <v>46153</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>44756</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51845,7 +51845,7 @@
         <v>45547</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>44936</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>46153</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>46155</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>46119</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>46105</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52298,7 +52298,7 @@
         <v>46155</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52376,7 +52376,7 @@
         <v>44911</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52449,7 +52449,7 @@
         <v>45600</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45649</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52595,7 +52595,7 @@
         <v>46155</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52668,7 +52668,7 @@
         <v>46105</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52746,7 +52746,7 @@
         <v>46101</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52824,7 +52824,7 @@
         <v>46154</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52902,7 +52902,7 @@
         <v>46107</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52980,7 +52980,7 @@
         <v>45320</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53053,7 +53053,7 @@
         <v>46107</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         <v>45312</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53204,7 +53204,7 @@
         <v>46106</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>46105</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53360,7 +53360,7 @@
         <v>46107</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53438,7 +53438,7 @@
         <v>46155</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53516,7 +53516,7 @@
         <v>46163</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53594,7 +53594,7 @@
         <v>45120</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53667,7 +53667,7 @@
         <v>46167</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53740,7 +53740,7 @@
         <v>45574</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53818,7 +53818,7 @@
         <v>45312</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>46169</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53969,7 +53969,7 @@
         <v>46169</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>46169</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>45257</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>46169</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>46169</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>45545</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>46168</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>46169</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>46168</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54671,7 +54671,7 @@
         <v>46169</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54749,7 +54749,7 @@
         <v>46168</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>44651</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>46170</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54978,7 +54978,7 @@
         <v>45182</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55056,7 +55056,7 @@
         <v>46173</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55129,7 +55129,7 @@
         <v>45757</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55202,7 +55202,7 @@
         <v>45740</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55280,7 +55280,7 @@
         <v>46147</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55358,7 +55358,7 @@
         <v>46176</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55431,7 +55431,7 @@
         <v>45539</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55504,7 +55504,7 @@
         <v>45660</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45884</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>46176</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>46178</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>46147</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55884,7 +55884,7 @@
         <v>46141</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>46177</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56035,7 +56035,7 @@
         <v>46178</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56108,7 +56108,7 @@
         <v>46177</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56181,7 +56181,7 @@
         <v>46181</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>45673</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>45673</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>46183</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>45646</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56556,7 +56556,7 @@
         <v>44853</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56629,7 +56629,7 @@
         <v>46183</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>46184</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56785,7 +56785,7 @@
         <v>46185</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>46185</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56936,7 +56936,7 @@
         <v>46185</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>46185</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57092,7 +57092,7 @@
         <v>46185</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>46185</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57248,7 +57248,7 @@
         <v>46185</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57326,7 +57326,7 @@
         <v>46185</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57404,7 +57404,7 @@
         <v>46188</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57482,7 +57482,7 @@
         <v>46185</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57560,7 +57560,7 @@
         <v>46185</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>46185</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>46185</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>46185</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57872,7 +57872,7 @@
         <v>44841</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57945,7 +57945,7 @@
         <v>46188</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>46188</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>46185</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58179,7 +58179,7 @@
         <v>46185</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58257,7 +58257,7 @@
         <v>46185</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>46185</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58413,7 +58413,7 @@
         <v>46185</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58491,7 +58491,7 @@
         <v>46185</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58569,7 +58569,7 @@
         <v>46185</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58647,7 +58647,7 @@
         <v>45330</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58720,7 +58720,7 @@
         <v>46132</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58793,7 +58793,7 @@
         <v>45217</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58866,7 +58866,7 @@
         <v>46196</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58944,7 +58944,7 @@
         <v>46196</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59022,7 +59022,7 @@
         <v>46196</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59100,7 +59100,7 @@
         <v>44616</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>46196</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59251,7 +59251,7 @@
         <v>44876</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59324,7 +59324,7 @@
         <v>46195</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59397,7 +59397,7 @@
         <v>44546</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59475,7 +59475,7 @@
         <v>46160</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59553,7 +59553,7 @@
         <v>46198</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59631,7 +59631,7 @@
         <v>46198</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59709,7 +59709,7 @@
         <v>46198</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>46197</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59865,7 +59865,7 @@
         <v>46198</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59943,7 +59943,7 @@
         <v>46198</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60021,7 +60021,7 @@
         <v>46198</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60099,7 +60099,7 @@
         <v>46198</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>46198</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60255,7 +60255,7 @@
         <v>44488</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>46202</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60406,7 +60406,7 @@
         <v>44519</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60479,7 +60479,7 @@
         <v>46202</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60557,7 +60557,7 @@
         <v>45090</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60630,7 +60630,7 @@
         <v>46203</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60708,7 +60708,7 @@
         <v>44936</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60781,7 +60781,7 @@
         <v>46106</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60859,7 +60859,7 @@
         <v>45950</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60932,7 +60932,7 @@
         <v>45312</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61005,7 +61005,7 @@
         <v>46206</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61083,7 +61083,7 @@
         <v>46207</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61161,7 +61161,7 @@
         <v>45218</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61234,7 +61234,7 @@
         <v>46154</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61312,7 +61312,7 @@
         <v>45412</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61385,7 +61385,7 @@
         <v>45595</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61458,7 +61458,7 @@
         <v>46210</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61536,7 +61536,7 @@
         <v>46210</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61614,7 +61614,7 @@
         <v>45282</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>45282</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>45282</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>46213</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61911,7 +61911,7 @@
         <v>46258</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61989,7 +61989,7 @@
         <v>46217</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>45182</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>44804</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62218,7 +62218,7 @@
         <v>44845</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>46258</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>46213</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62442,7 +62442,7 @@
         <v>46213</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62520,7 +62520,7 @@
         <v>46217</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62593,7 +62593,7 @@
         <v>46261</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62671,7 +62671,7 @@
         <v>45644</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62749,7 +62749,7 @@
         <v>46260</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62822,7 +62822,7 @@
         <v>45644</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62900,7 +62900,7 @@
         <v>46261</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62978,7 +62978,7 @@
         <v>46261</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63056,7 +63056,7 @@
         <v>46261</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63134,7 +63134,7 @@
         <v>44713</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63212,7 +63212,7 @@
         <v>45245</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63290,7 +63290,7 @@
         <v>46265</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63363,7 +63363,7 @@
         <v>45400</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>46262</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63514,7 +63514,7 @@
         <v>46220</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>46262</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>46265</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63743,7 +63743,7 @@
         <v>46223</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63821,7 +63821,7 @@
         <v>46262</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63899,7 +63899,7 @@
         <v>46262</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63977,7 +63977,7 @@
         <v>45104</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64055,7 +64055,7 @@
         <v>46267</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64133,7 +64133,7 @@
         <v>46267</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64211,7 +64211,7 @@
         <v>46267</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64289,7 +64289,7 @@
         <v>44910</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64362,7 +64362,7 @@
         <v>45462</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64435,7 +64435,7 @@
         <v>45660</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64508,7 +64508,7 @@
         <v>45660</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64581,7 +64581,7 @@
         <v>44741</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64654,7 +64654,7 @@
         <v>46267</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>46267</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64810,7 +64810,7 @@
         <v>46269</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>46269</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64966,7 +64966,7 @@
         <v>46269</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65044,7 +65044,7 @@
         <v>46269</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65122,7 +65122,7 @@
         <v>45350</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65195,7 +65195,7 @@
         <v>44498</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65268,7 +65268,7 @@
         <v>46273</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65346,7 +65346,7 @@
         <v>46273</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65424,7 +65424,7 @@
         <v>46273</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65502,7 +65502,7 @@
         <v>46273</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65580,7 +65580,7 @@
         <v>46273</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65658,7 +65658,7 @@
         <v>45614</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65731,7 +65731,7 @@
         <v>46272</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65804,7 +65804,7 @@
         <v>46272</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>45261</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65950,7 +65950,7 @@
         <v>46273</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66028,7 +66028,7 @@
         <v>46272</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66106,7 +66106,7 @@
         <v>46274</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66184,7 +66184,7 @@
         <v>45019</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66257,7 +66257,7 @@
         <v>46275</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66335,7 +66335,7 @@
         <v>46275</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66413,7 +66413,7 @@
         <v>46274</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66491,7 +66491,7 @@
         <v>46274</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66569,7 +66569,7 @@
         <v>46276</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66647,7 +66647,7 @@
         <v>46276</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66725,7 +66725,7 @@
         <v>46276</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66803,7 +66803,7 @@
         <v>46279</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66876,7 +66876,7 @@
         <v>46276</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66954,7 +66954,7 @@
         <v>46279</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67032,7 +67032,7 @@
         <v>46280</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67110,7 +67110,7 @@
         <v>46280</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67188,7 +67188,7 @@
         <v>44874</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -67266,7 +67266,7 @@
         <v>45113</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -67339,7 +67339,7 @@
         <v>46280</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -67417,7 +67417,7 @@
         <v>46280</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67495,7 +67495,7 @@
         <v>46280</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67573,7 +67573,7 @@
         <v>46281</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67646,7 +67646,7 @@
         <v>46281</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67724,7 +67724,7 @@
         <v>46280</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67802,7 +67802,7 @@
         <v>45070</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67875,7 +67875,7 @@
         <v>46280</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67953,7 +67953,7 @@
         <v>46281</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68031,7 +68031,7 @@
         <v>45026</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68104,7 +68104,7 @@
         <v>46280</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -68182,7 +68182,7 @@
         <v>45467</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -68260,7 +68260,7 @@
         <v>46282</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -68338,7 +68338,7 @@
         <v>45702</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -68411,7 +68411,7 @@
         <v>46239</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68489,7 +68489,7 @@
         <v>44539</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68562,7 +68562,7 @@
         <v>45652</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68635,7 +68635,7 @@
         <v>46283</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68713,7 +68713,7 @@
         <v>46282</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68791,7 +68791,7 @@
         <v>46239</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68869,7 +68869,7 @@
         <v>44694</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68947,7 +68947,7 @@
         <v>46283</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69025,7 +69025,7 @@
         <v>44818</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69098,7 +69098,7 @@
         <v>46283</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -69176,7 +69176,7 @@
         <v>46283</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -69254,7 +69254,7 @@
         <v>46283</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -69332,7 +69332,7 @@
         <v>46283</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -69410,7 +69410,7 @@
         <v>44763</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -69483,7 +69483,7 @@
         <v>46283</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69561,7 +69561,7 @@
         <v>46282</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69639,7 +69639,7 @@
         <v>46282</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69717,7 +69717,7 @@
         <v>46282</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69795,7 +69795,7 @@
         <v>46282</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69873,7 +69873,7 @@
         <v>46283</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69951,7 +69951,7 @@
         <v>46282</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70029,7 +70029,7 @@
         <v>46283</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70107,7 +70107,7 @@
         <v>46283</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70185,7 +70185,7 @@
         <v>46283</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -70263,7 +70263,7 @@
         <v>46283</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -70341,7 +70341,7 @@
         <v>46283</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -70419,7 +70419,7 @@
         <v>46283</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -70497,7 +70497,7 @@
         <v>46283</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70575,7 +70575,7 @@
         <v>45540</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70648,7 +70648,7 @@
         <v>45757</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70721,7 +70721,7 @@
         <v>45757</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70794,7 +70794,7 @@
         <v>46286</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70872,7 +70872,7 @@
         <v>46244</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70950,7 +70950,7 @@
         <v>46287</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71028,7 +71028,7 @@
         <v>46287</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71106,7 +71106,7 @@
         <v>46287</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71184,7 +71184,7 @@
         <v>46287</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -71262,7 +71262,7 @@
         <v>46286</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -71335,7 +71335,7 @@
         <v>46287</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -71413,7 +71413,7 @@
         <v>46244</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -71491,7 +71491,7 @@
         <v>45243</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71564,7 +71564,7 @@
         <v>44616</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71637,7 +71637,7 @@
         <v>46244</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71715,7 +71715,7 @@
         <v>46287</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71793,7 +71793,7 @@
         <v>45735</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71866,7 +71866,7 @@
         <v>45106</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71939,7 +71939,7 @@
         <v>45014</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72012,7 +72012,7 @@
         <v>46246</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72085,7 +72085,7 @@
         <v>46246</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72163,7 +72163,7 @@
         <v>46246</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72241,7 +72241,7 @@
         <v>46289</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -72319,7 +72319,7 @@
         <v>44790</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -72392,7 +72392,7 @@
         <v>46246</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -72470,7 +72470,7 @@
         <v>46246</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -72548,7 +72548,7 @@
         <v>45699</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72621,7 +72621,7 @@
         <v>46289</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72699,7 +72699,7 @@
         <v>46289</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72772,7 +72772,7 @@
         <v>46246</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72845,7 +72845,7 @@
         <v>45373</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72918,7 +72918,7 @@
         <v>44885</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -72991,7 +72991,7 @@
         <v>46246</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73069,7 +73069,7 @@
         <v>45282</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73142,7 +73142,7 @@
         <v>46288</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73220,7 +73220,7 @@
         <v>46248</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -73293,7 +73293,7 @@
         <v>46248</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -73366,7 +73366,7 @@
         <v>45819</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -73444,7 +73444,7 @@
         <v>46248</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -73522,7 +73522,7 @@
         <v>45107</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73595,7 +73595,7 @@
         <v>46293</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73673,7 +73673,7 @@
         <v>46185</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73751,7 +73751,7 @@
         <v>46293</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73829,7 +73829,7 @@
         <v>46248</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73907,7 +73907,7 @@
         <v>45082</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -73980,7 +73980,7 @@
         <v>46290</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -74058,7 +74058,7 @@
         <v>46290</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -74136,7 +74136,7 @@
         <v>46290</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -74214,7 +74214,7 @@
         <v>45034</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -74292,7 +74292,7 @@
         <v>46290</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -74370,7 +74370,7 @@
         <v>44973</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -74443,7 +74443,7 @@
         <v>46293</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -74521,7 +74521,7 @@
         <v>46290</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -74599,7 +74599,7 @@
         <v>45397</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74677,7 +74677,7 @@
         <v>46293</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74755,7 +74755,7 @@
         <v>44800</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74828,7 +74828,7 @@
         <v>46169</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74901,7 +74901,7 @@
         <v>46258</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74979,7 +74979,7 @@
         <v>46295</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -75057,7 +75057,7 @@
         <v>46295</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -75135,7 +75135,7 @@
         <v>46251</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -75213,7 +75213,7 @@
         <v>46295</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -75291,7 +75291,7 @@
         <v>46252</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -75364,7 +75364,7 @@
         <v>46280</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -75442,7 +75442,7 @@
         <v>45266</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -75515,7 +75515,7 @@
         <v>46104</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -75588,7 +75588,7 @@
         <v>46161</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75666,7 +75666,7 @@
         <v>45414</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75739,7 +75739,7 @@
         <v>46294</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75817,7 +75817,7 @@
         <v>46297</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75895,7 +75895,7 @@
         <v>46297</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -75973,7 +75973,7 @@
         <v>46297</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -76051,7 +76051,7 @@
         <v>46254</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -76129,7 +76129,7 @@
         <v>46185</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -76207,7 +76207,7 @@
         <v>44922</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -76280,7 +76280,7 @@
         <v>45631</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -76358,7 +76358,7 @@
         <v>46255</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -76436,7 +76436,7 @@
         <v>46255</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -76509,7 +76509,7 @@
         <v>45715</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -76582,7 +76582,7 @@
         <v>46296</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -76660,7 +76660,7 @@
         <v>45266</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76733,7 +76733,7 @@
         <v>45660</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76806,7 +76806,7 @@
         <v>45586</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76884,7 +76884,7 @@
         <v>45519</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76957,7 +76957,7 @@
         <v>45146</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -77030,7 +77030,7 @@
         <v>46063</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -77108,7 +77108,7 @@
         <v>44586</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -77186,7 +77186,7 @@
         <v>45705</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -77259,7 +77259,7 @@
         <v>45967</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -77337,7 +77337,7 @@
         <v>45530</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -77410,7 +77410,7 @@
         <v>44927</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -77483,7 +77483,7 @@
         <v>46255</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -77561,7 +77561,7 @@
         <v>46296</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -77639,7 +77639,7 @@
         <v>46254</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77717,7 +77717,7 @@
         <v>45574</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77795,7 +77795,7 @@
         <v>46297</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77873,7 +77873,7 @@
         <v>46297</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77951,7 +77951,7 @@
         <v>46297</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -78029,7 +78029,7 @@
         <v>46297</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -78107,7 +78107,7 @@
         <v>45944</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -78185,7 +78185,7 @@
         <v>45967</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -78263,7 +78263,7 @@
         <v>45608</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -78336,7 +78336,7 @@
         <v>44767</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -78409,7 +78409,7 @@
         <v>44910</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -78482,7 +78482,7 @@
         <v>45559</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -78555,7 +78555,7 @@
         <v>45530</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -78633,7 +78633,7 @@
         <v>45751</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -78711,7 +78711,7 @@
         <v>45334</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78784,7 +78784,7 @@
         <v>45392</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78857,7 +78857,7 @@
         <v>45089</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78930,7 +78930,7 @@
         <v>44603</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -79003,7 +79003,7 @@
         <v>45176</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -79076,7 +79076,7 @@
         <v>45176</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -79149,7 +79149,7 @@
         <v>44959</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -79222,7 +79222,7 @@
         <v>45685</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -79295,7 +79295,7 @@
         <v>45660</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -79368,7 +79368,7 @@
         <v>45240</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -79441,7 +79441,7 @@
         <v>45520</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -79514,7 +79514,7 @@
         <v>45520</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -79587,7 +79587,7 @@
         <v>45089</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -79665,7 +79665,7 @@
         <v>44973</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -79738,7 +79738,7 @@
         <v>45232</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -79816,7 +79816,7 @@
         <v>45749</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -79889,7 +79889,7 @@
         <v>45090</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -79962,7 +79962,7 @@
         <v>45014</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -80035,7 +80035,7 @@
         <v>45728</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -80108,7 +80108,7 @@
         <v>45306</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -80181,7 +80181,7 @@
         <v>45272</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -80254,7 +80254,7 @@
         <v>45523</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -80327,7 +80327,7 @@
         <v>45776</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -80400,7 +80400,7 @@
         <v>45580</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -80478,7 +80478,7 @@
         <v>45782</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -80551,7 +80551,7 @@
         <v>45702</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -80629,7 +80629,7 @@
         <v>45252</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -80702,7 +80702,7 @@
         <v>45205</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -80795,7 +80795,7 @@
         <v>44995</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -80873,7 +80873,7 @@
         <v>45376</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -80951,7 +80951,7 @@
         <v>45470</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -81029,7 +81029,7 @@
         <v>46089</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -601,7 +601,7 @@
         <v>45741</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46014</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>45966</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44588</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45019</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>46135</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>46079</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45623</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>45593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>46052</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45825</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45302</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45982</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45107</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45741</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>45926</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>45926</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>45848</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45315</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>45638</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46089</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45324</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>45614</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45302</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45281</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>46041</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>46052</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>46282</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>46174</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>45715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>46136</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>46304</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>45398</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45420</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>45825</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>46076</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>46176</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>46279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>46293</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>46254</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44876</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45338</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>44887</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>45512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45898</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>45281</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45903</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>45792</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>45943</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>45420</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45737</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>45533</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>46094</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45994</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>46134</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>45107</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>46139</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>46101</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>46153</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>46119</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>46169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>46185</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>46199</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>46280</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>46185</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>46254</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>46100</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>46093</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45699</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44658</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>45379</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45884</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>45530</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>44959</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>44959</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>45120</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>44999</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45440</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45631</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45604</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>45820</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>45588</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45938</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45730</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>45272</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45015</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45827</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45967</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45645</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>44790</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45728</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>44840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>45720</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45726</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>45984</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44811</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46094</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>46101</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>46101</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>46101</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45719</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>46141</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>46101</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>46153</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>45943</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>46157</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>46097</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>46185</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>46185</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>46185</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>46197</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>46217</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>46267</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>46274</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>46282</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>46283</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46265</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>46287</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>46185</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>46290</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>46290</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>46294</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>46251</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>46252</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>46093</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>46160</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>46119</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>46255</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>46133</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>45420</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45973</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>46259</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44585</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45680</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45562</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>46113</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44749</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44775</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44519</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44886</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44629</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>44494</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>44735</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44775</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44663</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44573</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44882</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44756</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44813</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44671</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>44735</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44658</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44498</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>44776</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44796</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44571</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>44788</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>44840</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44785</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>44785</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>44599</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44589</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>44845</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>44599</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44734</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45261</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45070</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>44684</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45757</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45757</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45090</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44795</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45162</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>44491</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45138</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45608</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45757</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45706</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44951</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45272</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45400</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>44804</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44874</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44867</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45436</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45468</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45559</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44840</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45084</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44539</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45334</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45107</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45715</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45715</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44876</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45240</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>44733</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44862</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44841</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45217</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45373</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45593</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45467</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45526</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45632</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45182</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45454</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>45574</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45454</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45257</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45232</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45645</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45672</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45660</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45660</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>44498</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45117</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45884</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44935</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45649</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45113</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45645</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>44823</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45468</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>44818</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45884</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>45168</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45699</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45162</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45600</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45749</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44533</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45519</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45539</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44756</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44910</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>44910</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>44942</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45530</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>44885</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45665</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>45891</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45895</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45895</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45896</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>45898</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45898</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45898</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45898</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45898</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45882</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45898</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45898</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>45902</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45720</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45586</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45485</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>44936</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45749</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>44845</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45511</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45658</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44488</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45644</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45530</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>45306</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45266</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45312</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45905</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>45440</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45540</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45161</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45266</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45660</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>44546</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45595</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45909</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45909</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>45475</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>45580</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>45908</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45776</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45540</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45909</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45909</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45911</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45782</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45414</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45412</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45120</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45252</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44889</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44637</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>45719</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>44517</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44988</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45915</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45705</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>44585</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>45702</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>45324</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45182</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45726</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>45742</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>45547</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45888</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44585</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45146</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45106</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>44959</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>45924</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45923</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45790</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44693</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>45223</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45896</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>45924</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>45523</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>45660</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45790</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>45660</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>45926</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45791</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>45644</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45926</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>45926</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45030</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>45019</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45791</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45652</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>45791</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45930</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>45930</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>44691</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>45594</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45040</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45104</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>45623</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         <v>45702</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>45595</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45932</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>45632</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32360,7 +32360,7 @@
         <v>45932</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45931</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45931</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44951</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45797</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44951</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45798</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>45797</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45324</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45932</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45505</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45282</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45282</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45933</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44763</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>44713</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45933</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45330</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>45933</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>44739</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>45058</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45804</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45356</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>44586</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>45938</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>45937</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44708</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>45699</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34454,7 +34454,7 @@
         <v>45646</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>45082</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45735</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45462</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>45463</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45916</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45939</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45940</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>45939</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>45547</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>45943</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
         <v>45944</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45614</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>45817</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45673</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>45673</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45813</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45813</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>44684</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>45728</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>45034</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>45084</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>45705</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>45090</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45817</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45819</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>44684</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36460,7 +36460,7 @@
         <v>45218</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>44586</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>45741</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>45666</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45827</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45827</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45827</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45827</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45952</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45089</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45245</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45672</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37351,7 +37351,7 @@
         <v>45832</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45953</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45957</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>45957</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>45960</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>44936</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44790</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37867,7 +37867,7 @@
         <v>44518</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37940,7 +37940,7 @@
         <v>45084</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45964</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45834</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>45835</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45631</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>44735</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44701</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>44922</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>45965</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>45089</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>45965</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45014</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45967</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45968</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>45113</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>44741</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>44800</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>45845</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45630</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45784</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45845</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45971</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45184</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>44694</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45974</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45974</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>45848</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45974</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>45974</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>45974</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>44904</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>45848</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45974</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45540</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>45973</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>45632</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45974</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>45974</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45974</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45973</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45973</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45660</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45854</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44756</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>44756</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45265</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45859</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>45014</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>45862</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45862</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>44767</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>45862</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>45715</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>45652</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>45978</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>45978</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>45866</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45867</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>45261</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>45978</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45869</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>45530</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>45869</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>45312</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45089</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45685</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>45873</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>45660</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45660</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45176</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45176</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45681</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>45350</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>44973</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>44589</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45751</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>45545</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45282</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45282</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>45243</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45740</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>46094</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>46094</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>44539</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>46098</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>46099</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45392</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>45401</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44554,7 +44554,7 @@
         <v>45526</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>46101</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>46100</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45645</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45985</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>45574</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>46104</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45090,7 +45090,7 @@
         <v>45026</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>46105</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>44853</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>46104</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45392,7 +45392,7 @@
         <v>45245</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>46106</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>45922</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>45912</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45912</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>45922</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>45922</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>46106</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46011,7 +46011,7 @@
         <v>45320</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45520</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
         <v>45520</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45014</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>46111</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46381,7 +46381,7 @@
         <v>45922</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45922</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46537,7 +46537,7 @@
         <v>45726</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45912</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46688,7 +46688,7 @@
         <v>45912</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45922</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45922</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>45646</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>46108</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45922</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>45912</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>45922</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>45922</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45992</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47458,7 +47458,7 @@
         <v>45611</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47531,7 +47531,7 @@
         <v>45706</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         <v>45992</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45203</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45993</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>44519</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>46077</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>44603</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>44973</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>46120</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>46124</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
         <v>46124</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48339,7 +48339,7 @@
         <v>45994</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>45995</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>46122</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>46031</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>46124</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>46125</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>45995</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>46125</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>45968</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>46106</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>46106</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>45995</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>46000</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>46002</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49381,7 +49381,7 @@
         <v>46002</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>46106</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>46002</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>46094</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>46104</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>46132</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>46106</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>46128</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>44959</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>46132</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>44911</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>44735</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>44960</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50365,7 +50365,7 @@
         <v>46132</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>46128</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50521,7 +50521,7 @@
         <v>46132</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>46006</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>46133</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50755,7 +50755,7 @@
         <v>46105</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50833,7 +50833,7 @@
         <v>46133</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50911,7 +50911,7 @@
         <v>46133</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>46100</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>44693</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>46134</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51223,7 +51223,7 @@
         <v>46134</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51301,7 +51301,7 @@
         <v>46094</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         <v>46134</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>46008</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>46134</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>46100</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>45915</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>46134</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51842,7 +51842,7 @@
         <v>46134</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>46090</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45158</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>45158</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>44656</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52217,7 +52217,7 @@
         <v>45397</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>46107</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>44694</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52451,7 +52451,7 @@
         <v>45869</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52524,7 +52524,7 @@
         <v>45862</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52597,7 +52597,7 @@
         <v>44600</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>46019</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52748,7 +52748,7 @@
         <v>45967</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45931</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52894,7 +52894,7 @@
         <v>45937</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52967,7 +52967,7 @@
         <v>45855</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>44651</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>46019</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53191,7 +53191,7 @@
         <v>45908</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>45932</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45932</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>45937</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>45908</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>44616</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>46077</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>46022</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>46106</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>46106</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53931,7 +53931,7 @@
         <v>45932</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         <v>46108</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54082,7 +54082,7 @@
         <v>44962</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54155,7 +54155,7 @@
         <v>45744</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54233,7 +54233,7 @@
         <v>46107</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>46140</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>46030</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>46105</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54535,7 +54535,7 @@
         <v>46105</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>46107</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>46107</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>46069</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54842,7 +54842,7 @@
         <v>46030</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54915,7 +54915,7 @@
         <v>45422</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>44927</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>45125</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>45686</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>46034</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>45282</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45705</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>45784</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>46070</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>46077</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55660,7 +55660,7 @@
         <v>46029</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>45945</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>44616</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>46041</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45146</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56025,7 +56025,7 @@
         <v>46105</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56103,7 +56103,7 @@
         <v>45905</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56181,7 +56181,7 @@
         <v>45034</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>46045</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>45120</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45744</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>44942</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56556,7 +56556,7 @@
         <v>46031</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56629,7 +56629,7 @@
         <v>46045</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>46033</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>46065</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56853,7 +56853,7 @@
         <v>46141</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56931,7 +56931,7 @@
         <v>46141</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57009,7 +57009,7 @@
         <v>46030</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57082,7 +57082,7 @@
         <v>46111</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>46111</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57238,7 +57238,7 @@
         <v>46141</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>46052</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57394,7 +57394,7 @@
         <v>46052</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57472,7 +57472,7 @@
         <v>46052</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         <v>46056</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>46056</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57696,7 +57696,7 @@
         <v>46056</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57769,7 +57769,7 @@
         <v>46058</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57842,7 +57842,7 @@
         <v>46058</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57915,7 +57915,7 @@
         <v>46141</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57993,7 +57993,7 @@
         <v>46142</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58071,7 +58071,7 @@
         <v>46062</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58149,7 +58149,7 @@
         <v>46062</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58222,7 +58222,7 @@
         <v>46063</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>46045</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58373,7 +58373,7 @@
         <v>46146</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58451,7 +58451,7 @@
         <v>46108</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>46147</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58607,7 +58607,7 @@
         <v>46065</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>46101</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58758,7 +58758,7 @@
         <v>46069</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>46069</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58909,7 +58909,7 @@
         <v>46071</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>46072</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>46101</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59143,7 +59143,7 @@
         <v>46154</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59221,7 +59221,7 @@
         <v>46072</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         <v>46076</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59377,7 +59377,7 @@
         <v>46077</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59455,7 +59455,7 @@
         <v>46153</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>46079</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>46153</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>46083</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>46155</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>46155</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59908,7 +59908,7 @@
         <v>46119</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>46085</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60059,7 +60059,7 @@
         <v>46105</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60137,7 +60137,7 @@
         <v>46155</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60215,7 +60215,7 @@
         <v>46105</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60293,7 +60293,7 @@
         <v>46085</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60366,7 +60366,7 @@
         <v>46155</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60444,7 +60444,7 @@
         <v>46105</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60522,7 +60522,7 @@
         <v>46107</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60600,7 +60600,7 @@
         <v>46106</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>46107</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60756,7 +60756,7 @@
         <v>46093</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60834,7 +60834,7 @@
         <v>46092</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60912,7 +60912,7 @@
         <v>46092</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60990,7 +60990,7 @@
         <v>46092</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61068,7 +61068,7 @@
         <v>46094</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61146,7 +61146,7 @@
         <v>46094</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61224,7 +61224,7 @@
         <v>46094</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61302,7 +61302,7 @@
         <v>45312</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>46094</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61453,7 +61453,7 @@
         <v>46095</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>46094</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61604,7 +61604,7 @@
         <v>46094</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61682,7 +61682,7 @@
         <v>46094</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>46107</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61838,7 +61838,7 @@
         <v>46163</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61916,7 +61916,7 @@
         <v>46168</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61994,7 +61994,7 @@
         <v>46167</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>46168</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>46168</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62223,7 +62223,7 @@
         <v>46169</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         <v>46169</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>46169</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>46169</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62535,7 +62535,7 @@
         <v>46169</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62613,7 +62613,7 @@
         <v>46173</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62686,7 +62686,7 @@
         <v>46170</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62759,7 +62759,7 @@
         <v>46177</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62832,7 +62832,7 @@
         <v>46177</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62905,7 +62905,7 @@
         <v>46141</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>46176</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63056,7 +63056,7 @@
         <v>46176</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63129,7 +63129,7 @@
         <v>46178</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63202,7 +63202,7 @@
         <v>46183</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63280,7 +63280,7 @@
         <v>46183</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63358,7 +63358,7 @@
         <v>46185</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>46185</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63514,7 +63514,7 @@
         <v>46185</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>46185</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63670,7 +63670,7 @@
         <v>46185</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63748,7 +63748,7 @@
         <v>46185</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63826,7 +63826,7 @@
         <v>46185</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63904,7 +63904,7 @@
         <v>46185</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63982,7 +63982,7 @@
         <v>46184</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64060,7 +64060,7 @@
         <v>46185</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64138,7 +64138,7 @@
         <v>46185</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64216,7 +64216,7 @@
         <v>46185</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64294,7 +64294,7 @@
         <v>46185</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64372,7 +64372,7 @@
         <v>46185</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64445,7 +64445,7 @@
         <v>46185</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64523,7 +64523,7 @@
         <v>46185</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64601,7 +64601,7 @@
         <v>46185</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64679,7 +64679,7 @@
         <v>46185</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64757,7 +64757,7 @@
         <v>46185</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64835,7 +64835,7 @@
         <v>46188</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64913,7 +64913,7 @@
         <v>46188</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64991,7 +64991,7 @@
         <v>46188</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65069,7 +65069,7 @@
         <v>46132</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65142,7 +65142,7 @@
         <v>46195</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65215,7 +65215,7 @@
         <v>46198</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65293,7 +65293,7 @@
         <v>46198</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65371,7 +65371,7 @@
         <v>46196</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65449,7 +65449,7 @@
         <v>46197</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65527,7 +65527,7 @@
         <v>46196</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65605,7 +65605,7 @@
         <v>46196</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65683,7 +65683,7 @@
         <v>46160</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65761,7 +65761,7 @@
         <v>46196</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65839,7 +65839,7 @@
         <v>46198</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65917,7 +65917,7 @@
         <v>46198</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         <v>46198</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66073,7 +66073,7 @@
         <v>46198</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66151,7 +66151,7 @@
         <v>46198</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66229,7 +66229,7 @@
         <v>46198</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66307,7 +66307,7 @@
         <v>46202</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66385,7 +66385,7 @@
         <v>46202</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66463,7 +66463,7 @@
         <v>46203</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66541,7 +66541,7 @@
         <v>46206</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66619,7 +66619,7 @@
         <v>45950</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66692,7 +66692,7 @@
         <v>46106</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>46154</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66848,7 +66848,7 @@
         <v>46207</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66926,7 +66926,7 @@
         <v>46210</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -67004,7 +67004,7 @@
         <v>46213</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -67082,7 +67082,7 @@
         <v>46213</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -67160,7 +67160,7 @@
         <v>46217</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67238,7 +67238,7 @@
         <v>46217</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67311,7 +67311,7 @@
         <v>46220</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>46223</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67467,7 +67467,7 @@
         <v>46265</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67540,7 +67540,7 @@
         <v>46265</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67618,7 +67618,7 @@
         <v>46267</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67696,7 +67696,7 @@
         <v>46267</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -67774,7 +67774,7 @@
         <v>46267</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67852,7 +67852,7 @@
         <v>46267</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67930,7 +67930,7 @@
         <v>46267</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -68008,7 +68008,7 @@
         <v>46269</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -68086,7 +68086,7 @@
         <v>46269</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -68164,7 +68164,7 @@
         <v>46269</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68242,7 +68242,7 @@
         <v>46269</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68320,7 +68320,7 @@
         <v>46272</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68398,7 +68398,7 @@
         <v>46272</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68471,7 +68471,7 @@
         <v>46272</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68544,7 +68544,7 @@
         <v>46274</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68622,7 +68622,7 @@
         <v>46273</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68700,7 +68700,7 @@
         <v>46274</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -68778,7 +68778,7 @@
         <v>46274</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68856,7 +68856,7 @@
         <v>46273</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68934,7 +68934,7 @@
         <v>46273</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -69012,7 +69012,7 @@
         <v>46273</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -69090,7 +69090,7 @@
         <v>46273</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -69168,7 +69168,7 @@
         <v>46273</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -69246,7 +69246,7 @@
         <v>46276</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69324,7 +69324,7 @@
         <v>46276</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69402,7 +69402,7 @@
         <v>46275</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69480,7 +69480,7 @@
         <v>46275</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69558,7 +69558,7 @@
         <v>46276</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69636,7 +69636,7 @@
         <v>46276</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69714,7 +69714,7 @@
         <v>46280</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -69792,7 +69792,7 @@
         <v>46280</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -69870,7 +69870,7 @@
         <v>46280</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -69948,7 +69948,7 @@
         <v>46280</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -70026,7 +70026,7 @@
         <v>46279</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -70099,7 +70099,7 @@
         <v>46279</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -70177,7 +70177,7 @@
         <v>46280</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -70255,7 +70255,7 @@
         <v>46280</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70333,7 +70333,7 @@
         <v>46280</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70411,7 +70411,7 @@
         <v>46280</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70489,7 +70489,7 @@
         <v>46281</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70567,7 +70567,7 @@
         <v>46239</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70645,7 +70645,7 @@
         <v>46282</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70723,7 +70723,7 @@
         <v>46282</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -70801,7 +70801,7 @@
         <v>46282</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -70879,7 +70879,7 @@
         <v>46282</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -70957,7 +70957,7 @@
         <v>46282</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -71035,7 +71035,7 @@
         <v>46239</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -71113,7 +71113,7 @@
         <v>46282</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -71191,7 +71191,7 @@
         <v>46281</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -71269,7 +71269,7 @@
         <v>46282</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71347,7 +71347,7 @@
         <v>46283</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71425,7 +71425,7 @@
         <v>46283</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71503,7 +71503,7 @@
         <v>46283</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71581,7 +71581,7 @@
         <v>46283</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71659,7 +71659,7 @@
         <v>46283</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71737,7 +71737,7 @@
         <v>46286</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -71815,7 +71815,7 @@
         <v>46283</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -71893,7 +71893,7 @@
         <v>46283</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -71971,7 +71971,7 @@
         <v>46283</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72049,7 +72049,7 @@
         <v>46283</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -72127,7 +72127,7 @@
         <v>46283</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -72205,7 +72205,7 @@
         <v>46283</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -72283,7 +72283,7 @@
         <v>46283</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -72361,7 +72361,7 @@
         <v>46283</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72439,7 +72439,7 @@
         <v>46283</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72517,7 +72517,7 @@
         <v>46283</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72595,7 +72595,7 @@
         <v>46287</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72673,7 +72673,7 @@
         <v>46287</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72751,7 +72751,7 @@
         <v>46288</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -72829,7 +72829,7 @@
         <v>46244</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -72907,7 +72907,7 @@
         <v>46287</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -72985,7 +72985,7 @@
         <v>46287</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73063,7 +73063,7 @@
         <v>46244</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -73141,7 +73141,7 @@
         <v>46244</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -73219,7 +73219,7 @@
         <v>46287</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -73297,7 +73297,7 @@
         <v>46287</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -73375,7 +73375,7 @@
         <v>46185</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73453,7 +73453,7 @@
         <v>46246</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73531,7 +73531,7 @@
         <v>46246</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73609,7 +73609,7 @@
         <v>46246</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73682,7 +73682,7 @@
         <v>46246</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73755,7 +73755,7 @@
         <v>46290</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -73833,7 +73833,7 @@
         <v>46290</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -73911,7 +73911,7 @@
         <v>46289</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -73984,7 +73984,7 @@
         <v>46246</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -74062,7 +74062,7 @@
         <v>46246</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -74140,7 +74140,7 @@
         <v>46246</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -74218,7 +74218,7 @@
         <v>46289</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -74296,7 +74296,7 @@
         <v>46290</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -74374,7 +74374,7 @@
         <v>45819</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -74452,7 +74452,7 @@
         <v>46289</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74530,7 +74530,7 @@
         <v>46290</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74608,7 +74608,7 @@
         <v>46290</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74686,7 +74686,7 @@
         <v>46293</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74764,7 +74764,7 @@
         <v>46294</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74842,7 +74842,7 @@
         <v>46248</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -74915,7 +74915,7 @@
         <v>46248</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -74988,7 +74988,7 @@
         <v>46169</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -75061,7 +75061,7 @@
         <v>46248</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -75139,7 +75139,7 @@
         <v>46248</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -75217,7 +75217,7 @@
         <v>46293</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -75295,7 +75295,7 @@
         <v>46104</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -75368,7 +75368,7 @@
         <v>46161</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -75446,7 +75446,7 @@
         <v>46293</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75524,7 +75524,7 @@
         <v>46293</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75602,7 +75602,7 @@
         <v>46296</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75680,7 +75680,7 @@
         <v>46251</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75758,7 +75758,7 @@
         <v>46295</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -75836,7 +75836,7 @@
         <v>46295</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -75914,7 +75914,7 @@
         <v>46252</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -75987,7 +75987,7 @@
         <v>46295</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -76065,7 +76065,7 @@
         <v>45967</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -76143,7 +76143,7 @@
         <v>45944</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -76221,7 +76221,7 @@
         <v>46255</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -76299,7 +76299,7 @@
         <v>45987</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -76377,7 +76377,7 @@
         <v>46300</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -76455,7 +76455,7 @@
         <v>46185</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -76533,7 +76533,7 @@
         <v>46094</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76611,7 +76611,7 @@
         <v>45967</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76689,7 +76689,7 @@
         <v>46297</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76767,7 +76767,7 @@
         <v>46063</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76845,7 +76845,7 @@
         <v>46147</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -76923,7 +76923,7 @@
         <v>46297</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -77001,7 +77001,7 @@
         <v>46297</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -77079,7 +77079,7 @@
         <v>46254</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -77157,7 +77157,7 @@
         <v>46280</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -77235,7 +77235,7 @@
         <v>46254</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -77313,7 +77313,7 @@
         <v>46181</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -77391,7 +77391,7 @@
         <v>46185</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -77469,7 +77469,7 @@
         <v>46255</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -77547,7 +77547,7 @@
         <v>46255</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77620,7 +77620,7 @@
         <v>46297</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77698,7 +77698,7 @@
         <v>46297</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77776,7 +77776,7 @@
         <v>46147</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77854,7 +77854,7 @@
         <v>46297</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -77932,7 +77932,7 @@
         <v>46297</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -78010,7 +78010,7 @@
         <v>46210</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -78088,7 +78088,7 @@
         <v>46178</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -78166,7 +78166,7 @@
         <v>46296</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -78244,7 +78244,7 @@
         <v>46258</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -78317,7 +78317,7 @@
         <v>45805</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -78390,7 +78390,7 @@
         <v>46281</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -78463,7 +78463,7 @@
         <v>46301</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -78541,7 +78541,7 @@
         <v>46301</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -78619,7 +78619,7 @@
         <v>46258</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78697,7 +78697,7 @@
         <v>46301</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78775,7 +78775,7 @@
         <v>46262</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78853,7 +78853,7 @@
         <v>46304</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -78931,7 +78931,7 @@
         <v>46084</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -79009,7 +79009,7 @@
         <v>46304</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -79087,7 +79087,7 @@
         <v>46304</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -79165,7 +79165,7 @@
         <v>46303</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -79238,7 +79238,7 @@
         <v>46261</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -79316,7 +79316,7 @@
         <v>45420</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -79394,7 +79394,7 @@
         <v>46262</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -79472,7 +79472,7 @@
         <v>46100</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -79550,7 +79550,7 @@
         <v>46260</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -79623,7 +79623,7 @@
         <v>46304</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -79701,7 +79701,7 @@
         <v>46304</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -79779,7 +79779,7 @@
         <v>46261</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -79857,7 +79857,7 @@
         <v>46261</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -79935,7 +79935,7 @@
         <v>46304</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -80013,7 +80013,7 @@
         <v>46261</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -80091,7 +80091,7 @@
         <v>46093</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -80169,7 +80169,7 @@
         <v>46094</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -80247,7 +80247,7 @@
         <v>46262</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -80320,7 +80320,7 @@
         <v>46304</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -80398,7 +80398,7 @@
         <v>46304</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -80476,7 +80476,7 @@
         <v>46304</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -80554,7 +80554,7 @@
         <v>46262</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -80632,7 +80632,7 @@
         <v>45933</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -80710,7 +80710,7 @@
         <v>45205</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -80803,7 +80803,7 @@
         <v>44995</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -80881,7 +80881,7 @@
         <v>45376</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -80959,7 +80959,7 @@
         <v>45470</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -81037,7 +81037,7 @@
         <v>46089</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -601,7 +601,7 @@
         <v>45741</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46014</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>45966</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44588</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45019</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>46135</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>46079</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45623</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45842</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>45593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>46052</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45825</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45302</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45982</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45107</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45741</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>45926</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>45926</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>45848</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45315</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>45638</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46089</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45324</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>45614</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45302</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45281</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>46041</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>46052</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>46282</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>46174</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>45715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>46136</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>46304</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>45398</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45420</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>45825</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>46107</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>46076</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>46176</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>46279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>46293</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>46254</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44876</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45338</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>44887</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>45512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45898</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>45281</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45903</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>45792</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>45943</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>45420</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45737</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>45533</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>46094</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45994</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>46134</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>45107</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>46139</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>46101</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>46153</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>46119</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>46169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>46185</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>46199</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>46280</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>46185</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>46254</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>46100</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>46093</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45699</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44658</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>45379</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>45386</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45884</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>45530</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>44959</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>44959</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>45120</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>44999</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45440</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45631</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45604</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>45820</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>45588</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45938</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45730</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>45272</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45015</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45827</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45967</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45645</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>44790</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>45728</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>44840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>45720</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45726</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>45984</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>44811</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>46094</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>46101</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>46101</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>46101</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45719</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>46141</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>46101</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>46153</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>45943</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>46157</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>46097</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>46185</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>46185</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>46185</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>46197</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>46217</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>46267</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>46274</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>46282</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>46283</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46265</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>46287</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>46185</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>46290</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>46290</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>46294</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>46251</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>46252</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>46093</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>46160</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>46119</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>46255</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>46133</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>45420</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45973</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>46259</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44585</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45680</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45562</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>46113</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44749</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44775</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>44519</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44886</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44629</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>44494</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>44735</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44775</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44663</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44573</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44882</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44756</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44813</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44671</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>44735</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44658</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44498</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>44776</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44796</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44571</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>44788</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>44840</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>44785</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>44785</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>44599</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44589</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>44845</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>44599</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44734</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45261</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45070</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>44684</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45757</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45757</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45090</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44795</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>45162</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>44491</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45138</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>45608</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45757</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>45706</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>44951</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45272</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45400</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>44804</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44874</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44867</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45436</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45468</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45559</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44840</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45084</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44539</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45334</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45107</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45715</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45715</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44876</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45240</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>44733</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>44862</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44841</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45217</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45373</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45593</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45467</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45526</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21933,7 +21933,7 @@
         <v>45632</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45182</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45454</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>45574</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45454</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45257</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45232</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45645</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45672</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45660</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45660</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>44498</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45117</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45884</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>44935</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45649</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45113</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45645</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>44823</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45468</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>44818</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45884</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>45168</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45699</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45162</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45600</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45749</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44533</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45519</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45539</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44756</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44910</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>44910</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>44942</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45530</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>44885</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45665</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>45891</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45895</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45895</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45896</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>45898</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45898</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45898</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45898</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45898</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>45882</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45898</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45898</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>45902</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45720</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45586</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45485</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>44936</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45749</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>44845</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45511</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45658</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44488</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45644</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45530</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>45306</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45266</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45312</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45905</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>45440</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45540</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45161</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45266</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45660</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>44546</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45595</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45909</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>45909</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>45475</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>45580</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>45908</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45776</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45540</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45909</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45909</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45911</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45782</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45414</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45412</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45120</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45252</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44889</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44637</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>45719</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>44517</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44988</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45915</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45705</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29068,7 +29068,7 @@
         <v>44585</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>45702</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>45324</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45182</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45726</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>45742</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>45547</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45888</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44585</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45146</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45106</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>44959</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>45924</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45923</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45790</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>44693</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>45223</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>45896</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>45924</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>45523</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>45660</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45790</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>45660</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>45926</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45791</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>45644</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45926</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>45926</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45030</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>45019</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45791</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45652</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31469,7 +31469,7 @@
         <v>45791</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45930</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>45930</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>44691</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>45594</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45040</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45104</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31995,7 +31995,7 @@
         <v>45623</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         <v>45702</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>45595</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45932</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>45632</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32360,7 +32360,7 @@
         <v>45932</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45931</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45931</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44951</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45797</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44951</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45798</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>45797</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45324</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45932</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45505</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45282</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45282</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45933</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>44763</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>44713</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45933</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45330</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>45933</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>44739</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>45058</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45804</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45356</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>44586</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>45938</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>45937</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>44708</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>45699</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34454,7 +34454,7 @@
         <v>45646</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>45082</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45735</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45462</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>45463</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>45916</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>45939</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45940</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>45939</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>45547</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>45943</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
         <v>45944</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45614</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35428,7 +35428,7 @@
         <v>45817</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45673</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>45673</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45813</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45813</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35793,7 +35793,7 @@
         <v>44684</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>45728</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>45034</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>45084</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>45705</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>45090</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45817</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45819</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>44684</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36460,7 +36460,7 @@
         <v>45218</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>44586</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>45741</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>45666</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45827</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>45827</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45827</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45827</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45952</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45089</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45245</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37273,7 +37273,7 @@
         <v>45672</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37351,7 +37351,7 @@
         <v>45832</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45953</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45957</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
         <v>45957</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>45960</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>44936</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44790</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37867,7 +37867,7 @@
         <v>44518</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37940,7 +37940,7 @@
         <v>45084</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45964</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45834</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>45835</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45631</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>44735</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>44701</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>44922</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>45965</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>45089</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>45965</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45014</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45967</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45968</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>45113</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>44741</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>44800</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>45845</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>45630</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45784</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45845</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45971</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45184</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>44694</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45974</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45974</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>45848</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45974</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>45974</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>45974</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>44904</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>45848</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>45974</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45540</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>45973</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>45632</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45974</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>45974</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45974</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45973</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45973</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45660</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45854</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44756</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>44756</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45265</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>45859</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>45014</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>45862</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45862</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>44767</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>45862</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>45715</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>45652</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41992,7 +41992,7 @@
         <v>45978</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>45978</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>45866</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45867</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>45261</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>45978</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45869</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>45530</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>45869</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>45312</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45089</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45685</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42898,7 +42898,7 @@
         <v>45873</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>45660</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45660</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45176</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>45176</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45681</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>45350</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>44973</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>44589</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45751</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>45545</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45282</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45282</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>45243</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45740</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>46094</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>46094</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>44539</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>46098</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>46099</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45392</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>45401</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44554,7 +44554,7 @@
         <v>45526</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>46101</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>46100</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45645</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45985</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>45574</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>46104</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45090,7 +45090,7 @@
         <v>45026</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>46105</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>44853</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>46104</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45392,7 +45392,7 @@
         <v>45245</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>46106</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>45922</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>45912</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45912</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>45922</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>45922</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>46106</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46011,7 +46011,7 @@
         <v>45320</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45520</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
         <v>45520</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45014</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>46111</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46381,7 +46381,7 @@
         <v>45922</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45922</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46537,7 +46537,7 @@
         <v>45726</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45912</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46688,7 +46688,7 @@
         <v>45912</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45922</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45922</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>45646</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>46108</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45922</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>45912</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>45922</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>45922</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45992</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47458,7 +47458,7 @@
         <v>45611</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47531,7 +47531,7 @@
         <v>45706</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         <v>45992</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45203</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45993</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>44519</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>46077</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>44603</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>44973</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>46120</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>46124</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
         <v>46124</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48339,7 +48339,7 @@
         <v>45994</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>45995</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>46122</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>46031</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>46124</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>46125</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>45995</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>46125</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>45968</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>46106</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49079,7 +49079,7 @@
         <v>46106</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>45995</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>46000</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>46002</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49381,7 +49381,7 @@
         <v>46002</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>46106</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>46002</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>46094</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>46104</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>46132</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>46106</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>46128</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>44959</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>46132</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>44911</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50214,7 +50214,7 @@
         <v>44735</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>44960</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50365,7 +50365,7 @@
         <v>46132</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>46128</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50521,7 +50521,7 @@
         <v>46132</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>46006</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>46133</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50755,7 +50755,7 @@
         <v>46105</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50833,7 +50833,7 @@
         <v>46133</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50911,7 +50911,7 @@
         <v>46133</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         <v>46100</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>44693</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>46134</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51223,7 +51223,7 @@
         <v>46134</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51301,7 +51301,7 @@
         <v>46094</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         <v>46134</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>46008</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>46134</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>46100</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>45915</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>46134</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51842,7 +51842,7 @@
         <v>46134</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>46090</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45158</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>45158</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>44656</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52217,7 +52217,7 @@
         <v>45397</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>46107</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>44694</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52451,7 +52451,7 @@
         <v>45869</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52524,7 +52524,7 @@
         <v>45862</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52597,7 +52597,7 @@
         <v>44600</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>46019</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52748,7 +52748,7 @@
         <v>45967</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52821,7 +52821,7 @@
         <v>45931</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52894,7 +52894,7 @@
         <v>45937</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52967,7 +52967,7 @@
         <v>45855</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53040,7 +53040,7 @@
         <v>44651</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>46019</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53191,7 +53191,7 @@
         <v>45908</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>45932</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45932</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>45937</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>45908</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>44616</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>46077</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>46022</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>46106</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>46106</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53931,7 +53931,7 @@
         <v>45932</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         <v>46108</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54082,7 +54082,7 @@
         <v>44962</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54155,7 +54155,7 @@
         <v>45744</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54233,7 +54233,7 @@
         <v>46107</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54311,7 +54311,7 @@
         <v>46140</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>46030</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>46105</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54535,7 +54535,7 @@
         <v>46105</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>46107</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>46107</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>46069</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54842,7 +54842,7 @@
         <v>46030</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54915,7 +54915,7 @@
         <v>45422</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>44927</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>45125</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>45686</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>46034</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>45282</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45705</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55436,7 +55436,7 @@
         <v>45784</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>46070</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55582,7 +55582,7 @@
         <v>46077</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55660,7 +55660,7 @@
         <v>46029</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>45945</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>44616</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>46041</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55952,7 +55952,7 @@
         <v>45146</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56025,7 +56025,7 @@
         <v>46105</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56103,7 +56103,7 @@
         <v>45905</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56181,7 +56181,7 @@
         <v>45034</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56259,7 +56259,7 @@
         <v>46045</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56332,7 +56332,7 @@
         <v>45120</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56405,7 +56405,7 @@
         <v>45744</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>44942</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56556,7 +56556,7 @@
         <v>46031</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56629,7 +56629,7 @@
         <v>46045</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>46033</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>46065</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56853,7 +56853,7 @@
         <v>46141</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56931,7 +56931,7 @@
         <v>46141</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57009,7 +57009,7 @@
         <v>46030</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57082,7 +57082,7 @@
         <v>46111</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>46111</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57238,7 +57238,7 @@
         <v>46141</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>46052</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57394,7 +57394,7 @@
         <v>46052</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57472,7 +57472,7 @@
         <v>46052</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         <v>46056</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>46056</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57696,7 +57696,7 @@
         <v>46056</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57769,7 +57769,7 @@
         <v>46058</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57842,7 +57842,7 @@
         <v>46058</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57915,7 +57915,7 @@
         <v>46141</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57993,7 +57993,7 @@
         <v>46142</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58071,7 +58071,7 @@
         <v>46062</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58149,7 +58149,7 @@
         <v>46062</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58222,7 +58222,7 @@
         <v>46063</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>46045</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58373,7 +58373,7 @@
         <v>46146</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58451,7 +58451,7 @@
         <v>46108</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>46147</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58607,7 +58607,7 @@
         <v>46065</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>46101</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58758,7 +58758,7 @@
         <v>46069</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>46069</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58909,7 +58909,7 @@
         <v>46071</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>46072</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>46101</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59143,7 +59143,7 @@
         <v>46154</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59221,7 +59221,7 @@
         <v>46072</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         <v>46076</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59377,7 +59377,7 @@
         <v>46077</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59455,7 +59455,7 @@
         <v>46153</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>46079</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>46153</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>46083</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>46155</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>46155</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59908,7 +59908,7 @@
         <v>46119</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>46085</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60059,7 +60059,7 @@
         <v>46105</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60137,7 +60137,7 @@
         <v>46155</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60215,7 +60215,7 @@
         <v>46105</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60293,7 +60293,7 @@
         <v>46085</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60366,7 +60366,7 @@
         <v>46155</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60444,7 +60444,7 @@
         <v>46105</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60522,7 +60522,7 @@
         <v>46107</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60600,7 +60600,7 @@
         <v>46106</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>46107</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60756,7 +60756,7 @@
         <v>46093</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60834,7 +60834,7 @@
         <v>46092</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60912,7 +60912,7 @@
         <v>46092</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60990,7 +60990,7 @@
         <v>46092</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61068,7 +61068,7 @@
         <v>46094</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61146,7 +61146,7 @@
         <v>46094</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61224,7 +61224,7 @@
         <v>46094</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61302,7 +61302,7 @@
         <v>45312</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>46094</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61453,7 +61453,7 @@
         <v>46095</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>46094</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61604,7 +61604,7 @@
         <v>46094</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61682,7 +61682,7 @@
         <v>46094</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>46107</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61838,7 +61838,7 @@
         <v>46163</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61916,7 +61916,7 @@
         <v>46168</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61994,7 +61994,7 @@
         <v>46167</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>46168</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>46168</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62223,7 +62223,7 @@
         <v>46169</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         <v>46169</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>46169</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>46169</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62535,7 +62535,7 @@
         <v>46169</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62613,7 +62613,7 @@
         <v>46173</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62686,7 +62686,7 @@
         <v>46170</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62759,7 +62759,7 @@
         <v>46177</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62832,7 +62832,7 @@
         <v>46177</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62905,7 +62905,7 @@
         <v>46141</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>46176</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63056,7 +63056,7 @@
         <v>46176</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63129,7 +63129,7 @@
         <v>46178</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63202,7 +63202,7 @@
         <v>46183</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63280,7 +63280,7 @@
         <v>46183</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63358,7 +63358,7 @@
         <v>46185</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>46185</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63514,7 +63514,7 @@
         <v>46185</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>46185</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63670,7 +63670,7 @@
         <v>46185</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63748,7 +63748,7 @@
         <v>46185</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63826,7 +63826,7 @@
         <v>46185</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63904,7 +63904,7 @@
         <v>46185</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63982,7 +63982,7 @@
         <v>46184</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64060,7 +64060,7 @@
         <v>46185</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64138,7 +64138,7 @@
         <v>46185</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64216,7 +64216,7 @@
         <v>46185</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64294,7 +64294,7 @@
         <v>46185</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64372,7 +64372,7 @@
         <v>46185</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64445,7 +64445,7 @@
         <v>46185</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64523,7 +64523,7 @@
         <v>46185</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64601,7 +64601,7 @@
         <v>46185</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64679,7 +64679,7 @@
         <v>46185</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64757,7 +64757,7 @@
         <v>46185</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64835,7 +64835,7 @@
         <v>46188</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64913,7 +64913,7 @@
         <v>46188</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64991,7 +64991,7 @@
         <v>46188</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65069,7 +65069,7 @@
         <v>46132</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65142,7 +65142,7 @@
         <v>46195</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65215,7 +65215,7 @@
         <v>46198</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65293,7 +65293,7 @@
         <v>46198</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65371,7 +65371,7 @@
         <v>46196</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65449,7 +65449,7 @@
         <v>46197</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65527,7 +65527,7 @@
         <v>46196</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65605,7 +65605,7 @@
         <v>46196</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65683,7 +65683,7 @@
         <v>46160</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65761,7 +65761,7 @@
         <v>46196</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -65839,7 +65839,7 @@
         <v>46198</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -65917,7 +65917,7 @@
         <v>46198</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         <v>46198</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66073,7 +66073,7 @@
         <v>46198</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66151,7 +66151,7 @@
         <v>46198</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66229,7 +66229,7 @@
         <v>46198</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66307,7 +66307,7 @@
         <v>46202</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66385,7 +66385,7 @@
         <v>46202</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66463,7 +66463,7 @@
         <v>46203</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66541,7 +66541,7 @@
         <v>46206</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66619,7 +66619,7 @@
         <v>45950</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66692,7 +66692,7 @@
         <v>46106</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>46154</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -66848,7 +66848,7 @@
         <v>46207</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -66926,7 +66926,7 @@
         <v>46210</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -67004,7 +67004,7 @@
         <v>46213</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -67082,7 +67082,7 @@
         <v>46213</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -67160,7 +67160,7 @@
         <v>46217</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67238,7 +67238,7 @@
         <v>46217</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67311,7 +67311,7 @@
         <v>46220</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>46223</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67467,7 +67467,7 @@
         <v>46265</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67540,7 +67540,7 @@
         <v>46265</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67618,7 +67618,7 @@
         <v>46267</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -67696,7 +67696,7 @@
         <v>46267</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -67774,7 +67774,7 @@
         <v>46267</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -67852,7 +67852,7 @@
         <v>46267</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -67930,7 +67930,7 @@
         <v>46267</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -68008,7 +68008,7 @@
         <v>46269</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -68086,7 +68086,7 @@
         <v>46269</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -68164,7 +68164,7 @@
         <v>46269</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68242,7 +68242,7 @@
         <v>46269</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68320,7 +68320,7 @@
         <v>46272</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68398,7 +68398,7 @@
         <v>46272</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68471,7 +68471,7 @@
         <v>46272</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68544,7 +68544,7 @@
         <v>46274</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68622,7 +68622,7 @@
         <v>46273</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68700,7 +68700,7 @@
         <v>46274</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -68778,7 +68778,7 @@
         <v>46274</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -68856,7 +68856,7 @@
         <v>46273</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -68934,7 +68934,7 @@
         <v>46273</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -69012,7 +69012,7 @@
         <v>46273</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -69090,7 +69090,7 @@
         <v>46273</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -69168,7 +69168,7 @@
         <v>46273</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -69246,7 +69246,7 @@
         <v>46276</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69324,7 +69324,7 @@
         <v>46276</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69402,7 +69402,7 @@
         <v>46275</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69480,7 +69480,7 @@
         <v>46275</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69558,7 +69558,7 @@
         <v>46276</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69636,7 +69636,7 @@
         <v>46276</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69714,7 +69714,7 @@
         <v>46280</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -69792,7 +69792,7 @@
         <v>46280</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -69870,7 +69870,7 @@
         <v>46280</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -69948,7 +69948,7 @@
         <v>46280</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -70026,7 +70026,7 @@
         <v>46279</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -70099,7 +70099,7 @@
         <v>46279</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -70177,7 +70177,7 @@
         <v>46280</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -70255,7 +70255,7 @@
         <v>46280</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70333,7 +70333,7 @@
         <v>46280</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70411,7 +70411,7 @@
         <v>46280</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70489,7 +70489,7 @@
         <v>46281</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70567,7 +70567,7 @@
         <v>46239</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70645,7 +70645,7 @@
         <v>46282</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70723,7 +70723,7 @@
         <v>46282</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -70801,7 +70801,7 @@
         <v>46282</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -70879,7 +70879,7 @@
         <v>46282</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -70957,7 +70957,7 @@
         <v>46282</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -71035,7 +71035,7 @@
         <v>46239</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -71113,7 +71113,7 @@
         <v>46282</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -71191,7 +71191,7 @@
         <v>46281</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -71269,7 +71269,7 @@
         <v>46282</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71347,7 +71347,7 @@
         <v>46283</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71425,7 +71425,7 @@
         <v>46283</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71503,7 +71503,7 @@
         <v>46283</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71581,7 +71581,7 @@
         <v>46283</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71659,7 +71659,7 @@
         <v>46283</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71737,7 +71737,7 @@
         <v>46286</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -71815,7 +71815,7 @@
         <v>46283</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -71893,7 +71893,7 @@
         <v>46283</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -71971,7 +71971,7 @@
         <v>46283</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72049,7 +72049,7 @@
         <v>46283</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -72127,7 +72127,7 @@
         <v>46283</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -72205,7 +72205,7 @@
         <v>46283</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -72283,7 +72283,7 @@
         <v>46283</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -72361,7 +72361,7 @@
         <v>46283</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72439,7 +72439,7 @@
         <v>46283</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72517,7 +72517,7 @@
         <v>46283</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72595,7 +72595,7 @@
         <v>46287</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72673,7 +72673,7 @@
         <v>46287</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72751,7 +72751,7 @@
         <v>46288</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -72829,7 +72829,7 @@
         <v>46244</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -72907,7 +72907,7 @@
         <v>46287</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -72985,7 +72985,7 @@
         <v>46287</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73063,7 +73063,7 @@
         <v>46244</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -73141,7 +73141,7 @@
         <v>46244</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -73219,7 +73219,7 @@
         <v>46287</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -73297,7 +73297,7 @@
         <v>46287</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -73375,7 +73375,7 @@
         <v>46185</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73453,7 +73453,7 @@
         <v>46246</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73531,7 +73531,7 @@
         <v>46246</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73609,7 +73609,7 @@
         <v>46246</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73682,7 +73682,7 @@
         <v>46246</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73755,7 +73755,7 @@
         <v>46290</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -73833,7 +73833,7 @@
         <v>46290</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -73911,7 +73911,7 @@
         <v>46289</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -73984,7 +73984,7 @@
         <v>46246</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -74062,7 +74062,7 @@
         <v>46246</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -74140,7 +74140,7 @@
         <v>46246</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -74218,7 +74218,7 @@
         <v>46289</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -74296,7 +74296,7 @@
         <v>46290</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -74374,7 +74374,7 @@
         <v>45819</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -74452,7 +74452,7 @@
         <v>46289</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74530,7 +74530,7 @@
         <v>46290</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74608,7 +74608,7 @@
         <v>46290</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74686,7 +74686,7 @@
         <v>46293</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74764,7 +74764,7 @@
         <v>46294</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -74842,7 +74842,7 @@
         <v>46248</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -74915,7 +74915,7 @@
         <v>46248</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -74988,7 +74988,7 @@
         <v>46169</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -75061,7 +75061,7 @@
         <v>46248</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -75139,7 +75139,7 @@
         <v>46248</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -75217,7 +75217,7 @@
         <v>46293</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -75295,7 +75295,7 @@
         <v>46104</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -75368,7 +75368,7 @@
         <v>46161</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -75446,7 +75446,7 @@
         <v>46293</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75524,7 +75524,7 @@
         <v>46293</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75602,7 +75602,7 @@
         <v>46296</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75680,7 +75680,7 @@
         <v>46251</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75758,7 +75758,7 @@
         <v>46295</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -75836,7 +75836,7 @@
         <v>46295</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -75914,7 +75914,7 @@
         <v>46252</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -75987,7 +75987,7 @@
         <v>46295</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -76065,7 +76065,7 @@
         <v>45967</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -76143,7 +76143,7 @@
         <v>45944</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -76221,7 +76221,7 @@
         <v>46255</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -76299,7 +76299,7 @@
         <v>45987</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -76377,7 +76377,7 @@
         <v>46300</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -76455,7 +76455,7 @@
         <v>46185</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -76533,7 +76533,7 @@
         <v>46094</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76611,7 +76611,7 @@
         <v>45967</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76689,7 +76689,7 @@
         <v>46297</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76767,7 +76767,7 @@
         <v>46063</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -76845,7 +76845,7 @@
         <v>46147</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -76923,7 +76923,7 @@
         <v>46297</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -77001,7 +77001,7 @@
         <v>46297</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -77079,7 +77079,7 @@
         <v>46254</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -77157,7 +77157,7 @@
         <v>46280</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -77235,7 +77235,7 @@
         <v>46254</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -77313,7 +77313,7 @@
         <v>46181</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -77391,7 +77391,7 @@
         <v>46185</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -77469,7 +77469,7 @@
         <v>46255</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -77547,7 +77547,7 @@
         <v>46255</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77620,7 +77620,7 @@
         <v>46297</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77698,7 +77698,7 @@
         <v>46297</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77776,7 +77776,7 @@
         <v>46147</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -77854,7 +77854,7 @@
         <v>46297</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -77932,7 +77932,7 @@
         <v>46297</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -78010,7 +78010,7 @@
         <v>46210</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -78088,7 +78088,7 @@
         <v>46178</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -78166,7 +78166,7 @@
         <v>46296</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -78244,7 +78244,7 @@
         <v>46258</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -78317,7 +78317,7 @@
         <v>45805</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -78390,7 +78390,7 @@
         <v>46281</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -78463,7 +78463,7 @@
         <v>46301</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -78541,7 +78541,7 @@
         <v>46301</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -78619,7 +78619,7 @@
         <v>46258</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78697,7 +78697,7 @@
         <v>46301</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78775,7 +78775,7 @@
         <v>46262</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78853,7 +78853,7 @@
         <v>46304</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -78931,7 +78931,7 @@
         <v>46084</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -79009,7 +79009,7 @@
         <v>46304</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -79087,7 +79087,7 @@
         <v>46304</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -79165,7 +79165,7 @@
         <v>46303</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -79238,7 +79238,7 @@
         <v>46261</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -79316,7 +79316,7 @@
         <v>45420</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -79394,7 +79394,7 @@
         <v>46262</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -79472,7 +79472,7 @@
         <v>46100</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -79550,7 +79550,7 @@
         <v>46260</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -79623,7 +79623,7 @@
         <v>46304</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -79701,7 +79701,7 @@
         <v>46304</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -79779,7 +79779,7 @@
         <v>46261</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -79857,7 +79857,7 @@
         <v>46261</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -79935,7 +79935,7 @@
         <v>46304</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -80013,7 +80013,7 @@
         <v>46261</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -80091,7 +80091,7 @@
         <v>46093</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -80169,7 +80169,7 @@
         <v>46094</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -80247,7 +80247,7 @@
         <v>46262</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -80320,7 +80320,7 @@
         <v>46304</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -80398,7 +80398,7 @@
         <v>46304</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -80476,7 +80476,7 @@
         <v>46304</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -80554,7 +80554,7 @@
         <v>46262</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -80632,7 +80632,7 @@
         <v>45933</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -80710,7 +80710,7 @@
         <v>45205</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -80803,7 +80803,7 @@
         <v>44995</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -80881,7 +80881,7 @@
         <v>45376</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -80959,7 +80959,7 @@
         <v>45470</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -81037,7 +81037,7 @@
         <v>46089</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -601,7 +601,7 @@
         <v>45741</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46014</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>45966</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44588</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45019</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>46135</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>46079</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45623</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45842</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45302</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45825</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45982</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45926</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45926</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>45848</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45107</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45741</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45315</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>45638</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46089</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45324</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>45614</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>46041</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>46052</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45302</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>46282</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>46136</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>46174</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>46304</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>45715</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>46107</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>46176</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>46076</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>45398</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>45420</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>46279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46293</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>46254</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>45825</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44876</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45107</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45737</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>46139</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45903</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>44887</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>45420</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45281</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>46101</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>46119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>46153</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45943</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>46169</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>45994</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45338</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>46185</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>46094</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>46199</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>46280</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>46254</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>45533</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>46185</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>46100</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>46093</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45699</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44658</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44959</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44959</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45530</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45120</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45645</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45015</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>44790</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44840</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>46101</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45884</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>46101</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>46101</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45719</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>46141</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>46101</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>45820</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>46153</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>45938</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45272</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>46157</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45967</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>45604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>45984</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45379</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45720</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44999</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>45440</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45631</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>46185</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>46185</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>46185</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45943</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>46097</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>46197</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>46094</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>46217</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>46274</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>46283</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>46282</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>46185</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44811</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>46287</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>46290</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>46290</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>46252</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>46294</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>46251</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45728</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45386</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>46119</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45420</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>46255</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>46093</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>46160</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>46133</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>46259</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>45805</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45973</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>46265</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>45588</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>45730</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>46311</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>46267</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45827</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45726</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44585</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45680</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>45562</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>46113</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44749</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44519</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44775</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44886</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44629</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44805</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44494</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44735</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44775</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44663</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44573</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44882</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>44756</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>44813</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>44671</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>44671</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>44599</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>44735</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>44658</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>44776</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44571</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>44788</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>44589</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>44498</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>44796</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>44785</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>44599</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>44845</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>44840</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44785</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>44734</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44684</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>44795</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>44491</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45706</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>44585</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>44889</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>45014</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45454</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>44959</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>45611</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45699</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44637</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45040</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45660</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>44656</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45726</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45646</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45547</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45089</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45706</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45158</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45158</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45265</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>44708</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45104</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>44862</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45715</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>44840</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>44942</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>44691</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45184</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45324</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45117</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>44756</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>44756</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45084</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45125</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44539</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44693</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>44867</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45632</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45162</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45719</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44733</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45645</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45540</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45652</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>44988</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>45726</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45030</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44589</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45468</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45530</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45475</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45146</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>45324</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45261</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45672</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45034</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45463</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>44951</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>44935</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>44960</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45720</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45084</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>44823</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>44533</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45356</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>44517</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45681</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>46094</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45862</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>46031</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45744</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>45884</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45905</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45526</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45593</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>46106</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>46077</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>46107</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45468</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>46105</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45744</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45245</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46070</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46065</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44684</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>46107</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>46105</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45884</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>46069</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45891</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45895</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45895</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45161</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>45665</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45896</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45113</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>45882</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45869</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45897</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>44735</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45223</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>46100</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>45715</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45898</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45898</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>44600</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>46106</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44693</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>45749</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>46140</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>46030</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45898</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45898</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>46077</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>46111</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>46111</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45401</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>45898</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>45898</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>46108</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45898</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>46141</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45485</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>46033</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>46141</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45454</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45595</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>45902</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>45742</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45705</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>45905</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45784</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>44585</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45909</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45909</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>45909</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45909</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>46141</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>46141</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45911</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>45908</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>46142</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>44735</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>45915</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44701</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>45511</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>46045</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>45630</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>46147</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45888</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45923</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45896</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>46146</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>46101</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>46108</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>45924</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>45924</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44684</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45926</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45926</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>45926</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44694</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>45931</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>45931</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>46153</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45930</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45930</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45932</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45933</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45933</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>45932</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45932</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>45933</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45138</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45168</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>44951</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>44951</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>45937</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>46153</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>45938</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>45939</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45916</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45939</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45940</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>44904</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>44962</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45660</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>45943</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>46155</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45944</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46119</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>46105</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45817</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>44942</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>46155</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45586</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45440</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45203</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>45632</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45526</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45666</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>46155</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45952</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45953</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45436</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>46105</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>45957</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>46101</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>45120</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>46154</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45957</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>46107</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>46107</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45312</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>45960</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45645</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45964</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45965</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45282</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>46106</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>45967</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45672</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>46105</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>46107</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>46155</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45965</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45971</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45645</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>45422</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>45162</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45968</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45973</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46163</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45058</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>45973</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45973</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>45974</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45974</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44586</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45974</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45974</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>45974</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45974</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45974</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>45974</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45974</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45978</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>45978</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>45658</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38306,7 +38306,7 @@
         <v>44518</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
         <v>45084</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45978</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44756</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45547</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>46167</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>44936</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>44911</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45600</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45649</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45912</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45912</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45922</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>45922</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45922</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45922</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45922</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>45912</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45985</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45912</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>45922</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45922</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45922</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45922</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45922</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>45912</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>45320</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>46169</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>46169</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>45992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>45993</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>46169</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45992</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>46169</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>46168</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>45994</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45995</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>46169</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>45995</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>46168</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>45968</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>45120</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45995</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>46168</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>46031</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45574</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>46000</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45312</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>46170</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>46002</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>46002</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>46002</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45257</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46173</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>46006</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>44651</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>45182</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>46008</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>45757</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45539</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45660</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         <v>45855</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>46019</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45967</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>45932</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45932</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43284,7 +43284,7 @@
         <v>46019</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43357,7 +43357,7 @@
         <v>45908</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45937</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45937</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>45908</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45931</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>45932</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>46022</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>46176</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45673</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45673</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>46030</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>45646</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>46030</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>44853</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>46176</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>46034</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>46141</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>44841</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>46041</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>46177</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45330</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>46178</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>46177</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>46045</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>46045</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45217</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>44616</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>46052</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>44876</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>46052</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>46052</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>44546</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>46056</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>46056</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>46056</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>46058</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>46058</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>46183</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>46063</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>46062</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>46062</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>44488</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>46183</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>46184</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>46065</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44519</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>46069</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>46185</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>46185</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>46185</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>46185</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>46185</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>46185</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>46069</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>46071</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>46185</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>46072</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>46185</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47696,7 +47696,7 @@
         <v>46188</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>46185</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>46072</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>46185</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>46185</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>46185</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>46185</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45090</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48315,7 +48315,7 @@
         <v>46076</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44936</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>46077</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48544,7 +48544,7 @@
         <v>46188</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>46188</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>46185</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>46185</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>46079</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45312</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>46185</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>46185</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>46185</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>45218</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>46083</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>45412</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>46085</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>46085</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>45595</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>46092</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45282</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>45282</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45282</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49986,7 +49986,7 @@
         <v>46092</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>46092</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>46132</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>46094</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>46094</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>46094</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>46094</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>46094</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>46094</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>46094</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50761,7 +50761,7 @@
         <v>46094</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>46093</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>46094</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>46095</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>46196</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51146,7 +51146,7 @@
         <v>46196</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>46098</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>45182</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>46099</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>44804</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51531,7 +51531,7 @@
         <v>44845</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>46100</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51682,7 +51682,7 @@
         <v>46196</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>46196</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>46104</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51916,7 +51916,7 @@
         <v>46101</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51994,7 +51994,7 @@
         <v>46104</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52067,7 +52067,7 @@
         <v>45644</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52145,7 +52145,7 @@
         <v>45644</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>46106</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>46195</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>46106</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>46105</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>44713</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45245</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52686,7 +52686,7 @@
         <v>46160</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45400</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52837,7 +52837,7 @@
         <v>46198</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>46198</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52993,7 +52993,7 @@
         <v>46198</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53071,7 +53071,7 @@
         <v>46108</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53149,7 +53149,7 @@
         <v>46197</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53227,7 +53227,7 @@
         <v>46198</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53305,7 +53305,7 @@
         <v>46198</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>46111</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>46198</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>46198</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53617,7 +53617,7 @@
         <v>46198</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53695,7 +53695,7 @@
         <v>44910</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53768,7 +53768,7 @@
         <v>46120</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53841,7 +53841,7 @@
         <v>46202</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53919,7 +53919,7 @@
         <v>45462</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53992,7 +53992,7 @@
         <v>45660</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45660</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54138,7 +54138,7 @@
         <v>46202</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54216,7 +54216,7 @@
         <v>46122</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54294,7 +54294,7 @@
         <v>44741</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54367,7 +54367,7 @@
         <v>46077</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54445,7 +54445,7 @@
         <v>46125</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54518,7 +54518,7 @@
         <v>46125</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54591,7 +54591,7 @@
         <v>46124</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>46124</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54737,7 +54737,7 @@
         <v>46124</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54810,7 +54810,7 @@
         <v>46128</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>46106</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54966,7 +54966,7 @@
         <v>45350</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55039,7 +55039,7 @@
         <v>46104</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55117,7 +55117,7 @@
         <v>44498</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55190,7 +55190,7 @@
         <v>46128</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>46094</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55346,7 +55346,7 @@
         <v>46106</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>46106</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55502,7 +55502,7 @@
         <v>46106</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55580,7 +55580,7 @@
         <v>46132</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>46132</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>45614</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55809,7 +55809,7 @@
         <v>46132</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55887,7 +55887,7 @@
         <v>46133</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55965,7 +55965,7 @@
         <v>46133</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>45261</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56116,7 +56116,7 @@
         <v>46132</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56189,7 +56189,7 @@
         <v>46134</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>46134</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>46090</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>46134</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56501,7 +56501,7 @@
         <v>46134</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>46105</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>46203</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56735,7 +56735,7 @@
         <v>46134</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>46100</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56891,7 +56891,7 @@
         <v>46133</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45019</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>46134</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57120,7 +57120,7 @@
         <v>45915</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57198,7 +57198,7 @@
         <v>46105</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57276,7 +57276,7 @@
         <v>46029</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
         <v>44874</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57427,7 +57427,7 @@
         <v>45113</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>45070</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57573,7 +57573,7 @@
         <v>46107</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57651,7 +57651,7 @@
         <v>46106</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57729,7 +57729,7 @@
         <v>45950</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57802,7 +57802,7 @@
         <v>45686</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57880,7 +57880,7 @@
         <v>45026</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57953,7 +57953,7 @@
         <v>45945</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58026,7 +58026,7 @@
         <v>46206</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>46107</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58182,7 +58182,7 @@
         <v>45467</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>45702</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58333,7 +58333,7 @@
         <v>46207</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>46154</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58489,7 +58489,7 @@
         <v>44539</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58562,7 +58562,7 @@
         <v>45652</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58635,7 +58635,7 @@
         <v>44694</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58713,7 +58713,7 @@
         <v>44818</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58786,7 +58786,7 @@
         <v>44763</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58859,7 +58859,7 @@
         <v>46210</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>45540</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59010,7 +59010,7 @@
         <v>45757</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59083,7 +59083,7 @@
         <v>45757</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59156,7 +59156,7 @@
         <v>46213</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59234,7 +59234,7 @@
         <v>46217</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>45243</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59385,7 +59385,7 @@
         <v>44616</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59458,7 +59458,7 @@
         <v>46213</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59536,7 +59536,7 @@
         <v>46217</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>45735</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45106</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59755,7 +59755,7 @@
         <v>46220</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>45014</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>44790</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>45699</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60052,7 +60052,7 @@
         <v>46273</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>46273</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>46273</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60286,7 +60286,7 @@
         <v>45373</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         <v>44885</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>46273</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60510,7 +60510,7 @@
         <v>45282</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>46273</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60661,7 +60661,7 @@
         <v>46272</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60734,7 +60734,7 @@
         <v>46272</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>46273</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60885,7 +60885,7 @@
         <v>46272</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>46274</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>45107</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61114,7 +61114,7 @@
         <v>46275</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61192,7 +61192,7 @@
         <v>46275</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61270,7 +61270,7 @@
         <v>46274</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61348,7 +61348,7 @@
         <v>45082</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>46274</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45034</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61577,7 +61577,7 @@
         <v>46276</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61655,7 +61655,7 @@
         <v>44973</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61728,7 +61728,7 @@
         <v>46276</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61806,7 +61806,7 @@
         <v>45397</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61884,7 +61884,7 @@
         <v>44800</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61957,7 +61957,7 @@
         <v>46276</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62035,7 +62035,7 @@
         <v>46279</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62108,7 +62108,7 @@
         <v>46276</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62186,7 +62186,7 @@
         <v>46279</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62264,7 +62264,7 @@
         <v>46280</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62342,7 +62342,7 @@
         <v>46280</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62420,7 +62420,7 @@
         <v>46280</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62498,7 +62498,7 @@
         <v>46280</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62576,7 +62576,7 @@
         <v>46280</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62654,7 +62654,7 @@
         <v>46281</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62732,7 +62732,7 @@
         <v>46280</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62810,7 +62810,7 @@
         <v>46280</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62888,7 +62888,7 @@
         <v>45266</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62961,7 +62961,7 @@
         <v>46281</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63039,7 +63039,7 @@
         <v>45414</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63112,7 +63112,7 @@
         <v>46280</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63190,7 +63190,7 @@
         <v>46282</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>44922</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63341,7 +63341,7 @@
         <v>46239</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63419,7 +63419,7 @@
         <v>45631</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>45715</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>46283</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63648,7 +63648,7 @@
         <v>46282</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63726,7 +63726,7 @@
         <v>45266</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63799,7 +63799,7 @@
         <v>46239</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63877,7 +63877,7 @@
         <v>45660</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>46283</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64028,7 +64028,7 @@
         <v>46283</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64106,7 +64106,7 @@
         <v>46283</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64184,7 +64184,7 @@
         <v>45519</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>46283</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64335,7 +64335,7 @@
         <v>46283</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64413,7 +64413,7 @@
         <v>45146</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64486,7 +64486,7 @@
         <v>46283</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64564,7 +64564,7 @@
         <v>46282</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64642,7 +64642,7 @@
         <v>46282</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64720,7 +64720,7 @@
         <v>44586</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64798,7 +64798,7 @@
         <v>45705</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64871,7 +64871,7 @@
         <v>46282</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64949,7 +64949,7 @@
         <v>46282</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65027,7 +65027,7 @@
         <v>46283</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65105,7 +65105,7 @@
         <v>46282</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65183,7 +65183,7 @@
         <v>46283</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65261,7 +65261,7 @@
         <v>46283</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65339,7 +65339,7 @@
         <v>45530</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65412,7 +65412,7 @@
         <v>46283</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65490,7 +65490,7 @@
         <v>46283</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65568,7 +65568,7 @@
         <v>46283</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65646,7 +65646,7 @@
         <v>46283</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65724,7 +65724,7 @@
         <v>44927</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65797,7 +65797,7 @@
         <v>46283</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65875,7 +65875,7 @@
         <v>45574</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65953,7 +65953,7 @@
         <v>46286</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>46244</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66109,7 +66109,7 @@
         <v>46287</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66187,7 +66187,7 @@
         <v>45608</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66260,7 +66260,7 @@
         <v>46287</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66338,7 +66338,7 @@
         <v>44767</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66411,7 +66411,7 @@
         <v>46287</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66489,7 +66489,7 @@
         <v>46287</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66567,7 +66567,7 @@
         <v>44910</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66640,7 +66640,7 @@
         <v>46287</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66718,7 +66718,7 @@
         <v>45559</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66791,7 +66791,7 @@
         <v>46244</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66869,7 +66869,7 @@
         <v>46244</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66947,7 +66947,7 @@
         <v>46287</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67025,7 +67025,7 @@
         <v>45530</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67103,7 +67103,7 @@
         <v>46246</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67176,7 +67176,7 @@
         <v>45751</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67254,7 +67254,7 @@
         <v>46246</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>46246</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -67410,7 +67410,7 @@
         <v>46289</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -67488,7 +67488,7 @@
         <v>46246</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67566,7 +67566,7 @@
         <v>46246</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67644,7 +67644,7 @@
         <v>45334</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67717,7 +67717,7 @@
         <v>45392</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67790,7 +67790,7 @@
         <v>46289</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67868,7 +67868,7 @@
         <v>46289</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67941,7 +67941,7 @@
         <v>46246</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68014,7 +68014,7 @@
         <v>45089</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68087,7 +68087,7 @@
         <v>46246</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68165,7 +68165,7 @@
         <v>46288</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -68243,7 +68243,7 @@
         <v>46248</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -68316,7 +68316,7 @@
         <v>46248</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -68389,7 +68389,7 @@
         <v>44603</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -68462,7 +68462,7 @@
         <v>45176</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68535,7 +68535,7 @@
         <v>45176</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68608,7 +68608,7 @@
         <v>44959</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68681,7 +68681,7 @@
         <v>45819</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68759,7 +68759,7 @@
         <v>46248</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68837,7 +68837,7 @@
         <v>46293</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68915,7 +68915,7 @@
         <v>46185</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68993,7 +68993,7 @@
         <v>45685</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69066,7 +69066,7 @@
         <v>46293</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69144,7 +69144,7 @@
         <v>46248</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -69222,7 +69222,7 @@
         <v>46290</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -69300,7 +69300,7 @@
         <v>45660</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -69373,7 +69373,7 @@
         <v>46290</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -69451,7 +69451,7 @@
         <v>45240</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -69524,7 +69524,7 @@
         <v>46290</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69602,7 +69602,7 @@
         <v>46290</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69680,7 +69680,7 @@
         <v>46293</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69758,7 +69758,7 @@
         <v>46290</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69836,7 +69836,7 @@
         <v>46293</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69914,7 +69914,7 @@
         <v>45520</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69987,7 +69987,7 @@
         <v>45520</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70060,7 +70060,7 @@
         <v>45089</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70138,7 +70138,7 @@
         <v>44973</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70211,7 +70211,7 @@
         <v>46169</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -70284,7 +70284,7 @@
         <v>46295</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -70362,7 +70362,7 @@
         <v>46295</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -70440,7 +70440,7 @@
         <v>46251</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -70518,7 +70518,7 @@
         <v>45232</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70596,7 +70596,7 @@
         <v>45749</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70669,7 +70669,7 @@
         <v>46295</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70747,7 +70747,7 @@
         <v>46252</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70820,7 +70820,7 @@
         <v>45090</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70893,7 +70893,7 @@
         <v>45014</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70966,7 +70966,7 @@
         <v>45728</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71039,7 +71039,7 @@
         <v>45306</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71112,7 +71112,7 @@
         <v>46104</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71185,7 +71185,7 @@
         <v>46161</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -71263,7 +71263,7 @@
         <v>46294</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -71341,7 +71341,7 @@
         <v>46297</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -71419,7 +71419,7 @@
         <v>46297</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -71497,7 +71497,7 @@
         <v>46297</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>45272</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71648,7 +71648,7 @@
         <v>46254</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71726,7 +71726,7 @@
         <v>46185</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71804,7 +71804,7 @@
         <v>45523</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71877,7 +71877,7 @@
         <v>46296</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71955,7 +71955,7 @@
         <v>46063</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72033,7 +72033,7 @@
         <v>45967</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72111,7 +72111,7 @@
         <v>46254</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72189,7 +72189,7 @@
         <v>46297</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72267,7 +72267,7 @@
         <v>46297</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -72345,7 +72345,7 @@
         <v>46297</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -72423,7 +72423,7 @@
         <v>46297</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -72501,7 +72501,7 @@
         <v>45944</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -72579,7 +72579,7 @@
         <v>45967</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72657,7 +72657,7 @@
         <v>46258</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>46258</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72808,7 +72808,7 @@
         <v>46178</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72886,7 +72886,7 @@
         <v>45987</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72964,7 +72964,7 @@
         <v>46185</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73042,7 +73042,7 @@
         <v>45776</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73115,7 +73115,7 @@
         <v>46301</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73193,7 +73193,7 @@
         <v>45580</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73271,7 +73271,7 @@
         <v>46255</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -73349,7 +73349,7 @@
         <v>46301</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -73427,7 +73427,7 @@
         <v>46300</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -73505,7 +73505,7 @@
         <v>45782</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -73578,7 +73578,7 @@
         <v>46147</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73656,7 +73656,7 @@
         <v>46210</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73734,7 +73734,7 @@
         <v>46094</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73812,7 +73812,7 @@
         <v>46281</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73885,7 +73885,7 @@
         <v>45702</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73963,7 +73963,7 @@
         <v>46147</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -74041,7 +74041,7 @@
         <v>46181</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -74119,7 +74119,7 @@
         <v>45252</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -74192,7 +74192,7 @@
         <v>46280</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -74270,7 +74270,7 @@
         <v>46301</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -74348,7 +74348,7 @@
         <v>46255</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -74426,7 +74426,7 @@
         <v>46255</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -74499,7 +74499,7 @@
         <v>45705</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -74577,7 +74577,7 @@
         <v>46084</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -74655,7 +74655,7 @@
         <v>46094</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74733,7 +74733,7 @@
         <v>45420</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74811,7 +74811,7 @@
         <v>45791</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74889,7 +74889,7 @@
         <v>45791</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74962,7 +74962,7 @@
         <v>45790</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -75035,7 +75035,7 @@
         <v>46100</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -75113,7 +75113,7 @@
         <v>45791</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -75186,7 +75186,7 @@
         <v>46093</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -75264,7 +75264,7 @@
         <v>46296</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -75342,7 +75342,7 @@
         <v>45790</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -75415,7 +75415,7 @@
         <v>46260</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -75488,7 +75488,7 @@
         <v>45660</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -75566,7 +75566,7 @@
         <v>46304</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -75644,7 +75644,7 @@
         <v>46261</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75722,7 +75722,7 @@
         <v>46304</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75800,7 +75800,7 @@
         <v>46262</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75873,7 +75873,7 @@
         <v>46262</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75951,7 +75951,7 @@
         <v>46304</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -76029,7 +76029,7 @@
         <v>46262</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -76107,7 +76107,7 @@
         <v>46261</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -76185,7 +76185,7 @@
         <v>46304</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -76263,7 +76263,7 @@
         <v>45797</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -76336,7 +76336,7 @@
         <v>46261</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -76414,7 +76414,7 @@
         <v>46261</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -76492,7 +76492,7 @@
         <v>45623</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -76565,7 +76565,7 @@
         <v>46304</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -76643,7 +76643,7 @@
         <v>46303</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -76716,7 +76716,7 @@
         <v>45933</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76794,7 +76794,7 @@
         <v>46262</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76872,7 +76872,7 @@
         <v>46304</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76950,7 +76950,7 @@
         <v>45594</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -77028,7 +77028,7 @@
         <v>45797</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -77101,7 +77101,7 @@
         <v>45632</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -77174,7 +77174,7 @@
         <v>45505</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -77247,7 +77247,7 @@
         <v>45798</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -77320,7 +77320,7 @@
         <v>46304</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -77398,7 +77398,7 @@
         <v>46304</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -77476,7 +77476,7 @@
         <v>46304</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -77554,7 +77554,7 @@
         <v>46308</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -77627,7 +77627,7 @@
         <v>46308</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -77705,7 +77705,7 @@
         <v>46308</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77783,7 +77783,7 @@
         <v>44739</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77856,7 +77856,7 @@
         <v>46309</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77929,7 +77929,7 @@
         <v>46265</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -78002,7 +78002,7 @@
         <v>46265</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -78080,7 +78080,7 @@
         <v>45804</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -78158,7 +78158,7 @@
         <v>45813</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -78231,7 +78231,7 @@
         <v>46269</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -78309,7 +78309,7 @@
         <v>45813</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -78382,7 +78382,7 @@
         <v>46269</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -78460,7 +78460,7 @@
         <v>45817</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -78533,7 +78533,7 @@
         <v>46267</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -78611,7 +78611,7 @@
         <v>46269</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -78689,7 +78689,7 @@
         <v>45819</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -78762,7 +78762,7 @@
         <v>46223</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78840,7 +78840,7 @@
         <v>46267</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78918,7 +78918,7 @@
         <v>46267</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78996,7 +78996,7 @@
         <v>46267</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -79074,7 +79074,7 @@
         <v>46267</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -79152,7 +79152,7 @@
         <v>46269</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -79230,7 +79230,7 @@
         <v>45827</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -79303,7 +79303,7 @@
         <v>45827</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -79376,7 +79376,7 @@
         <v>45741</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -79449,7 +79449,7 @@
         <v>45827</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -79522,7 +79522,7 @@
         <v>45827</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -79595,7 +79595,7 @@
         <v>45832</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -79668,7 +79668,7 @@
         <v>45834</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -79741,7 +79741,7 @@
         <v>45835</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -79814,7 +79814,7 @@
         <v>45784</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -79887,7 +79887,7 @@
         <v>45845</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -79960,7 +79960,7 @@
         <v>45845</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -80033,7 +80033,7 @@
         <v>45848</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -80106,7 +80106,7 @@
         <v>45848</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -80179,7 +80179,7 @@
         <v>45540</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -80252,7 +80252,7 @@
         <v>45854</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -80325,7 +80325,7 @@
         <v>45859</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -80403,7 +80403,7 @@
         <v>45862</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -80476,7 +80476,7 @@
         <v>45862</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -80554,7 +80554,7 @@
         <v>45862</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -80627,7 +80627,7 @@
         <v>45866</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -80705,7 +80705,7 @@
         <v>45867</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -80778,7 +80778,7 @@
         <v>45869</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -80851,7 +80851,7 @@
         <v>45869</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -80924,7 +80924,7 @@
         <v>45873</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -81002,7 +81002,7 @@
         <v>45545</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -81080,7 +81080,7 @@
         <v>45740</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -81158,7 +81158,7 @@
         <v>45205</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -81251,7 +81251,7 @@
         <v>44995</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -81329,7 +81329,7 @@
         <v>45376</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -81407,7 +81407,7 @@
         <v>45470</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -81485,7 +81485,7 @@
         <v>46089</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -601,7 +601,7 @@
         <v>45741</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46014</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>45966</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44588</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45019</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>46135</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>46079</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45623</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45842</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45302</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45825</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45982</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45926</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45926</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>45848</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45107</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45741</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45315</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>45638</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46089</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45324</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45898</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>45614</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45693</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>46041</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>46052</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45302</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>46282</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45281</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>46136</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>46174</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>46304</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>45715</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>46107</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>46176</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>46076</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>45398</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>45420</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>46279</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46293</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>46254</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>45825</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44876</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45107</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45737</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>46139</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45903</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>44887</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>45420</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45281</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>46101</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>46119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>46153</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45943</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>46169</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>45994</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45338</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>46185</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>46094</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>46199</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>46134</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>46280</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>46254</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>45533</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>46185</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>46100</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>46093</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45792</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45699</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44658</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44959</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44959</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45530</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>45120</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45645</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45015</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>44790</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44840</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>46101</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45884</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>46101</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>46101</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45719</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>46141</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>46101</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>45820</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>46153</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>45938</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>45272</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>46157</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45967</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         <v>45604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>45984</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45379</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45720</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44999</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>45440</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45631</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>46185</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>46185</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>46185</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45943</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>46097</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>46197</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>46094</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>46217</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>46274</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>46283</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>46282</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>46185</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44811</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>46287</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>46290</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>46290</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>46252</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>46294</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>46251</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45728</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45386</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>46119</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45420</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>46255</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>46093</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>46160</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>46133</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>46259</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>45805</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45973</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>46265</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>45588</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>45730</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>46311</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>46267</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45827</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45726</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44585</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45680</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>45562</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>46113</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44749</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44519</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44775</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44886</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>44629</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>44805</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44494</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44735</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44775</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44663</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>44573</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44882</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>44756</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>44813</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>44671</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>44671</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>44599</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>44735</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>44658</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>44776</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44571</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>44788</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>44589</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>44498</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>44796</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>44785</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>44599</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>44845</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>44840</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44785</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>44734</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44684</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>44795</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>44491</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45706</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>44585</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>44889</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>45014</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45454</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>44959</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>45611</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45699</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44637</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45040</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45660</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>44656</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45726</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45646</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45547</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45089</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45706</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45158</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45158</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45265</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>44708</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45104</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>44862</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45715</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>44840</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>44942</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>44691</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45184</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45324</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45117</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>44756</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>44756</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45084</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45125</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44539</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44693</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>44867</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45632</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45162</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45719</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44733</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45645</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45540</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45652</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>44988</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>45726</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45030</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44589</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45468</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45530</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45475</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45146</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>45324</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45261</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45672</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45034</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45463</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>44951</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>44935</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>44960</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45720</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>45084</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>44823</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>44533</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>45356</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>44517</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45681</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>46094</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45862</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>46031</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45744</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>45884</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45905</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45526</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45593</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>46106</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>46077</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>46107</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45468</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>46105</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45744</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45245</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46070</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46065</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44684</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>46107</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>46105</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45884</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>46069</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45891</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45895</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45895</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45161</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>45665</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45896</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45113</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26687,7 +26687,7 @@
         <v>45882</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45869</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45897</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>44735</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45223</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>46100</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         <v>45715</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>45898</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45898</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>44600</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>46106</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44693</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27598,7 +27598,7 @@
         <v>45749</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>46140</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>46030</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45898</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45898</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>46077</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>46111</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>46111</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45401</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>45898</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>45898</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>46108</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45898</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>46141</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45485</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>46033</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>46141</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45454</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45595</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>45902</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>45742</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45705</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>45905</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45784</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>44585</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45909</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45909</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>45909</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45909</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>46141</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>46141</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45911</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>45908</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>46142</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>44735</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>45915</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44701</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>45511</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>46045</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>45630</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>46147</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45888</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45923</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45896</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>46146</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>46101</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>46108</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>45924</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>45924</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44684</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45926</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45926</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>45926</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44694</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>45931</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>45931</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>46153</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45930</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45930</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45932</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45933</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45933</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>45932</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45932</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>45933</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45138</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45168</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>44951</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
         <v>44951</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>45937</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>46153</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>45938</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>45939</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45916</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45939</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45940</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>44904</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>44962</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45660</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33595,7 +33595,7 @@
         <v>45943</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>46155</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45944</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46119</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>46105</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45817</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>44942</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>46155</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45586</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45440</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45203</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>45632</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45526</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45666</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>46155</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45952</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45953</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45436</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>46105</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>45957</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>46101</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>45120</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>46154</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45957</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>46107</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>46107</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45312</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>45960</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45645</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45964</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45965</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45282</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>46106</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>45967</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45672</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>46105</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>46107</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>46155</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45965</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45971</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45645</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>45422</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>45162</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45968</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45973</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46163</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45058</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>45973</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45973</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>45974</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45974</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44586</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45974</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45974</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>45974</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>45974</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45974</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>45974</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45974</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45978</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>45978</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>45658</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38306,7 +38306,7 @@
         <v>44518</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
         <v>45084</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45978</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44756</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45547</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>46167</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>44936</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>44911</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45600</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45649</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45912</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45912</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45922</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>45922</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45922</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45922</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45922</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>45912</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45985</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45912</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>45922</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45922</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45922</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45922</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45922</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>45912</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>45320</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>46169</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>46169</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>45992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>45993</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>46169</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45992</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>46169</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>46168</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>45994</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45995</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>46169</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>45995</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>46168</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>45968</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>45120</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45995</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>46168</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>46031</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>45574</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>46000</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45312</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>46170</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>46002</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>46002</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>46002</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45257</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46173</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>46006</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>44651</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>45182</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>46008</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>45757</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45539</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45660</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         <v>45855</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>46019</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45967</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>45932</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45932</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43284,7 +43284,7 @@
         <v>46019</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43357,7 +43357,7 @@
         <v>45908</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45937</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45937</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>45908</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45931</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>45932</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>46022</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>46176</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45673</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45673</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>46030</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>45646</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>46030</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>44853</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>46176</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>46034</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>46141</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>44841</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>46041</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>46177</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45330</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>46178</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>46177</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>46045</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>46045</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45217</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>44616</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>46052</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>44876</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>46052</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>46052</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>44546</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>46056</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>46056</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>46056</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>46058</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>46058</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>46183</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>46063</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>46062</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>46062</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>44488</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>46183</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>46184</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>46065</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44519</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>46069</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>46185</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>46185</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>46185</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>46185</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>46185</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>46185</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>46069</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>46071</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>46185</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>46072</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>46185</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47696,7 +47696,7 @@
         <v>46188</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47774,7 +47774,7 @@
         <v>46185</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>46072</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>46185</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>46185</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>46185</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>46185</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>45090</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48315,7 +48315,7 @@
         <v>46076</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44936</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>46077</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48544,7 +48544,7 @@
         <v>46188</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>46188</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>46185</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>46185</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>46079</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45312</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>46185</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>46185</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>46185</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>45218</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>46083</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>45412</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>46085</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>46085</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>45595</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>46092</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45282</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>45282</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45282</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49986,7 +49986,7 @@
         <v>46092</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>46092</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>46132</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>46094</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>46094</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>46094</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>46094</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>46094</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>46094</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>46094</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50761,7 +50761,7 @@
         <v>46094</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>46093</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>46094</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>46095</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>46196</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51146,7 +51146,7 @@
         <v>46196</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>46098</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>45182</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>46099</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>44804</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51531,7 +51531,7 @@
         <v>44845</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>46100</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51682,7 +51682,7 @@
         <v>46196</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>46196</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>46104</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51916,7 +51916,7 @@
         <v>46101</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51994,7 +51994,7 @@
         <v>46104</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52067,7 +52067,7 @@
         <v>45644</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52145,7 +52145,7 @@
         <v>45644</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>46106</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>46195</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>46106</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>46105</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>44713</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45245</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52686,7 +52686,7 @@
         <v>46160</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45400</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52837,7 +52837,7 @@
         <v>46198</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>46198</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52993,7 +52993,7 @@
         <v>46198</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53071,7 +53071,7 @@
         <v>46108</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53149,7 +53149,7 @@
         <v>46197</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53227,7 +53227,7 @@
         <v>46198</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53305,7 +53305,7 @@
         <v>46198</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53383,7 +53383,7 @@
         <v>46111</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>46198</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>46198</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53617,7 +53617,7 @@
         <v>46198</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53695,7 +53695,7 @@
         <v>44910</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53768,7 +53768,7 @@
         <v>46120</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53841,7 +53841,7 @@
         <v>46202</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53919,7 +53919,7 @@
         <v>45462</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53992,7 +53992,7 @@
         <v>45660</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45660</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54138,7 +54138,7 @@
         <v>46202</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54216,7 +54216,7 @@
         <v>46122</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54294,7 +54294,7 @@
         <v>44741</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54367,7 +54367,7 @@
         <v>46077</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54445,7 +54445,7 @@
         <v>46125</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54518,7 +54518,7 @@
         <v>46125</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54591,7 +54591,7 @@
         <v>46124</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>46124</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54737,7 +54737,7 @@
         <v>46124</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54810,7 +54810,7 @@
         <v>46128</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>46106</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54966,7 +54966,7 @@
         <v>45350</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55039,7 +55039,7 @@
         <v>46104</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55117,7 +55117,7 @@
         <v>44498</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55190,7 +55190,7 @@
         <v>46128</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55268,7 +55268,7 @@
         <v>46094</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55346,7 +55346,7 @@
         <v>46106</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>46106</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55502,7 +55502,7 @@
         <v>46106</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55580,7 +55580,7 @@
         <v>46132</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
         <v>46132</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>45614</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55809,7 +55809,7 @@
         <v>46132</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55887,7 +55887,7 @@
         <v>46133</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55965,7 +55965,7 @@
         <v>46133</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>45261</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56116,7 +56116,7 @@
         <v>46132</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56189,7 +56189,7 @@
         <v>46134</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>46134</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>46090</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>46134</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56501,7 +56501,7 @@
         <v>46134</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>46105</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>46203</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56735,7 +56735,7 @@
         <v>46134</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>46100</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56891,7 +56891,7 @@
         <v>46133</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>45019</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57042,7 +57042,7 @@
         <v>46134</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57120,7 +57120,7 @@
         <v>45915</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57198,7 +57198,7 @@
         <v>46105</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57276,7 +57276,7 @@
         <v>46029</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
         <v>44874</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57427,7 +57427,7 @@
         <v>45113</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>45070</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57573,7 +57573,7 @@
         <v>46107</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57651,7 +57651,7 @@
         <v>46106</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57729,7 +57729,7 @@
         <v>45950</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57802,7 +57802,7 @@
         <v>45686</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57880,7 +57880,7 @@
         <v>45026</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57953,7 +57953,7 @@
         <v>45945</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58026,7 +58026,7 @@
         <v>46206</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>46107</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58182,7 +58182,7 @@
         <v>45467</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>45702</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58333,7 +58333,7 @@
         <v>46207</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>46154</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58489,7 +58489,7 @@
         <v>44539</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58562,7 +58562,7 @@
         <v>45652</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58635,7 +58635,7 @@
         <v>44694</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58713,7 +58713,7 @@
         <v>44818</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58786,7 +58786,7 @@
         <v>44763</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58859,7 +58859,7 @@
         <v>46210</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>45540</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59010,7 +59010,7 @@
         <v>45757</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59083,7 +59083,7 @@
         <v>45757</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59156,7 +59156,7 @@
         <v>46213</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59234,7 +59234,7 @@
         <v>46217</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59312,7 +59312,7 @@
         <v>45243</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59385,7 +59385,7 @@
         <v>44616</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59458,7 +59458,7 @@
         <v>46213</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59536,7 +59536,7 @@
         <v>46217</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>45735</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45106</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59755,7 +59755,7 @@
         <v>46220</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>45014</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>44790</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>45699</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60052,7 +60052,7 @@
         <v>46273</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>46273</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>46273</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60286,7 +60286,7 @@
         <v>45373</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         <v>44885</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>46273</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60510,7 +60510,7 @@
         <v>45282</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>46273</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60661,7 +60661,7 @@
         <v>46272</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60734,7 +60734,7 @@
         <v>46272</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>46273</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60885,7 +60885,7 @@
         <v>46272</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>46274</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>45107</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61114,7 +61114,7 @@
         <v>46275</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61192,7 +61192,7 @@
         <v>46275</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61270,7 +61270,7 @@
         <v>46274</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61348,7 +61348,7 @@
         <v>45082</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>46274</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61499,7 +61499,7 @@
         <v>45034</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61577,7 +61577,7 @@
         <v>46276</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61655,7 +61655,7 @@
         <v>44973</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61728,7 +61728,7 @@
         <v>46276</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61806,7 +61806,7 @@
         <v>45397</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61884,7 +61884,7 @@
         <v>44800</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61957,7 +61957,7 @@
         <v>46276</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62035,7 +62035,7 @@
         <v>46279</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62108,7 +62108,7 @@
         <v>46276</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62186,7 +62186,7 @@
         <v>46279</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62264,7 +62264,7 @@
         <v>46280</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62342,7 +62342,7 @@
         <v>46280</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62420,7 +62420,7 @@
         <v>46280</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62498,7 +62498,7 @@
         <v>46280</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62576,7 +62576,7 @@
         <v>46280</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62654,7 +62654,7 @@
         <v>46281</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62732,7 +62732,7 @@
         <v>46280</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62810,7 +62810,7 @@
         <v>46280</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62888,7 +62888,7 @@
         <v>45266</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62961,7 +62961,7 @@
         <v>46281</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63039,7 +63039,7 @@
         <v>45414</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63112,7 +63112,7 @@
         <v>46280</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63190,7 +63190,7 @@
         <v>46282</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>44922</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63341,7 +63341,7 @@
         <v>46239</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63419,7 +63419,7 @@
         <v>45631</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>45715</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63570,7 +63570,7 @@
         <v>46283</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63648,7 +63648,7 @@
         <v>46282</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63726,7 +63726,7 @@
         <v>45266</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63799,7 +63799,7 @@
         <v>46239</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63877,7 +63877,7 @@
         <v>45660</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>46283</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64028,7 +64028,7 @@
         <v>46283</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64106,7 +64106,7 @@
         <v>46283</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64184,7 +64184,7 @@
         <v>45519</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>46283</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64335,7 +64335,7 @@
         <v>46283</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64413,7 +64413,7 @@
         <v>45146</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64486,7 +64486,7 @@
         <v>46283</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64564,7 +64564,7 @@
         <v>46282</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64642,7 +64642,7 @@
         <v>46282</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64720,7 +64720,7 @@
         <v>44586</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64798,7 +64798,7 @@
         <v>45705</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64871,7 +64871,7 @@
         <v>46282</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64949,7 +64949,7 @@
         <v>46282</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65027,7 +65027,7 @@
         <v>46283</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65105,7 +65105,7 @@
         <v>46282</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65183,7 +65183,7 @@
         <v>46283</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65261,7 +65261,7 @@
         <v>46283</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65339,7 +65339,7 @@
         <v>45530</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65412,7 +65412,7 @@
         <v>46283</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65490,7 +65490,7 @@
         <v>46283</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65568,7 +65568,7 @@
         <v>46283</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65646,7 +65646,7 @@
         <v>46283</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65724,7 +65724,7 @@
         <v>44927</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65797,7 +65797,7 @@
         <v>46283</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65875,7 +65875,7 @@
         <v>45574</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65953,7 +65953,7 @@
         <v>46286</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>46244</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66109,7 +66109,7 @@
         <v>46287</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66187,7 +66187,7 @@
         <v>45608</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66260,7 +66260,7 @@
         <v>46287</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66338,7 +66338,7 @@
         <v>44767</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66411,7 +66411,7 @@
         <v>46287</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66489,7 +66489,7 @@
         <v>46287</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66567,7 +66567,7 @@
         <v>44910</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66640,7 +66640,7 @@
         <v>46287</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66718,7 +66718,7 @@
         <v>45559</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66791,7 +66791,7 @@
         <v>46244</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66869,7 +66869,7 @@
         <v>46244</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66947,7 +66947,7 @@
         <v>46287</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67025,7 +67025,7 @@
         <v>45530</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67103,7 +67103,7 @@
         <v>46246</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67176,7 +67176,7 @@
         <v>45751</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67254,7 +67254,7 @@
         <v>46246</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>46246</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -67410,7 +67410,7 @@
         <v>46289</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -67488,7 +67488,7 @@
         <v>46246</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67566,7 +67566,7 @@
         <v>46246</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67644,7 +67644,7 @@
         <v>45334</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67717,7 +67717,7 @@
         <v>45392</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67790,7 +67790,7 @@
         <v>46289</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -67868,7 +67868,7 @@
         <v>46289</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -67941,7 +67941,7 @@
         <v>46246</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68014,7 +68014,7 @@
         <v>45089</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68087,7 +68087,7 @@
         <v>46246</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68165,7 +68165,7 @@
         <v>46288</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -68243,7 +68243,7 @@
         <v>46248</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -68316,7 +68316,7 @@
         <v>46248</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -68389,7 +68389,7 @@
         <v>44603</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -68462,7 +68462,7 @@
         <v>45176</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68535,7 +68535,7 @@
         <v>45176</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68608,7 +68608,7 @@
         <v>44959</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68681,7 +68681,7 @@
         <v>45819</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68759,7 +68759,7 @@
         <v>46248</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -68837,7 +68837,7 @@
         <v>46293</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -68915,7 +68915,7 @@
         <v>46185</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -68993,7 +68993,7 @@
         <v>45685</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69066,7 +69066,7 @@
         <v>46293</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69144,7 +69144,7 @@
         <v>46248</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -69222,7 +69222,7 @@
         <v>46290</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -69300,7 +69300,7 @@
         <v>45660</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -69373,7 +69373,7 @@
         <v>46290</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -69451,7 +69451,7 @@
         <v>45240</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -69524,7 +69524,7 @@
         <v>46290</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69602,7 +69602,7 @@
         <v>46290</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69680,7 +69680,7 @@
         <v>46293</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69758,7 +69758,7 @@
         <v>46290</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -69836,7 +69836,7 @@
         <v>46293</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -69914,7 +69914,7 @@
         <v>45520</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -69987,7 +69987,7 @@
         <v>45520</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70060,7 +70060,7 @@
         <v>45089</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70138,7 +70138,7 @@
         <v>44973</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70211,7 +70211,7 @@
         <v>46169</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -70284,7 +70284,7 @@
         <v>46295</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -70362,7 +70362,7 @@
         <v>46295</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -70440,7 +70440,7 @@
         <v>46251</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -70518,7 +70518,7 @@
         <v>45232</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70596,7 +70596,7 @@
         <v>45749</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70669,7 +70669,7 @@
         <v>46295</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70747,7 +70747,7 @@
         <v>46252</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -70820,7 +70820,7 @@
         <v>45090</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -70893,7 +70893,7 @@
         <v>45014</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -70966,7 +70966,7 @@
         <v>45728</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71039,7 +71039,7 @@
         <v>45306</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71112,7 +71112,7 @@
         <v>46104</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71185,7 +71185,7 @@
         <v>46161</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -71263,7 +71263,7 @@
         <v>46294</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -71341,7 +71341,7 @@
         <v>46297</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -71419,7 +71419,7 @@
         <v>46297</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -71497,7 +71497,7 @@
         <v>46297</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>45272</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71648,7 +71648,7 @@
         <v>46254</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71726,7 +71726,7 @@
         <v>46185</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -71804,7 +71804,7 @@
         <v>45523</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -71877,7 +71877,7 @@
         <v>46296</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -71955,7 +71955,7 @@
         <v>46063</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72033,7 +72033,7 @@
         <v>45967</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72111,7 +72111,7 @@
         <v>46254</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72189,7 +72189,7 @@
         <v>46297</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72267,7 +72267,7 @@
         <v>46297</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -72345,7 +72345,7 @@
         <v>46297</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -72423,7 +72423,7 @@
         <v>46297</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -72501,7 +72501,7 @@
         <v>45944</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -72579,7 +72579,7 @@
         <v>45967</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72657,7 +72657,7 @@
         <v>46258</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72735,7 +72735,7 @@
         <v>46258</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -72808,7 +72808,7 @@
         <v>46178</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -72886,7 +72886,7 @@
         <v>45987</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -72964,7 +72964,7 @@
         <v>46185</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73042,7 +73042,7 @@
         <v>45776</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73115,7 +73115,7 @@
         <v>46301</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73193,7 +73193,7 @@
         <v>45580</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73271,7 +73271,7 @@
         <v>46255</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -73349,7 +73349,7 @@
         <v>46301</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -73427,7 +73427,7 @@
         <v>46300</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -73505,7 +73505,7 @@
         <v>45782</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -73578,7 +73578,7 @@
         <v>46147</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73656,7 +73656,7 @@
         <v>46210</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73734,7 +73734,7 @@
         <v>46094</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73812,7 +73812,7 @@
         <v>46281</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -73885,7 +73885,7 @@
         <v>45702</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -73963,7 +73963,7 @@
         <v>46147</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -74041,7 +74041,7 @@
         <v>46181</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -74119,7 +74119,7 @@
         <v>45252</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -74192,7 +74192,7 @@
         <v>46280</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -74270,7 +74270,7 @@
         <v>46301</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -74348,7 +74348,7 @@
         <v>46255</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -74426,7 +74426,7 @@
         <v>46255</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -74499,7 +74499,7 @@
         <v>45705</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -74577,7 +74577,7 @@
         <v>46084</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -74655,7 +74655,7 @@
         <v>46094</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74733,7 +74733,7 @@
         <v>45420</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74811,7 +74811,7 @@
         <v>45791</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74889,7 +74889,7 @@
         <v>45791</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -74962,7 +74962,7 @@
         <v>45790</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -75035,7 +75035,7 @@
         <v>46100</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -75113,7 +75113,7 @@
         <v>45791</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -75186,7 +75186,7 @@
         <v>46093</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -75264,7 +75264,7 @@
         <v>46296</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -75342,7 +75342,7 @@
         <v>45790</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -75415,7 +75415,7 @@
         <v>46260</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -75488,7 +75488,7 @@
         <v>45660</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -75566,7 +75566,7 @@
         <v>46304</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -75644,7 +75644,7 @@
         <v>46261</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75722,7 +75722,7 @@
         <v>46304</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75800,7 +75800,7 @@
         <v>46262</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75873,7 +75873,7 @@
         <v>46262</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -75951,7 +75951,7 @@
         <v>46304</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -76029,7 +76029,7 @@
         <v>46262</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -76107,7 +76107,7 @@
         <v>46261</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -76185,7 +76185,7 @@
         <v>46304</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -76263,7 +76263,7 @@
         <v>45797</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -76336,7 +76336,7 @@
         <v>46261</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -76414,7 +76414,7 @@
         <v>46261</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -76492,7 +76492,7 @@
         <v>45623</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -76565,7 +76565,7 @@
         <v>46304</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -76643,7 +76643,7 @@
         <v>46303</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -76716,7 +76716,7 @@
         <v>45933</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76794,7 +76794,7 @@
         <v>46262</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76872,7 +76872,7 @@
         <v>46304</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76950,7 +76950,7 @@
         <v>45594</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -77028,7 +77028,7 @@
         <v>45797</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -77101,7 +77101,7 @@
         <v>45632</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -77174,7 +77174,7 @@
         <v>45505</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -77247,7 +77247,7 @@
         <v>45798</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -77320,7 +77320,7 @@
         <v>46304</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -77398,7 +77398,7 @@
         <v>46304</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -77476,7 +77476,7 @@
         <v>46304</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -77554,7 +77554,7 @@
         <v>46308</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -77627,7 +77627,7 @@
         <v>46308</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -77705,7 +77705,7 @@
         <v>46308</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77783,7 +77783,7 @@
         <v>44739</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77856,7 +77856,7 @@
         <v>46309</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77929,7 +77929,7 @@
         <v>46265</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -78002,7 +78002,7 @@
         <v>46265</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -78080,7 +78080,7 @@
         <v>45804</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -78158,7 +78158,7 @@
         <v>45813</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -78231,7 +78231,7 @@
         <v>46269</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -78309,7 +78309,7 @@
         <v>45813</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -78382,7 +78382,7 @@
         <v>46269</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -78460,7 +78460,7 @@
         <v>45817</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -78533,7 +78533,7 @@
         <v>46267</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -78611,7 +78611,7 @@
         <v>46269</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -78689,7 +78689,7 @@
         <v>45819</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -78762,7 +78762,7 @@
         <v>46223</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78840,7 +78840,7 @@
         <v>46267</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78918,7 +78918,7 @@
         <v>46267</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78996,7 +78996,7 @@
         <v>46267</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -79074,7 +79074,7 @@
         <v>46267</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -79152,7 +79152,7 @@
         <v>46269</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -79230,7 +79230,7 @@
         <v>45827</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -79303,7 +79303,7 @@
         <v>45827</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -79376,7 +79376,7 @@
         <v>45741</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -79449,7 +79449,7 @@
         <v>45827</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -79522,7 +79522,7 @@
         <v>45827</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -79595,7 +79595,7 @@
         <v>45832</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -79668,7 +79668,7 @@
         <v>45834</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -79741,7 +79741,7 @@
         <v>45835</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -79814,7 +79814,7 @@
         <v>45784</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -79887,7 +79887,7 @@
         <v>45845</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -79960,7 +79960,7 @@
         <v>45845</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -80033,7 +80033,7 @@
         <v>45848</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -80106,7 +80106,7 @@
         <v>45848</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -80179,7 +80179,7 @@
         <v>45540</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -80252,7 +80252,7 @@
         <v>45854</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -80325,7 +80325,7 @@
         <v>45859</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -80403,7 +80403,7 @@
         <v>45862</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -80476,7 +80476,7 @@
         <v>45862</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -80554,7 +80554,7 @@
         <v>45862</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -80627,7 +80627,7 @@
         <v>45866</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -80705,7 +80705,7 @@
         <v>45867</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -80778,7 +80778,7 @@
         <v>45869</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -80851,7 +80851,7 @@
         <v>45869</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -80924,7 +80924,7 @@
         <v>45873</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -81002,7 +81002,7 @@
         <v>45545</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -81080,7 +81080,7 @@
         <v>45740</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -81158,7 +81158,7 @@
         <v>45205</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -81251,7 +81251,7 @@
         <v>44995</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -81329,7 +81329,7 @@
         <v>45376</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -81407,7 +81407,7 @@
         <v>45470</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -81485,7 +81485,7 @@
         <v>46089</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -601,7 +601,7 @@
         <v>45741</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46014</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>45966</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44588</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45019</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>46135</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45623</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45842</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>45593</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45825</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45302</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45982</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45926</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45926</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>45848</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45107</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45315</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>45638</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46089</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45898</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45281</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45614</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>46282</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>46041</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46052</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>46174</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>46136</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>46304</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45693</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45324</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>45302</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>45898</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>46176</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45398</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46293</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>46076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>45825</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>46254</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>46107</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>45420</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>46279</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44876</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45107</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45898</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>45338</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>46169</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>45943</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>46185</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>45512</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>46199</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>45281</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>45994</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>46280</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>45792</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>46185</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>46254</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>46100</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>46093</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>46134</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>46139</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>46101</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>46153</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>46119</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45420</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>44887</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>45737</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45533</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45699</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44658</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>45386</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45884</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>46157</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>45820</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>45938</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45272</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>45379</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>46185</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>46185</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>46185</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45967</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>46197</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>45530</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>45984</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46217</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>44999</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>46282</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>46283</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>46287</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>46185</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45588</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>46290</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45730</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>46290</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>46294</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>46251</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>46252</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45827</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45943</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>46093</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>46160</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>46119</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>46255</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>46133</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>46097</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>45120</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45420</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45973</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>46259</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>45805</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45726</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>46265</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>46094</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>46267</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>46311</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>46101</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>44735</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>46101</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>46101</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45604</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45719</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>46274</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>46141</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>46101</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>46153</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>45015</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45645</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>45728</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>44840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45720</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44959</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>44959</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45440</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45631</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>44790</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>44811</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>44585</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45680</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45562</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>46113</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>44519</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44749</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>44775</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>44886</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>44629</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>44805</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>44494</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>44735</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>44775</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>44663</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44573</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44882</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44756</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>44813</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>44671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>44671</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44599</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44735</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>44658</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>44776</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>44571</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>44788</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>44589</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>44498</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44796</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>44785</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44599</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44845</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>44840</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44785</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>44734</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>44684</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44795</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>44693</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45715</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>45715</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45665</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45891</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>45158</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>45158</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44862</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>45895</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>44656</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45895</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45467</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45896</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45397</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45898</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45898</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45898</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45898</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45897</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44694</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45898</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45882</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45898</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>45898</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45232</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45902</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45884</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45485</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44651</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45749</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>45261</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44616</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45905</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>44962</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45909</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45909</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>45908</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45909</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45909</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45312</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45422</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>46107</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>44927</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>45125</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45282</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>46163</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>46168</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>46167</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45888</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>46168</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44616</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>45924</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>45923</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45896</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45146</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45924</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45926</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>46168</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>46169</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>46169</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>46169</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>45926</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45926</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45138</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         <v>46169</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45034</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>46169</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45930</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45930</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>45932</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45932</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45120</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>46173</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>46170</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45931</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>45931</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>45932</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45933</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>44942</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>45933</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45933</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45400</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44804</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45938</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45436</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>45937</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45916</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45939</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45940</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>45939</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45162</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45943</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>45944</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46177</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>46177</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>46141</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>46176</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45608</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>46176</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44876</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45706</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>44841</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45373</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45817</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44951</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45454</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45574</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45468</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>46178</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45559</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44840</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45084</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45454</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45952</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>46183</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44539</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45953</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>46183</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45240</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>46185</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>46185</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         <v>46185</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>46185</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45957</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44733</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>46185</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>46185</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>46185</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>46185</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>46184</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45957</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45217</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>46185</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>46185</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>46185</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>45593</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45257</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>45632</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29891,7 +29891,7 @@
         <v>46185</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>45960</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>46185</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>46185</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>46185</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>46185</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45182</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>46185</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>46185</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45964</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>46188</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>46188</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>45965</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>46188</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>46132</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>45965</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45967</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45968</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>46195</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45649</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45971</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>46198</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45645</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>45974</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>45974</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>46198</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>45974</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>45974</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>46196</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45974</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>46197</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>46196</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>46196</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>46160</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>46196</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45974</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>44498</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45973</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45974</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45974</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45974</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45973</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45973</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>44818</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>46198</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45978</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45978</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>46198</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>46198</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>46198</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>45978</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45168</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46198</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>46198</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>46202</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>46202</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>45699</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>46203</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45749</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>44756</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>46206</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>45985</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45950</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45922</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45912</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>45912</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45922</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45922</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>46106</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>46154</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>45922</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45922</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45912</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>45912</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>45720</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>45922</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45922</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>46207</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45922</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45912</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>45922</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45922</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>45992</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>46210</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46213</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45992</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>46213</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45993</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>44823</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45468</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45994</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45995</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45530</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46217</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>46217</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45968</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45266</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45312</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45995</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37483,7 +37483,7 @@
         <v>46000</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>46220</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45440</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45266</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>45660</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45595</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45580</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>46002</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>46002</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45776</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>46002</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45782</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>46006</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45252</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>46008</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45705</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>46280</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>46280</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45702</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>46280</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>46280</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>46279</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>46280</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>46280</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>46280</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>46280</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>46281</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>46019</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45967</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45931</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>46239</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>46282</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>46282</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45937</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
         <v>46282</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45855</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>46019</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>45908</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>45932</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40425,7 +40425,7 @@
         <v>45932</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45937</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>45908</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>46282</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>46282</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>46022</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45790</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45932</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>46239</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>45790</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45660</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>46282</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>46030</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>46281</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>46282</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45791</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>46283</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>46030</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>46283</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41857,7 +41857,7 @@
         <v>46283</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>46283</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>46283</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>46034</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>46286</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45791</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46283</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45791</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>46283</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>46283</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>46283</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45594</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>46283</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>46283</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>46283</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>46283</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>46283</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>46283</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45623</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43324,7 +43324,7 @@
         <v>46287</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>46287</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
         <v>46041</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>45632</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>46288</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>46244</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>45797</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45798</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>45797</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45505</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>46045</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>46287</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>46287</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>46244</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>46244</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>46045</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>46287</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>46287</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>46185</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>46246</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>46246</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>44739</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>46052</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>46052</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>45804</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>46246</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>46052</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>46246</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>46290</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>46290</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>46289</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>46246</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>46246</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>46246</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>46289</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>46290</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45819</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>46056</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>46056</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>46056</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>46289</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>46290</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>46290</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>46058</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>46058</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>46293</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>46062</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>46062</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>46294</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>46248</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47134,7 +47134,7 @@
         <v>46248</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
         <v>46063</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         <v>44533</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45813</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47436,7 +47436,7 @@
         <v>45813</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>46169</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>46248</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>46065</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>46248</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>46293</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>46104</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>46161</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>46069</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>46293</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>46069</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>46293</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>45817</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
         <v>46071</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45819</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>46072</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>46072</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46076</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>46077</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>46296</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>46251</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>46079</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45741</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>46083</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49268,7 +49268,7 @@
         <v>45827</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45827</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49414,7 +49414,7 @@
         <v>45827</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>45827</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>46295</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>46295</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49716,7 +49716,7 @@
         <v>46252</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>46295</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45832</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45967</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45944</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50096,7 +50096,7 @@
         <v>46085</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>46085</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>45834</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>46255</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45987</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50476,7 +50476,7 @@
         <v>46300</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45835</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>46185</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50705,7 +50705,7 @@
         <v>46094</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45967</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50861,7 +50861,7 @@
         <v>46093</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50939,7 +50939,7 @@
         <v>46092</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>46297</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51095,7 +51095,7 @@
         <v>46092</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
         <v>46063</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>46147</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51329,7 +51329,7 @@
         <v>46297</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>46297</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>46092</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>46254</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>46094</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>46094</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>46094</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>46094</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51953,7 +51953,7 @@
         <v>46095</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52026,7 +52026,7 @@
         <v>46094</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>46094</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52182,7 +52182,7 @@
         <v>46280</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>46254</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52338,7 +52338,7 @@
         <v>46094</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52416,7 +52416,7 @@
         <v>46181</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>46185</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>46094</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>46255</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>46255</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>46094</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>44942</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>46297</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>46297</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>45530</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>46098</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53259,7 +53259,7 @@
         <v>46099</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>46147</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>46101</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53493,7 +53493,7 @@
         <v>46297</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>46297</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>46100</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53727,7 +53727,7 @@
         <v>45845</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45784</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53873,7 +53873,7 @@
         <v>45845</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>46210</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54024,7 +54024,7 @@
         <v>46178</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>46296</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>46104</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54253,7 +54253,7 @@
         <v>45848</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54326,7 +54326,7 @@
         <v>46105</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54404,7 +54404,7 @@
         <v>46104</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45848</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45540</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>46106</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>46106</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54784,7 +54784,7 @@
         <v>46258</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54857,7 +54857,7 @@
         <v>45854</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>45586</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>46111</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>46281</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>46108</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55232,7 +55232,7 @@
         <v>46301</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>46301</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55388,7 +55388,7 @@
         <v>45859</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55466,7 +55466,7 @@
         <v>46258</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>45862</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
         <v>45862</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>46301</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55773,7 +55773,7 @@
         <v>44936</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>45862</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>46304</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>46084</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56075,7 +56075,7 @@
         <v>46304</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>46304</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         <v>46303</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>46261</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56382,7 +56382,7 @@
         <v>44845</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45866</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>45867</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56606,7 +56606,7 @@
         <v>45420</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45511</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56762,7 +56762,7 @@
         <v>45869</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56835,7 +56835,7 @@
         <v>46077</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56913,7 +56913,7 @@
         <v>46100</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56991,7 +56991,7 @@
         <v>45869</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>46260</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>46304</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57215,7 +57215,7 @@
         <v>45658</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>46304</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57366,7 +57366,7 @@
         <v>46120</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>46124</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>46124</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>46261</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>46261</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57741,7 +57741,7 @@
         <v>46122</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45644</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57897,7 +57897,7 @@
         <v>46124</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>46125</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58043,7 +58043,7 @@
         <v>46125</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58116,7 +58116,7 @@
         <v>46304</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58194,7 +58194,7 @@
         <v>46261</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58272,7 +58272,7 @@
         <v>46106</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>46106</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58428,7 +58428,7 @@
         <v>45873</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58506,7 +58506,7 @@
         <v>46093</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58584,7 +58584,7 @@
         <v>46304</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58662,7 +58662,7 @@
         <v>46106</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58740,7 +58740,7 @@
         <v>46094</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58818,7 +58818,7 @@
         <v>46304</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58896,7 +58896,7 @@
         <v>46104</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58974,7 +58974,7 @@
         <v>46304</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59052,7 +59052,7 @@
         <v>46132</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59130,7 +59130,7 @@
         <v>46265</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59208,7 +59208,7 @@
         <v>45933</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>46106</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59364,7 +59364,7 @@
         <v>46128</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59442,7 +59442,7 @@
         <v>46132</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59515,7 +59515,7 @@
         <v>46132</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59593,7 +59593,7 @@
         <v>45545</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>46308</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59749,7 +59749,7 @@
         <v>46128</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59827,7 +59827,7 @@
         <v>46262</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>46262</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>46132</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>45740</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45540</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>46265</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>45475</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>46133</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>45884</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60514,7 +60514,7 @@
         <v>46105</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60592,7 +60592,7 @@
         <v>46133</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>46133</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         <v>45540</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>46308</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>46100</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>46134</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>46134</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61133,7 +61133,7 @@
         <v>46094</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61211,7 +61211,7 @@
         <v>46134</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61289,7 +61289,7 @@
         <v>46262</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61362,7 +61362,7 @@
         <v>46134</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>46100</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61518,7 +61518,7 @@
         <v>44889</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61596,7 +61596,7 @@
         <v>46308</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>44517</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>45915</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61825,7 +61825,7 @@
         <v>46262</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61903,7 +61903,7 @@
         <v>44988</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61981,7 +61981,7 @@
         <v>46134</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>46134</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62137,7 +62137,7 @@
         <v>46090</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62215,7 +62215,7 @@
         <v>44585</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>46309</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62361,7 +62361,7 @@
         <v>46267</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62439,7 +62439,7 @@
         <v>46107</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62517,7 +62517,7 @@
         <v>46267</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62595,7 +62595,7 @@
         <v>46267</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>46267</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>45869</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62824,7 +62824,7 @@
         <v>46267</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45862</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62975,7 +62975,7 @@
         <v>44600</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63053,7 +63053,7 @@
         <v>45726</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63126,7 +63126,7 @@
         <v>46077</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63199,7 +63199,7 @@
         <v>45742</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63272,7 +63272,7 @@
         <v>46106</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>46106</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63428,7 +63428,7 @@
         <v>46269</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63506,7 +63506,7 @@
         <v>46108</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63584,7 +63584,7 @@
         <v>45547</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63662,7 +63662,7 @@
         <v>46094</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45744</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63818,7 +63818,7 @@
         <v>46107</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63896,7 +63896,7 @@
         <v>46269</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63974,7 +63974,7 @@
         <v>46140</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64047,7 +64047,7 @@
         <v>46105</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64125,7 +64125,7 @@
         <v>46105</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64203,7 +64203,7 @@
         <v>46107</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64281,7 +64281,7 @@
         <v>46107</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64359,7 +64359,7 @@
         <v>46069</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>46269</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64510,7 +64510,7 @@
         <v>44959</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64583,7 +64583,7 @@
         <v>44693</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64661,7 +64661,7 @@
         <v>45223</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64734,7 +64734,7 @@
         <v>45686</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64812,7 +64812,7 @@
         <v>46314</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64890,7 +64890,7 @@
         <v>46223</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64968,7 +64968,7 @@
         <v>45705</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65041,7 +65041,7 @@
         <v>45784</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65114,7 +65114,7 @@
         <v>46269</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65192,7 +65192,7 @@
         <v>46314</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65270,7 +65270,7 @@
         <v>46070</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65343,7 +65343,7 @@
         <v>46314</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65421,7 +65421,7 @@
         <v>46077</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65499,7 +65499,7 @@
         <v>46316</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65572,7 +65572,7 @@
         <v>46315</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65650,7 +65650,7 @@
         <v>46029</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65723,7 +65723,7 @@
         <v>45945</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65796,7 +65796,7 @@
         <v>45030</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65874,7 +65874,7 @@
         <v>45019</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65947,7 +65947,7 @@
         <v>46273</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66025,7 +66025,7 @@
         <v>46273</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66103,7 +66103,7 @@
         <v>46105</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66181,7 +66181,7 @@
         <v>46273</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45905</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66337,7 +66337,7 @@
         <v>46273</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66415,7 +66415,7 @@
         <v>46272</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66488,7 +66488,7 @@
         <v>46272</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66561,7 +66561,7 @@
         <v>45652</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66634,7 +66634,7 @@
         <v>44691</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66707,7 +66707,7 @@
         <v>46273</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66785,7 +66785,7 @@
         <v>46031</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66858,7 +66858,7 @@
         <v>45040</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66936,7 +66936,7 @@
         <v>46315</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67009,7 +67009,7 @@
         <v>45744</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67087,7 +67087,7 @@
         <v>46031</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67160,7 +67160,7 @@
         <v>46273</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67238,7 +67238,7 @@
         <v>46314</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67316,7 +67316,7 @@
         <v>46033</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>46065</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67462,7 +67462,7 @@
         <v>45595</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -67535,7 +67535,7 @@
         <v>46318</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -67613,7 +67613,7 @@
         <v>46274</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -67691,7 +67691,7 @@
         <v>46318</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67769,7 +67769,7 @@
         <v>46141</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67847,7 +67847,7 @@
         <v>46141</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67925,7 +67925,7 @@
         <v>46279</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67998,7 +67998,7 @@
         <v>44951</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68076,7 +68076,7 @@
         <v>46030</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -68149,7 +68149,7 @@
         <v>44951</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68227,7 +68227,7 @@
         <v>46276</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68305,7 +68305,7 @@
         <v>46111</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68383,7 +68383,7 @@
         <v>46111</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -68461,7 +68461,7 @@
         <v>46141</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -68539,7 +68539,7 @@
         <v>45324</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -68612,7 +68612,7 @@
         <v>45282</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -68685,7 +68685,7 @@
         <v>45282</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68758,7 +68758,7 @@
         <v>46318</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68836,7 +68836,7 @@
         <v>46274</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68914,7 +68914,7 @@
         <v>46274</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68992,7 +68992,7 @@
         <v>46276</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -69070,7 +69070,7 @@
         <v>46141</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -69148,7 +69148,7 @@
         <v>46142</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -69226,7 +69226,7 @@
         <v>44713</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69304,7 +69304,7 @@
         <v>45330</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69377,7 +69377,7 @@
         <v>46276</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -69455,7 +69455,7 @@
         <v>46045</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -69528,7 +69528,7 @@
         <v>46276</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -69606,7 +69606,7 @@
         <v>46272</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -69684,7 +69684,7 @@
         <v>46275</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -69762,7 +69762,7 @@
         <v>46275</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69840,7 +69840,7 @@
         <v>46146</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69918,7 +69918,7 @@
         <v>46108</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69996,7 +69996,7 @@
         <v>46147</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -70074,7 +70074,7 @@
         <v>46101</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -70152,7 +70152,7 @@
         <v>44708</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -70225,7 +70225,7 @@
         <v>45699</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70298,7 +70298,7 @@
         <v>45082</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70371,7 +70371,7 @@
         <v>46101</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70449,7 +70449,7 @@
         <v>46154</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -70527,7 +70527,7 @@
         <v>45462</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -70600,7 +70600,7 @@
         <v>46153</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -70678,7 +70678,7 @@
         <v>45463</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -70756,7 +70756,7 @@
         <v>46153</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70829,7 +70829,7 @@
         <v>45614</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70902,7 +70902,7 @@
         <v>46155</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70975,7 +70975,7 @@
         <v>46155</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -71048,7 +71048,7 @@
         <v>46119</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -71121,7 +71121,7 @@
         <v>46105</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -71199,7 +71199,7 @@
         <v>46155</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71277,7 +71277,7 @@
         <v>46105</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71355,7 +71355,7 @@
         <v>45034</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71428,7 +71428,7 @@
         <v>46155</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -71506,7 +71506,7 @@
         <v>46105</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -71584,7 +71584,7 @@
         <v>46107</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -71662,7 +71662,7 @@
         <v>46106</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -71740,7 +71740,7 @@
         <v>46107</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71818,7 +71818,7 @@
         <v>45089</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71891,7 +71891,7 @@
         <v>44936</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71964,7 +71964,7 @@
         <v>44518</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -72037,7 +72037,7 @@
         <v>45084</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -72110,7 +72110,7 @@
         <v>45631</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -72188,7 +72188,7 @@
         <v>44922</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72261,7 +72261,7 @@
         <v>45089</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72334,7 +72334,7 @@
         <v>45014</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72407,7 +72407,7 @@
         <v>45113</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72485,7 +72485,7 @@
         <v>45630</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -72558,7 +72558,7 @@
         <v>45184</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -72631,7 +72631,7 @@
         <v>44694</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -72709,7 +72709,7 @@
         <v>45632</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -72782,7 +72782,7 @@
         <v>45660</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72855,7 +72855,7 @@
         <v>44756</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72928,7 +72928,7 @@
         <v>44756</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -73001,7 +73001,7 @@
         <v>45014</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -73074,7 +73074,7 @@
         <v>45652</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -73147,7 +73147,7 @@
         <v>45530</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73225,7 +73225,7 @@
         <v>45089</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73303,7 +73303,7 @@
         <v>45685</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73376,7 +73376,7 @@
         <v>45660</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73449,7 +73449,7 @@
         <v>45660</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -73522,7 +73522,7 @@
         <v>45176</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -73595,7 +73595,7 @@
         <v>45176</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -73668,7 +73668,7 @@
         <v>45681</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -73746,7 +73746,7 @@
         <v>45350</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73819,7 +73819,7 @@
         <v>44973</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73892,7 +73892,7 @@
         <v>44589</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73970,7 +73970,7 @@
         <v>45243</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -74043,7 +74043,7 @@
         <v>44539</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -74116,7 +74116,7 @@
         <v>45026</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -74189,7 +74189,7 @@
         <v>45245</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -74262,7 +74262,7 @@
         <v>45320</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -74335,7 +74335,7 @@
         <v>45014</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -74408,7 +74408,7 @@
         <v>45706</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -74481,7 +74481,7 @@
         <v>45203</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -74554,7 +74554,7 @@
         <v>45070</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -74627,7 +74627,7 @@
         <v>45757</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -74700,7 +74700,7 @@
         <v>45757</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -74773,7 +74773,7 @@
         <v>45090</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74846,7 +74846,7 @@
         <v>45757</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74919,7 +74919,7 @@
         <v>45272</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74992,7 +74992,7 @@
         <v>44874</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -75070,7 +75070,7 @@
         <v>44867</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -75143,7 +75143,7 @@
         <v>45334</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -75216,7 +75216,7 @@
         <v>45107</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -75289,7 +75289,7 @@
         <v>45526</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -75362,7 +75362,7 @@
         <v>45645</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -75440,7 +75440,7 @@
         <v>45672</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -75518,7 +75518,7 @@
         <v>45660</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -75591,7 +75591,7 @@
         <v>45660</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -75664,7 +75664,7 @@
         <v>45117</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -75742,7 +75742,7 @@
         <v>44935</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75815,7 +75815,7 @@
         <v>45113</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75888,7 +75888,7 @@
         <v>45162</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75961,7 +75961,7 @@
         <v>45600</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -76034,7 +76034,7 @@
         <v>45519</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -76107,7 +76107,7 @@
         <v>45539</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -76180,7 +76180,7 @@
         <v>44910</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -76253,7 +76253,7 @@
         <v>44910</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -76326,7 +76326,7 @@
         <v>44885</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -76399,7 +76399,7 @@
         <v>45306</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -76472,7 +76472,7 @@
         <v>45161</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -76550,7 +76550,7 @@
         <v>44546</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -76628,7 +76628,7 @@
         <v>45414</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -76701,7 +76701,7 @@
         <v>45412</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -76774,7 +76774,7 @@
         <v>45120</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76847,7 +76847,7 @@
         <v>44637</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76920,7 +76920,7 @@
         <v>45719</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76993,7 +76993,7 @@
         <v>45324</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -77066,7 +77066,7 @@
         <v>45182</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -77144,7 +77144,7 @@
         <v>44585</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -77217,7 +77217,7 @@
         <v>45146</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -77290,7 +77290,7 @@
         <v>45106</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -77363,7 +77363,7 @@
         <v>45523</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -77436,7 +77436,7 @@
         <v>45660</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -77509,7 +77509,7 @@
         <v>45644</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -77587,7 +77587,7 @@
         <v>45104</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -77665,7 +77665,7 @@
         <v>45702</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -77738,7 +77738,7 @@
         <v>44763</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77811,7 +77811,7 @@
         <v>45058</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77884,7 +77884,7 @@
         <v>45356</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77957,7 +77957,7 @@
         <v>44586</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -78035,7 +78035,7 @@
         <v>45646</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -78108,7 +78108,7 @@
         <v>45735</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -78181,7 +78181,7 @@
         <v>45547</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -78254,7 +78254,7 @@
         <v>45673</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -78327,7 +78327,7 @@
         <v>45673</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -78400,7 +78400,7 @@
         <v>44684</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -78478,7 +78478,7 @@
         <v>45728</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -78551,7 +78551,7 @@
         <v>45084</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -78624,7 +78624,7 @@
         <v>45705</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -78697,7 +78697,7 @@
         <v>45090</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -78770,7 +78770,7 @@
         <v>44684</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78848,7 +78848,7 @@
         <v>45218</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78921,7 +78921,7 @@
         <v>44586</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78999,7 +78999,7 @@
         <v>45666</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -79072,7 +79072,7 @@
         <v>45245</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -79150,7 +79150,7 @@
         <v>44790</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -79223,7 +79223,7 @@
         <v>44735</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -79296,7 +79296,7 @@
         <v>44701</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -79374,7 +79374,7 @@
         <v>44741</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -79447,7 +79447,7 @@
         <v>44800</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -79520,7 +79520,7 @@
         <v>44904</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -79598,7 +79598,7 @@
         <v>45265</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -79671,7 +79671,7 @@
         <v>44767</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -79744,7 +79744,7 @@
         <v>45715</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -79817,7 +79817,7 @@
         <v>45261</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -79890,7 +79890,7 @@
         <v>45312</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -79963,7 +79963,7 @@
         <v>45751</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -80041,7 +80041,7 @@
         <v>45282</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -80114,7 +80114,7 @@
         <v>45282</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -80187,7 +80187,7 @@
         <v>45392</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -80260,7 +80260,7 @@
         <v>45401</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -80333,7 +80333,7 @@
         <v>45526</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -80411,7 +80411,7 @@
         <v>45645</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -80484,7 +80484,7 @@
         <v>45574</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -80562,7 +80562,7 @@
         <v>44853</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -80635,7 +80635,7 @@
         <v>45520</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -80708,7 +80708,7 @@
         <v>45520</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -80781,7 +80781,7 @@
         <v>45726</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -80854,7 +80854,7 @@
         <v>45646</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -80927,7 +80927,7 @@
         <v>45611</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -81000,7 +81000,7 @@
         <v>44519</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -81073,7 +81073,7 @@
         <v>44603</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -81146,7 +81146,7 @@
         <v>44973</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -81219,7 +81219,7 @@
         <v>44959</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -81292,7 +81292,7 @@
         <v>44911</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -81365,7 +81365,7 @@
         <v>44735</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -81438,7 +81438,7 @@
         <v>44960</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -81516,7 +81516,7 @@
         <v>45205</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -81609,7 +81609,7 @@
         <v>44995</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -81687,7 +81687,7 @@
         <v>45376</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -81765,7 +81765,7 @@
         <v>45470</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -81843,7 +81843,7 @@
         <v>46089</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -601,7 +601,7 @@
         <v>45741</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46014</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>45966</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>44588</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>45019</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>46079</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>46135</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>45623</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46052</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45842</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>45593</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45825</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45302</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45982</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45926</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45926</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>45848</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45741</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45107</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45315</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>45638</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46089</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45898</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45281</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45614</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>46282</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>46041</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46052</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>46174</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>46136</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>46304</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45693</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45324</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>45302</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>45898</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>46176</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>45398</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46293</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>46076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>45825</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>46254</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>46107</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>45420</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>46279</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44876</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45107</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45898</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>45338</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>46169</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>45943</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>46185</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>45512</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>46199</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>45281</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>45994</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>46280</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>45792</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>46185</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>46254</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>46100</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>46093</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>46134</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>46139</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>46101</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>46153</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>46119</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45420</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>44887</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>45737</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45533</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45699</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44658</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>45386</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45884</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>46157</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>45820</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>45938</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45272</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>45379</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>46185</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>46185</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>46185</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>45967</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>46197</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>45530</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>45984</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>46217</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>44999</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>46282</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>46283</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>46287</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>46185</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45588</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>46290</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45730</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>46290</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>46294</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>46251</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>46252</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45827</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45943</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>46093</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>46160</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>46119</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>46255</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>46133</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>46097</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>45120</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45420</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45973</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>46259</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>45805</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45726</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>46265</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>46094</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>46267</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>46311</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>46101</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>44735</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>46101</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>46101</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45604</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45719</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>46274</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>46141</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>46101</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>46153</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>45015</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45645</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>45728</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>44840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45720</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44959</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>44959</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45440</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45631</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>44790</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>44811</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>44585</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45680</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45562</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>46113</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>44519</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44749</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>44775</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>44886</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>44629</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>44805</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>44494</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>44735</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>44775</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>44663</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44573</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>44882</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44756</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>44813</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>44671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>44671</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>44599</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>44735</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>44658</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>44776</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>44571</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>44788</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>44589</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>44498</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44796</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>44785</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44599</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44845</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>44840</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44785</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>44734</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>44684</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44795</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>44693</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45715</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>45715</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45665</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45891</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>45158</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>45158</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>44862</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>45895</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>44656</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45895</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45467</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45896</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45397</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45898</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45898</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45898</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45898</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45897</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44694</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45898</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45882</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45898</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>45898</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45232</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45902</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45884</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45485</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44651</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45749</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>45261</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44616</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45905</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>44962</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45909</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45909</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>45908</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45909</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45909</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45312</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45422</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>46107</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>44927</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>45125</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45282</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>46163</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>46168</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>46167</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45888</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>46168</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44616</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>45924</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>45923</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45896</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45146</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45924</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45926</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>46168</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>46169</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>46169</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>46169</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>45926</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45926</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45138</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         <v>46169</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45034</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>46169</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>45930</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45930</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>45932</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45932</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45120</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>46173</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>46170</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45931</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>45931</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>45932</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45933</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>44942</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>45933</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45933</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45400</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44804</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45938</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45436</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>45937</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45916</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45939</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45940</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>45939</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45162</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45943</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>45944</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46177</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>46177</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>46141</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>46176</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45608</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>46176</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44876</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45706</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>44841</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45373</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45817</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44951</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45454</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45574</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45468</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>46178</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45559</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44840</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45084</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45454</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45952</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>46183</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44539</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45953</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>46183</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45240</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>46185</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>46185</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         <v>46185</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>46185</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45957</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44733</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>46185</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>46185</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>46185</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         <v>46185</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>46184</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45957</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45217</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>46185</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>46185</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>46185</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>45593</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45257</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>45632</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29891,7 +29891,7 @@
         <v>46185</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>45960</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>46185</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>46185</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>46185</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>46185</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45182</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>46185</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>46185</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45964</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>46188</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>46188</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>45965</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>46188</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>46132</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>45965</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45967</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45968</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>46195</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45649</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45971</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>46198</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45645</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>45974</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>45974</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>46198</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>45974</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>45974</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>46196</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45974</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>46197</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>46196</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>46196</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>46160</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>46196</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45974</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>44498</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45973</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45974</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45974</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45974</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45973</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45973</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33195,7 +33195,7 @@
         <v>44818</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>46198</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45978</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45978</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>46198</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>46198</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>46198</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>45978</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45168</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46198</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>46198</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>46202</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>46202</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>45699</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>46203</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45749</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>44756</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>46206</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>45985</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45950</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45922</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45912</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>45912</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45922</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45922</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>46106</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>46154</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>45922</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45922</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45912</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>45912</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>45720</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>45922</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45922</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>46207</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45922</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45912</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>45922</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45922</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>45992</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>46210</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>46213</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45992</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>46213</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45993</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>44823</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45468</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45994</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45995</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45530</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46217</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>46217</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45968</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45266</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45312</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45995</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37483,7 +37483,7 @@
         <v>46000</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>46220</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45440</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45266</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>45660</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45595</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45580</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>46002</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>46002</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45776</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>46002</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45782</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>46006</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45252</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>46008</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45705</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>46280</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>46280</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45702</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38905,7 +38905,7 @@
         <v>46280</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>46280</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>46279</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>46280</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>46280</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>46280</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>46280</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>46281</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>46019</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45967</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45931</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>46239</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>46282</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>46282</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45937</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
         <v>46282</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45855</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>46019</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>45908</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>45932</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40425,7 +40425,7 @@
         <v>45932</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45937</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>45908</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>46282</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>46282</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>46022</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45790</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45932</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>46239</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>45790</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41170,7 +41170,7 @@
         <v>45660</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>46282</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>46030</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>46281</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>46282</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45791</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>46283</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>46030</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>46283</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41857,7 +41857,7 @@
         <v>46283</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>46283</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>46283</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>46034</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>46286</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45791</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>46283</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45791</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>46283</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>46283</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>46283</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45594</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>46283</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>46283</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>46283</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>46283</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>46283</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>46283</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45623</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43324,7 +43324,7 @@
         <v>46287</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>46287</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
         <v>46041</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>45632</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>46288</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>46244</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>45797</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45798</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>45797</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45505</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>46045</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>46287</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>46287</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44303,7 +44303,7 @@
         <v>46244</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>46244</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>46045</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>46287</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>46287</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>46185</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>46246</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>46246</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>44739</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>46052</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>46052</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>45804</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>46246</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>46052</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>46246</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>46290</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>46290</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>46289</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>46246</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>46246</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>46246</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>46289</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>46290</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45819</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>46056</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>46056</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>46056</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>46289</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>46290</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>46290</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>46058</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>46058</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>46293</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>46062</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>46062</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>46294</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>46248</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47134,7 +47134,7 @@
         <v>46248</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
         <v>46063</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         <v>44533</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45813</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47436,7 +47436,7 @@
         <v>45813</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>46169</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>46248</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>46065</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>46248</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>46293</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>46104</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>46161</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>46069</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>46293</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>46069</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>46293</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>45817</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
         <v>46071</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>45819</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>46072</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>46072</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46076</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>46077</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>46296</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>46251</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>46079</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45741</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>46083</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49268,7 +49268,7 @@
         <v>45827</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45827</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49414,7 +49414,7 @@
         <v>45827</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>45827</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>46295</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>46295</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49716,7 +49716,7 @@
         <v>46252</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>46295</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45832</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45967</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45944</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50096,7 +50096,7 @@
         <v>46085</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>46085</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>45834</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>46255</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45987</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50476,7 +50476,7 @@
         <v>46300</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45835</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>46185</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50705,7 +50705,7 @@
         <v>46094</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45967</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50861,7 +50861,7 @@
         <v>46093</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50939,7 +50939,7 @@
         <v>46092</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51017,7 +51017,7 @@
         <v>46297</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51095,7 +51095,7 @@
         <v>46092</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
         <v>46063</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>46147</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51329,7 +51329,7 @@
         <v>46297</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>46297</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>46092</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>46254</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51641,7 +51641,7 @@
         <v>46094</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>46094</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>46094</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51875,7 +51875,7 @@
         <v>46094</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51953,7 +51953,7 @@
         <v>46095</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52026,7 +52026,7 @@
         <v>46094</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>46094</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52182,7 +52182,7 @@
         <v>46280</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>46254</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52338,7 +52338,7 @@
         <v>46094</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52416,7 +52416,7 @@
         <v>46181</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>46185</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>46094</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>46255</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>46255</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>46094</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>44942</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>46297</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>46297</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>45530</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>46098</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53259,7 +53259,7 @@
         <v>46099</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>46147</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>46101</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53493,7 +53493,7 @@
         <v>46297</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>46297</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>46100</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53727,7 +53727,7 @@
         <v>45845</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45784</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53873,7 +53873,7 @@
         <v>45845</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>46210</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54024,7 +54024,7 @@
         <v>46178</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54102,7 +54102,7 @@
         <v>46296</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>46104</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54253,7 +54253,7 @@
         <v>45848</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54326,7 +54326,7 @@
         <v>46105</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54404,7 +54404,7 @@
         <v>46104</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54482,7 +54482,7 @@
         <v>45848</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45540</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54628,7 +54628,7 @@
         <v>46106</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>46106</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54784,7 +54784,7 @@
         <v>46258</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54857,7 +54857,7 @@
         <v>45854</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>45586</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>46111</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>46281</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55154,7 +55154,7 @@
         <v>46108</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55232,7 +55232,7 @@
         <v>46301</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>46301</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55388,7 +55388,7 @@
         <v>45859</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55466,7 +55466,7 @@
         <v>46258</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>45862</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
         <v>45862</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>46301</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55773,7 +55773,7 @@
         <v>44936</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>45862</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>46304</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>46084</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56075,7 +56075,7 @@
         <v>46304</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>46304</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         <v>46303</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>46261</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56382,7 +56382,7 @@
         <v>44845</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45866</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>45867</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56606,7 +56606,7 @@
         <v>45420</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>45511</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56762,7 +56762,7 @@
         <v>45869</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56835,7 +56835,7 @@
         <v>46077</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56913,7 +56913,7 @@
         <v>46100</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56991,7 +56991,7 @@
         <v>45869</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>46260</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>46304</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57215,7 +57215,7 @@
         <v>45658</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>46304</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57366,7 +57366,7 @@
         <v>46120</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>46124</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>46124</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>46261</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>46261</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57741,7 +57741,7 @@
         <v>46122</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45644</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57897,7 +57897,7 @@
         <v>46124</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>46125</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58043,7 +58043,7 @@
         <v>46125</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58116,7 +58116,7 @@
         <v>46304</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58194,7 +58194,7 @@
         <v>46261</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58272,7 +58272,7 @@
         <v>46106</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>46106</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58428,7 +58428,7 @@
         <v>45873</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58506,7 +58506,7 @@
         <v>46093</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58584,7 +58584,7 @@
         <v>46304</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58662,7 +58662,7 @@
         <v>46106</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58740,7 +58740,7 @@
         <v>46094</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58818,7 +58818,7 @@
         <v>46304</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58896,7 +58896,7 @@
         <v>46104</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58974,7 +58974,7 @@
         <v>46304</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59052,7 +59052,7 @@
         <v>46132</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59130,7 +59130,7 @@
         <v>46265</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59208,7 +59208,7 @@
         <v>45933</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>46106</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59364,7 +59364,7 @@
         <v>46128</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59442,7 +59442,7 @@
         <v>46132</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59515,7 +59515,7 @@
         <v>46132</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59593,7 +59593,7 @@
         <v>45545</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>46308</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59749,7 +59749,7 @@
         <v>46128</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59827,7 +59827,7 @@
         <v>46262</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>46262</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>46132</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>45740</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45540</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>46265</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>45475</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>46133</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>45884</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60514,7 +60514,7 @@
         <v>46105</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60592,7 +60592,7 @@
         <v>46133</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>46133</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         <v>45540</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>46308</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>46100</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60977,7 +60977,7 @@
         <v>46134</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>46134</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61133,7 +61133,7 @@
         <v>46094</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61211,7 +61211,7 @@
         <v>46134</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61289,7 +61289,7 @@
         <v>46262</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61362,7 +61362,7 @@
         <v>46134</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>46100</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61518,7 +61518,7 @@
         <v>44889</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61596,7 +61596,7 @@
         <v>46308</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>44517</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>45915</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61825,7 +61825,7 @@
         <v>46262</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61903,7 +61903,7 @@
         <v>44988</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61981,7 +61981,7 @@
         <v>46134</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -62059,7 +62059,7 @@
         <v>46134</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -62137,7 +62137,7 @@
         <v>46090</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -62215,7 +62215,7 @@
         <v>44585</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>46309</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62361,7 +62361,7 @@
         <v>46267</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62439,7 +62439,7 @@
         <v>46107</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62517,7 +62517,7 @@
         <v>46267</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62595,7 +62595,7 @@
         <v>46267</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>46267</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>45869</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62824,7 +62824,7 @@
         <v>46267</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45862</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62975,7 +62975,7 @@
         <v>44600</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -63053,7 +63053,7 @@
         <v>45726</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -63126,7 +63126,7 @@
         <v>46077</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -63199,7 +63199,7 @@
         <v>45742</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63272,7 +63272,7 @@
         <v>46106</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>46106</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63428,7 +63428,7 @@
         <v>46269</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63506,7 +63506,7 @@
         <v>46108</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63584,7 +63584,7 @@
         <v>45547</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63662,7 +63662,7 @@
         <v>46094</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45744</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63818,7 +63818,7 @@
         <v>46107</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63896,7 +63896,7 @@
         <v>46269</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63974,7 +63974,7 @@
         <v>46140</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -64047,7 +64047,7 @@
         <v>46105</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -64125,7 +64125,7 @@
         <v>46105</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -64203,7 +64203,7 @@
         <v>46107</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64281,7 +64281,7 @@
         <v>46107</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64359,7 +64359,7 @@
         <v>46069</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>46269</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64510,7 +64510,7 @@
         <v>44959</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64583,7 +64583,7 @@
         <v>44693</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64661,7 +64661,7 @@
         <v>45223</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64734,7 +64734,7 @@
         <v>45686</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64812,7 +64812,7 @@
         <v>46314</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64890,7 +64890,7 @@
         <v>46223</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64968,7 +64968,7 @@
         <v>45705</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -65041,7 +65041,7 @@
         <v>45784</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -65114,7 +65114,7 @@
         <v>46269</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -65192,7 +65192,7 @@
         <v>46314</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -65270,7 +65270,7 @@
         <v>46070</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65343,7 +65343,7 @@
         <v>46314</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65421,7 +65421,7 @@
         <v>46077</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65499,7 +65499,7 @@
         <v>46316</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65572,7 +65572,7 @@
         <v>46315</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65650,7 +65650,7 @@
         <v>46029</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65723,7 +65723,7 @@
         <v>45945</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65796,7 +65796,7 @@
         <v>45030</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65874,7 +65874,7 @@
         <v>45019</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65947,7 +65947,7 @@
         <v>46273</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -66025,7 +66025,7 @@
         <v>46273</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -66103,7 +66103,7 @@
         <v>46105</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -66181,7 +66181,7 @@
         <v>46273</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45905</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66337,7 +66337,7 @@
         <v>46273</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66415,7 +66415,7 @@
         <v>46272</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66488,7 +66488,7 @@
         <v>46272</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66561,7 +66561,7 @@
         <v>45652</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66634,7 +66634,7 @@
         <v>44691</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66707,7 +66707,7 @@
         <v>46273</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66785,7 +66785,7 @@
         <v>46031</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66858,7 +66858,7 @@
         <v>45040</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66936,7 +66936,7 @@
         <v>46315</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -67009,7 +67009,7 @@
         <v>45744</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -67087,7 +67087,7 @@
         <v>46031</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -67160,7 +67160,7 @@
         <v>46273</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -67238,7 +67238,7 @@
         <v>46314</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -67316,7 +67316,7 @@
         <v>46033</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>46065</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -67462,7 +67462,7 @@
         <v>45595</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -67535,7 +67535,7 @@
         <v>46318</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -67613,7 +67613,7 @@
         <v>46274</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -67691,7 +67691,7 @@
         <v>46318</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -67769,7 +67769,7 @@
         <v>46141</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -67847,7 +67847,7 @@
         <v>46141</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -67925,7 +67925,7 @@
         <v>46279</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -67998,7 +67998,7 @@
         <v>44951</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -68076,7 +68076,7 @@
         <v>46030</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -68149,7 +68149,7 @@
         <v>44951</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -68227,7 +68227,7 @@
         <v>46276</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -68305,7 +68305,7 @@
         <v>46111</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -68383,7 +68383,7 @@
         <v>46111</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -68461,7 +68461,7 @@
         <v>46141</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -68539,7 +68539,7 @@
         <v>45324</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -68612,7 +68612,7 @@
         <v>45282</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -68685,7 +68685,7 @@
         <v>45282</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -68758,7 +68758,7 @@
         <v>46318</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -68836,7 +68836,7 @@
         <v>46274</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -68914,7 +68914,7 @@
         <v>46274</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -68992,7 +68992,7 @@
         <v>46276</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -69070,7 +69070,7 @@
         <v>46141</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -69148,7 +69148,7 @@
         <v>46142</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -69226,7 +69226,7 @@
         <v>44713</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -69304,7 +69304,7 @@
         <v>45330</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -69377,7 +69377,7 @@
         <v>46276</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -69455,7 +69455,7 @@
         <v>46045</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -69528,7 +69528,7 @@
         <v>46276</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -69606,7 +69606,7 @@
         <v>46272</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -69684,7 +69684,7 @@
         <v>46275</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -69762,7 +69762,7 @@
         <v>46275</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -69840,7 +69840,7 @@
         <v>46146</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -69918,7 +69918,7 @@
         <v>46108</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -69996,7 +69996,7 @@
         <v>46147</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -70074,7 +70074,7 @@
         <v>46101</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -70152,7 +70152,7 @@
         <v>44708</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -70225,7 +70225,7 @@
         <v>45699</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -70298,7 +70298,7 @@
         <v>45082</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -70371,7 +70371,7 @@
         <v>46101</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -70449,7 +70449,7 @@
         <v>46154</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -70527,7 +70527,7 @@
         <v>45462</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -70600,7 +70600,7 @@
         <v>46153</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -70678,7 +70678,7 @@
         <v>45463</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -70756,7 +70756,7 @@
         <v>46153</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -70829,7 +70829,7 @@
         <v>45614</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -70902,7 +70902,7 @@
         <v>46155</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -70975,7 +70975,7 @@
         <v>46155</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -71048,7 +71048,7 @@
         <v>46119</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -71121,7 +71121,7 @@
         <v>46105</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -71199,7 +71199,7 @@
         <v>46155</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -71277,7 +71277,7 @@
         <v>46105</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -71355,7 +71355,7 @@
         <v>45034</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -71428,7 +71428,7 @@
         <v>46155</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -71506,7 +71506,7 @@
         <v>46105</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -71584,7 +71584,7 @@
         <v>46107</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -71662,7 +71662,7 @@
         <v>46106</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -71740,7 +71740,7 @@
         <v>46107</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -71818,7 +71818,7 @@
         <v>45089</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -71891,7 +71891,7 @@
         <v>44936</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -71964,7 +71964,7 @@
         <v>44518</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -72037,7 +72037,7 @@
         <v>45084</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -72110,7 +72110,7 @@
         <v>45631</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -72188,7 +72188,7 @@
         <v>44922</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -72261,7 +72261,7 @@
         <v>45089</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -72334,7 +72334,7 @@
         <v>45014</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -72407,7 +72407,7 @@
         <v>45113</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -72485,7 +72485,7 @@
         <v>45630</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -72558,7 +72558,7 @@
         <v>45184</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -72631,7 +72631,7 @@
         <v>44694</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -72709,7 +72709,7 @@
         <v>45632</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -72782,7 +72782,7 @@
         <v>45660</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -72855,7 +72855,7 @@
         <v>44756</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -72928,7 +72928,7 @@
         <v>44756</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -73001,7 +73001,7 @@
         <v>45014</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -73074,7 +73074,7 @@
         <v>45652</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -73147,7 +73147,7 @@
         <v>45530</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -73225,7 +73225,7 @@
         <v>45089</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -73303,7 +73303,7 @@
         <v>45685</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -73376,7 +73376,7 @@
         <v>45660</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -73449,7 +73449,7 @@
         <v>45660</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -73522,7 +73522,7 @@
         <v>45176</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -73595,7 +73595,7 @@
         <v>45176</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -73668,7 +73668,7 @@
         <v>45681</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -73746,7 +73746,7 @@
         <v>45350</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -73819,7 +73819,7 @@
         <v>44973</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -73892,7 +73892,7 @@
         <v>44589</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -73970,7 +73970,7 @@
         <v>45243</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -74043,7 +74043,7 @@
         <v>44539</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -74116,7 +74116,7 @@
         <v>45026</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -74189,7 +74189,7 @@
         <v>45245</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -74262,7 +74262,7 @@
         <v>45320</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -74335,7 +74335,7 @@
         <v>45014</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -74408,7 +74408,7 @@
         <v>45706</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -74481,7 +74481,7 @@
         <v>45203</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -74554,7 +74554,7 @@
         <v>45070</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -74627,7 +74627,7 @@
         <v>45757</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -74700,7 +74700,7 @@
         <v>45757</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -74773,7 +74773,7 @@
         <v>45090</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -74846,7 +74846,7 @@
         <v>45757</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -74919,7 +74919,7 @@
         <v>45272</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -74992,7 +74992,7 @@
         <v>44874</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -75070,7 +75070,7 @@
         <v>44867</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -75143,7 +75143,7 @@
         <v>45334</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -75216,7 +75216,7 @@
         <v>45107</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -75289,7 +75289,7 @@
         <v>45526</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -75362,7 +75362,7 @@
         <v>45645</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -75440,7 +75440,7 @@
         <v>45672</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -75518,7 +75518,7 @@
         <v>45660</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -75591,7 +75591,7 @@
         <v>45660</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -75664,7 +75664,7 @@
         <v>45117</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -75742,7 +75742,7 @@
         <v>44935</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -75815,7 +75815,7 @@
         <v>45113</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -75888,7 +75888,7 @@
         <v>45162</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -75961,7 +75961,7 @@
         <v>45600</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -76034,7 +76034,7 @@
         <v>45519</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -76107,7 +76107,7 @@
         <v>45539</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -76180,7 +76180,7 @@
         <v>44910</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -76253,7 +76253,7 @@
         <v>44910</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -76326,7 +76326,7 @@
         <v>44885</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -76399,7 +76399,7 @@
         <v>45306</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -76472,7 +76472,7 @@
         <v>45161</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -76550,7 +76550,7 @@
         <v>44546</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -76628,7 +76628,7 @@
         <v>45414</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -76701,7 +76701,7 @@
         <v>45412</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -76774,7 +76774,7 @@
         <v>45120</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -76847,7 +76847,7 @@
         <v>44637</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -76920,7 +76920,7 @@
         <v>45719</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -76993,7 +76993,7 @@
         <v>45324</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -77066,7 +77066,7 @@
         <v>45182</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -77144,7 +77144,7 @@
         <v>44585</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -77217,7 +77217,7 @@
         <v>45146</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -77290,7 +77290,7 @@
         <v>45106</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -77363,7 +77363,7 @@
         <v>45523</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -77436,7 +77436,7 @@
         <v>45660</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -77509,7 +77509,7 @@
         <v>45644</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -77587,7 +77587,7 @@
         <v>45104</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -77665,7 +77665,7 @@
         <v>45702</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -77738,7 +77738,7 @@
         <v>44763</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -77811,7 +77811,7 @@
         <v>45058</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -77884,7 +77884,7 @@
         <v>45356</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -77957,7 +77957,7 @@
         <v>44586</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -78035,7 +78035,7 @@
         <v>45646</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -78108,7 +78108,7 @@
         <v>45735</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -78181,7 +78181,7 @@
         <v>45547</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -78254,7 +78254,7 @@
         <v>45673</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -78327,7 +78327,7 @@
         <v>45673</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -78400,7 +78400,7 @@
         <v>44684</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -78478,7 +78478,7 @@
         <v>45728</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -78551,7 +78551,7 @@
         <v>45084</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -78624,7 +78624,7 @@
         <v>45705</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -78697,7 +78697,7 @@
         <v>45090</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -78770,7 +78770,7 @@
         <v>44684</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -78848,7 +78848,7 @@
         <v>45218</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -78921,7 +78921,7 @@
         <v>44586</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -78999,7 +78999,7 @@
         <v>45666</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -79072,7 +79072,7 @@
         <v>45245</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -79150,7 +79150,7 @@
         <v>44790</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -79223,7 +79223,7 @@
         <v>44735</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -79296,7 +79296,7 @@
         <v>44701</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -79374,7 +79374,7 @@
         <v>44741</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -79447,7 +79447,7 @@
         <v>44800</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -79520,7 +79520,7 @@
         <v>44904</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -79598,7 +79598,7 @@
         <v>45265</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -79671,7 +79671,7 @@
         <v>44767</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -79744,7 +79744,7 @@
         <v>45715</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -79817,7 +79817,7 @@
         <v>45261</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -79890,7 +79890,7 @@
         <v>45312</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -79963,7 +79963,7 @@
         <v>45751</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -80041,7 +80041,7 @@
         <v>45282</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -80114,7 +80114,7 @@
         <v>45282</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -80187,7 +80187,7 @@
         <v>45392</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -80260,7 +80260,7 @@
         <v>45401</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -80333,7 +80333,7 @@
         <v>45526</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -80411,7 +80411,7 @@
         <v>45645</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -80484,7 +80484,7 @@
         <v>45574</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -80562,7 +80562,7 @@
         <v>44853</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -80635,7 +80635,7 @@
         <v>45520</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -80708,7 +80708,7 @@
         <v>45520</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -80781,7 +80781,7 @@
         <v>45726</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -80854,7 +80854,7 @@
         <v>45646</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -80927,7 +80927,7 @@
         <v>45611</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -81000,7 +81000,7 @@
         <v>44519</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -81073,7 +81073,7 @@
         <v>44603</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -81146,7 +81146,7 @@
         <v>44973</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -81219,7 +81219,7 @@
         <v>44959</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -81292,7 +81292,7 @@
         <v>44911</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -81365,7 +81365,7 @@
         <v>44735</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -81438,7 +81438,7 @@
         <v>44960</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -81516,7 +81516,7 @@
         <v>45205</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -81609,7 +81609,7 @@
         <v>44995</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -81687,7 +81687,7 @@
         <v>45376</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -81765,7 +81765,7 @@
         <v>45470</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -81843,7 +81843,7 @@
         <v>46089</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
